--- a/data/merged/2026-10-08/MERGED_IT_Mite-Vacuum_2026-10-08.xlsx
+++ b/data/merged/2026-10-08/MERGED_IT_Mite-Vacuum_2026-10-08.xlsx
@@ -4541,13 +4541,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>16</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>16</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4629,13 +4629,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>18</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
+      <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>18</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4673,13 +4673,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>19</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>19</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5444,138 +5444,6 @@
       </xdr:nvPicPr>
       <xdr:blipFill>
         <a:blip r:embed="rId36" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="37" name="Product 37">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <ns2:creationId id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId37" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="38" name="Product 38">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <ns2:creationId id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId38" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="39" name="Product 39">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <ns2:creationId id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId39" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -5917,7 +5785,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:BR40"/>
+  <dimension ref="A1:BR37"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="5" style="1" customWidth="1"/>
@@ -9392,40 +9260,40 @@
       <c r="B16" s="13"/>
       <c r="C16" s="14" t="inlineStr">
         <is>
-          <t>B0FDWVV95V</t>
+          <t>B0BPKND56B</t>
         </is>
       </c>
       <c r="D16" s="14"/>
       <c r="E16" s="14"/>
       <c r="F16" s="14" t="inlineStr">
         <is>
-          <t>JIGOO</t>
+          <t>Vihoom</t>
         </is>
       </c>
       <c r="G16" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/stores/JIGOO-IT/page/7F1C5254-18CC-4331-A449-F5F68B2E288D?lp_asin=B0FDWVV95V&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.it/Vihoom/b/ref=bl_dp_s_web_76112668031?ie=UTF8&amp;node=76112668031&amp;field-lbr_brands_browse-bin=Vihoom</t>
         </is>
       </c>
       <c r="H16" s="14" t="inlineStr">
         <is>
-          <t>JIGOO T600 Aspiratore Floreale Delight (Plant Essential Oil)</t>
+          <t>Vihoom Aspirapolvere antiacaro per acari pulisci materassi con luce UV e contenitore per polvere permanente HEPA, aspirapolve</t>
         </is>
       </c>
       <c r="I16" s="14"/>
       <c r="J16" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0FDWVV95V?psc=1</t>
+          <t>https://www.amazon.it/dp/B0BPKND56B?psc=1</t>
         </is>
       </c>
       <c r="K16" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/61tL+-AcL6L._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/61soarCZgdL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L16" s="14" t="inlineStr">
         <is>
-          <t>B0FDWVV95V</t>
+          <t>B0BPKND56B</t>
         </is>
       </c>
       <c r="M16" s="14" t="inlineStr">
@@ -9439,13 +9307,13 @@
         </is>
       </c>
       <c r="O16" s="15">
-        <v>217003</v>
+        <v>201244</v>
       </c>
       <c r="P16" s="15">
-        <v>255045</v>
+        <v>11938</v>
       </c>
       <c r="Q16" s="16">
-        <v>0.54</v>
+        <v>0.06</v>
       </c>
       <c r="R16" s="17" t="inlineStr">
         <is>
@@ -9454,53 +9322,51 @@
       </c>
       <c r="S16" s="18" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="T16" s="15">
-        <v>6</v>
-      </c>
-      <c r="U16" s="16"/>
-      <c r="V16" s="15">
-        <v>114</v>
-      </c>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="T16" s="15"/>
+      <c r="U16" s="16">
+        <v>-0.8</v>
+      </c>
+      <c r="V16" s="15"/>
       <c r="W16" s="15"/>
       <c r="X16" s="15"/>
       <c r="Y16" s="19">
         <v>1</v>
       </c>
       <c r="Z16" s="20">
-        <v>18.99</v>
+        <v>40.33</v>
       </c>
       <c r="AA16"/>
       <c r="AB16"/>
       <c r="AC16" s="2"/>
       <c r="AD16" s="19">
-        <v>10</v>
+        <v>289</v>
       </c>
       <c r="AE16" s="15">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AF16" s="21">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AG16" s="22">
-        <v>0.16670000000000001</v>
+        <v>0</v>
       </c>
       <c r="AH16" s="20">
-        <v>2.81</v>
+        <v>5.2</v>
       </c>
       <c r="AI16" s="16">
-        <v>0.7</v>
+        <v>0.72</v>
       </c>
       <c r="AJ16"/>
       <c r="AK16" s="13" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2023-02-23</t>
         </is>
       </c>
       <c r="AL16" s="19">
-        <v>437</v>
+        <v>1322</v>
       </c>
       <c r="AM16" s="13" t="inlineStr">
         <is>
@@ -9510,13 +9376,15 @@
       <c r="AN16" s="13"/>
       <c r="AO16" s="13"/>
       <c r="AP16"/>
-      <c r="AQ16" s="19"/>
+      <c r="AQ16" s="19">
+        <v>10</v>
+      </c>
       <c r="AR16" s="19">
         <v>1</v>
       </c>
       <c r="AS16" s="14" t="inlineStr">
         <is>
-          <t>yefengdianzi</t>
+          <t>PETERTOS Kft.</t>
         </is>
       </c>
       <c r="AT16" s="13" t="inlineStr">
@@ -9526,17 +9394,17 @@
       </c>
       <c r="AU16" s="13" t="inlineStr">
         <is>
-          <t>CN(HK)</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="AV16" s="14" t="inlineStr">
         <is>
-          <t>KWUN TONG HONG KONG 999077 HK</t>
+          <t>Olcsva 4826 HU</t>
         </is>
       </c>
       <c r="AW16" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1OG68CATOOAOD</t>
+          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1AHZ7S75PQI7K</t>
         </is>
       </c>
       <c r="AX16" s="13"/>
@@ -9544,7 +9412,11 @@
       <c r="AZ16" s="13"/>
       <c r="BA16" s="13"/>
       <c r="BB16" s="13"/>
-      <c r="BC16" s="13"/>
+      <c r="BC16" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BD16" s="13"/>
       <c r="BE16" s="13"/>
       <c r="BF16" s="13"/>
@@ -9553,43 +9425,43 @@
       <c r="BI16" s="23"/>
       <c r="BJ16" s="23" t="inlineStr">
         <is>
-          <t>50 g</t>
+          <t>1.62 kg</t>
         </is>
       </c>
       <c r="BK16" s="23" t="inlineStr">
         <is>
-          <t>50.00 g</t>
+          <t>1.62 kg</t>
         </is>
       </c>
       <c r="BL16" s="23" t="inlineStr">
         <is>
-          <t>6L x 1,3l x 8H cm</t>
+          <t>23,5L x 23,5l x 14H cm</t>
         </is>
       </c>
       <c r="BM16" s="23"/>
       <c r="BN16" s="23" t="inlineStr">
         <is>
-          <t>50 g</t>
+          <t>1.6 kg</t>
         </is>
       </c>
       <c r="BO16" s="23" t="inlineStr">
         <is>
-          <t>50.00 g</t>
+          <t>1.60 kg</t>
         </is>
       </c>
       <c r="BP16" s="23" t="inlineStr">
         <is>
-          <t>10 x 6 x 1.5 cm</t>
+          <t>24.3 x 23.4 x 14.4 cm</t>
         </is>
       </c>
       <c r="BQ16" s="23" t="inlineStr">
         <is>
-          <t>10.00 x 6.00 x 1.50 cm</t>
+          <t>24.30 x 23.40 x 14.40 cm</t>
         </is>
       </c>
       <c r="BR16" s="13" t="inlineStr">
         <is>
-          <t>轻型信封</t>
+          <t>标准包裹</t>
         </is>
       </c>
     </row>
@@ -9600,40 +9472,40 @@
       <c r="B17" s="13"/>
       <c r="C17" s="14" t="inlineStr">
         <is>
-          <t>B0BPKND56B</t>
+          <t>B0CSN4RZV3</t>
         </is>
       </c>
       <c r="D17" s="14"/>
       <c r="E17" s="14"/>
       <c r="F17" s="14" t="inlineStr">
         <is>
-          <t>Vihoom</t>
+          <t>Dibea</t>
         </is>
       </c>
       <c r="G17" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/Vihoom/b/ref=bl_dp_s_web_76112668031?ie=UTF8&amp;node=76112668031&amp;field-lbr_brands_browse-bin=Vihoom</t>
+          <t>https://www.amazon.it/stores/Dibea/page/2F0F673F-94DF-4200-9096-92CD398CE8D0?lp_asin=B0CSN4RZV3&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
         </is>
       </c>
       <c r="H17" s="14" t="inlineStr">
         <is>
-          <t>Vihoom Aspirapolvere antiacaro per acari pulisci materassi con luce UV e contenitore per polvere permanente HEPA, aspirapolve</t>
+          <t>Dibea Aspirapolvere a mano per materassi, 18 kpa aspirapolvere acari per materassi, 450 W, sensore acari della polvere, indic</t>
         </is>
       </c>
       <c r="I17" s="14"/>
       <c r="J17" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0BPKND56B?psc=1</t>
+          <t>https://www.amazon.it/dp/B0CSN4RZV3?psc=1</t>
         </is>
       </c>
       <c r="K17" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/61soarCZgdL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/61kgLFAeJWL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L17" s="14" t="inlineStr">
         <is>
-          <t>B0BPKND56B</t>
+          <t>B0CSN4RZV3</t>
         </is>
       </c>
       <c r="M17" s="14" t="inlineStr">
@@ -9647,13 +9519,11 @@
         </is>
       </c>
       <c r="O17" s="15">
-        <v>201244</v>
-      </c>
-      <c r="P17" s="15">
-        <v>11938</v>
-      </c>
+        <v>596751</v>
+      </c>
+      <c r="P17" s="15"/>
       <c r="Q17" s="16">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="R17" s="17" t="inlineStr">
         <is>
@@ -9662,13 +9532,11 @@
       </c>
       <c r="S17" s="18" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>20</t>
         </is>
       </c>
       <c r="T17" s="15"/>
-      <c r="U17" s="16">
-        <v>-0.8</v>
-      </c>
+      <c r="U17" s="16"/>
       <c r="V17" s="15"/>
       <c r="W17" s="15"/>
       <c r="X17" s="15"/>
@@ -9676,37 +9544,37 @@
         <v>1</v>
       </c>
       <c r="Z17" s="20">
-        <v>40.33</v>
+        <v>47.45</v>
       </c>
       <c r="AA17"/>
       <c r="AB17"/>
       <c r="AC17" s="2"/>
       <c r="AD17" s="19">
-        <v>289</v>
+        <v>49</v>
       </c>
       <c r="AE17" s="15">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AF17" s="21">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="AG17" s="22">
         <v>0</v>
       </c>
       <c r="AH17" s="20">
-        <v>5.2</v>
+        <v>5.21</v>
       </c>
       <c r="AI17" s="16">
-        <v>0.72</v>
+        <v>0.74</v>
       </c>
       <c r="AJ17"/>
       <c r="AK17" s="13" t="inlineStr">
         <is>
-          <t>2023-02-23</t>
+          <t>2024-04-27</t>
         </is>
       </c>
       <c r="AL17" s="19">
-        <v>1322</v>
+        <v>894</v>
       </c>
       <c r="AM17" s="13" t="inlineStr">
         <is>
@@ -9724,7 +9592,7 @@
       </c>
       <c r="AS17" s="14" t="inlineStr">
         <is>
-          <t>PETERTOS Kft.</t>
+          <t>DIBEA HOME</t>
         </is>
       </c>
       <c r="AT17" s="13" t="inlineStr">
@@ -9734,17 +9602,17 @@
       </c>
       <c r="AU17" s="13" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="AV17" s="14" t="inlineStr">
         <is>
-          <t>Olcsva 4826 HU</t>
+          <t>苏州市 高新区 江苏省 215000 CN</t>
         </is>
       </c>
       <c r="AW17" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1AHZ7S75PQI7K</t>
+          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3B52P1ZT41O2I</t>
         </is>
       </c>
       <c r="AX17" s="13"/>
@@ -9765,38 +9633,38 @@
       <c r="BI17" s="23"/>
       <c r="BJ17" s="23" t="inlineStr">
         <is>
-          <t>1.62 kg</t>
+          <t>2.2 kg</t>
         </is>
       </c>
       <c r="BK17" s="23" t="inlineStr">
         <is>
-          <t>1.62 kg</t>
+          <t>2.20 kg</t>
         </is>
       </c>
       <c r="BL17" s="23" t="inlineStr">
         <is>
-          <t>23,5L x 23,5l x 14H cm</t>
+          <t>31,8L x 25,2l x 18,5H cm</t>
         </is>
       </c>
       <c r="BM17" s="23"/>
       <c r="BN17" s="23" t="inlineStr">
         <is>
-          <t>1.6 kg</t>
+          <t>3.13 kg</t>
         </is>
       </c>
       <c r="BO17" s="23" t="inlineStr">
         <is>
-          <t>1.60 kg</t>
+          <t>3.13 kg</t>
         </is>
       </c>
       <c r="BP17" s="23" t="inlineStr">
         <is>
-          <t>24.3 x 23.4 x 14.4 cm</t>
+          <t>38.9 x 28.9 x 22.5 cm</t>
         </is>
       </c>
       <c r="BQ17" s="23" t="inlineStr">
         <is>
-          <t>24.30 x 23.40 x 14.40 cm</t>
+          <t>38.90 x 28.90 x 22.50 cm</t>
         </is>
       </c>
       <c r="BR17" s="13" t="inlineStr">
@@ -9812,206 +9680,104 @@
       <c r="B18" s="13"/>
       <c r="C18" s="14" t="inlineStr">
         <is>
-          <t>B0CSN4RZV3</t>
+          <t>B0D454221Z</t>
         </is>
       </c>
       <c r="D18" s="14"/>
       <c r="E18" s="14"/>
-      <c r="F18" s="14" t="inlineStr">
-        <is>
-          <t>Dibea</t>
-        </is>
-      </c>
+      <c r="F18" s="14"/>
       <c r="G18" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/stores/Dibea/page/2F0F673F-94DF-4200-9096-92CD398CE8D0?lp_asin=B0CSN4RZV3&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
+          <t>https://www.amazon.itundefined</t>
         </is>
       </c>
       <c r="H18" s="14" t="inlineStr">
         <is>
-          <t>Dibea Aspirapolvere a mano per materassi, 18 kpa aspirapolvere acari per materassi, 450 W, sensore acari della polvere, indic</t>
+          <t>Aspiratore Acaro per Materassi, 16KPA 700W Potente, Sensore Antiacaro della Polvere con Vento Caldo 65 ℃ per Chi Soffre di Al</t>
         </is>
       </c>
       <c r="I18" s="14"/>
       <c r="J18" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0CSN4RZV3?psc=1</t>
+          <t>https://www.amazon.it/dp/B0D454221Z?psc=1</t>
         </is>
       </c>
       <c r="K18" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/61kgLFAeJWL._AC_US600_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71MEJ7kD0dL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L18" s="14" t="inlineStr">
         <is>
-          <t>B0CSN4RZV3</t>
-        </is>
-      </c>
-      <c r="M18" s="14" t="inlineStr">
-        <is>
-          <t>Casa e cucina:Aspirapolvere e pulizia di pavimenti e finestre:Aspirapolvere:Aspirapolvere per futon</t>
-        </is>
-      </c>
-      <c r="N18" s="14" t="inlineStr">
-        <is>
-          <t>Visualizza i Top 100 nella categoria Casa e c</t>
-        </is>
-      </c>
-      <c r="O18" s="15">
-        <v>596751</v>
-      </c>
+          <t>B0D454221Z</t>
+        </is>
+      </c>
+      <c r="M18" s="14"/>
+      <c r="N18" s="14"/>
+      <c r="O18" s="15"/>
       <c r="P18" s="15"/>
-      <c r="Q18" s="16">
-        <v>0</v>
-      </c>
-      <c r="R18" s="17" t="inlineStr">
-        <is>
-          <t>Aspirapolvere per futon</t>
-        </is>
-      </c>
-      <c r="S18" s="18" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+      <c r="Q18" s="16"/>
+      <c r="R18" s="17"/>
+      <c r="S18" s="18"/>
       <c r="T18" s="15"/>
       <c r="U18" s="16"/>
       <c r="V18" s="15"/>
       <c r="W18" s="15"/>
       <c r="X18" s="15"/>
-      <c r="Y18" s="19">
-        <v>1</v>
-      </c>
-      <c r="Z18" s="20">
-        <v>47.45</v>
-      </c>
+      <c r="Y18" s="19"/>
+      <c r="Z18" s="20"/>
       <c r="AA18"/>
       <c r="AB18"/>
       <c r="AC18" s="2"/>
       <c r="AD18" s="19">
-        <v>49</v>
-      </c>
-      <c r="AE18" s="15">
-        <v>0</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="AE18" s="15"/>
       <c r="AF18" s="21">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="AG18" s="22">
         <v>0</v>
       </c>
-      <c r="AH18" s="20">
-        <v>5.21</v>
-      </c>
+      <c r="AH18" s="20"/>
       <c r="AI18" s="16">
-        <v>0.74</v>
+        <v>0</v>
       </c>
       <c r="AJ18"/>
-      <c r="AK18" s="13" t="inlineStr">
-        <is>
-          <t>2024-04-27</t>
-        </is>
-      </c>
-      <c r="AL18" s="19">
-        <v>894</v>
-      </c>
-      <c r="AM18" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
+      <c r="AK18" s="13"/>
+      <c r="AL18" s="19"/>
+      <c r="AM18" s="13"/>
       <c r="AN18" s="13"/>
       <c r="AO18" s="13"/>
       <c r="AP18"/>
-      <c r="AQ18" s="19">
-        <v>10</v>
-      </c>
-      <c r="AR18" s="19">
-        <v>1</v>
-      </c>
-      <c r="AS18" s="14" t="inlineStr">
-        <is>
-          <t>DIBEA HOME</t>
-        </is>
-      </c>
-      <c r="AT18" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AU18" s="13" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="AV18" s="14" t="inlineStr">
-        <is>
-          <t>苏州市 高新区 江苏省 215000 CN</t>
-        </is>
-      </c>
-      <c r="AW18" s="13" t="inlineStr">
-        <is>
-          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3B52P1ZT41O2I</t>
-        </is>
-      </c>
+      <c r="AQ18" s="19"/>
+      <c r="AR18" s="19"/>
+      <c r="AS18" s="14"/>
+      <c r="AT18" s="13"/>
+      <c r="AU18" s="13"/>
+      <c r="AV18" s="14"/>
+      <c r="AW18" s="13"/>
       <c r="AX18" s="13"/>
       <c r="AY18" s="13"/>
       <c r="AZ18" s="13"/>
       <c r="BA18" s="13"/>
       <c r="BB18" s="13"/>
-      <c r="BC18" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BC18" s="13"/>
       <c r="BD18" s="13"/>
       <c r="BE18" s="13"/>
       <c r="BF18" s="13"/>
       <c r="BG18" s="13"/>
       <c r="BH18" s="14"/>
       <c r="BI18" s="23"/>
-      <c r="BJ18" s="23" t="inlineStr">
-        <is>
-          <t>2.2 kg</t>
-        </is>
-      </c>
-      <c r="BK18" s="23" t="inlineStr">
-        <is>
-          <t>2.20 kg</t>
-        </is>
-      </c>
-      <c r="BL18" s="23" t="inlineStr">
-        <is>
-          <t>31,8L x 25,2l x 18,5H cm</t>
-        </is>
-      </c>
+      <c r="BJ18" s="23"/>
+      <c r="BK18" s="23"/>
+      <c r="BL18" s="23"/>
       <c r="BM18" s="23"/>
-      <c r="BN18" s="23" t="inlineStr">
-        <is>
-          <t>3.13 kg</t>
-        </is>
-      </c>
-      <c r="BO18" s="23" t="inlineStr">
-        <is>
-          <t>3.13 kg</t>
-        </is>
-      </c>
-      <c r="BP18" s="23" t="inlineStr">
-        <is>
-          <t>38.9 x 28.9 x 22.5 cm</t>
-        </is>
-      </c>
-      <c r="BQ18" s="23" t="inlineStr">
-        <is>
-          <t>38.90 x 28.90 x 22.50 cm</t>
-        </is>
-      </c>
-      <c r="BR18" s="13" t="inlineStr">
-        <is>
-          <t>标准包裹</t>
-        </is>
-      </c>
+      <c r="BN18" s="23"/>
+      <c r="BO18" s="23"/>
+      <c r="BP18" s="23"/>
+      <c r="BQ18" s="23"/>
+      <c r="BR18" s="13"/>
     </row>
     <row r="19" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="13">
@@ -10020,104 +9786,216 @@
       <c r="B19" s="13"/>
       <c r="C19" s="14" t="inlineStr">
         <is>
-          <t>B0D454221Z</t>
+          <t>B0DLWJD9MV</t>
         </is>
       </c>
       <c r="D19" s="14"/>
       <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
+      <c r="F19" s="14" t="inlineStr">
+        <is>
+          <t>SIKITUT</t>
+        </is>
+      </c>
       <c r="G19" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.itundefined</t>
+          <t>https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=SIKITUT</t>
         </is>
       </c>
       <c r="H19" s="14" t="inlineStr">
         <is>
-          <t>Aspiratore Acaro per Materassi, 16KPA 700W Potente, Sensore Antiacaro della Polvere con Vento Caldo 65 ℃ per Chi Soffre di Al</t>
+          <t>SIKITUT Battimaterasso, Aspirapolvere per Materassi, Aspira Materasso Antiacaro, Luce UV-C, Rimuove il 99,9% di Batteri e All</t>
         </is>
       </c>
       <c r="I19" s="14"/>
       <c r="J19" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0D454221Z?psc=1</t>
+          <t>https://www.amazon.it/dp/B0DLWJD9MV?psc=1</t>
         </is>
       </c>
       <c r="K19" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71MEJ7kD0dL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71tdIOZsxcL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L19" s="14" t="inlineStr">
         <is>
-          <t>B0D454221Z</t>
-        </is>
-      </c>
-      <c r="M19" s="14"/>
-      <c r="N19" s="14"/>
-      <c r="O19" s="15"/>
+          <t>B0DLWJD9MV</t>
+        </is>
+      </c>
+      <c r="M19" s="14" t="inlineStr">
+        <is>
+          <t>Casa e cucina:Aspirapolvere e pulizia di pavimenti e finestre:Aspirapolvere:Aspirapolvere per futon</t>
+        </is>
+      </c>
+      <c r="N19" s="14" t="inlineStr">
+        <is>
+          <t>Visualizza i Top 100 nella categoria Casa e c</t>
+        </is>
+      </c>
+      <c r="O19" s="15">
+        <v>292642</v>
+      </c>
       <c r="P19" s="15"/>
-      <c r="Q19" s="16"/>
-      <c r="R19" s="17"/>
-      <c r="S19" s="18"/>
+      <c r="Q19" s="16">
+        <v>0</v>
+      </c>
+      <c r="R19" s="17" t="inlineStr">
+        <is>
+          <t>Aspirapolvere per futon</t>
+        </is>
+      </c>
+      <c r="S19" s="18" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
       <c r="T19" s="15"/>
-      <c r="U19" s="16"/>
+      <c r="U19" s="16">
+        <v>-1</v>
+      </c>
       <c r="V19" s="15"/>
       <c r="W19" s="15"/>
       <c r="X19" s="15"/>
-      <c r="Y19" s="19"/>
-      <c r="Z19" s="20"/>
+      <c r="Y19" s="19">
+        <v>1</v>
+      </c>
+      <c r="Z19" s="20">
+        <v>42.98</v>
+      </c>
       <c r="AA19"/>
       <c r="AB19"/>
       <c r="AC19" s="2"/>
       <c r="AD19" s="19">
-        <v>17</v>
-      </c>
-      <c r="AE19" s="15"/>
+        <v>108</v>
+      </c>
+      <c r="AE19" s="15">
+        <v>0</v>
+      </c>
       <c r="AF19" s="21">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="AG19" s="22">
         <v>0</v>
       </c>
-      <c r="AH19" s="20"/>
+      <c r="AH19" s="20">
+        <v>5.48</v>
+      </c>
       <c r="AI19" s="16">
-        <v>0</v>
+        <v>0.72</v>
       </c>
       <c r="AJ19"/>
-      <c r="AK19" s="13"/>
-      <c r="AL19" s="19"/>
-      <c r="AM19" s="13"/>
+      <c r="AK19" s="13" t="inlineStr">
+        <is>
+          <t>2025-01-11</t>
+        </is>
+      </c>
+      <c r="AL19" s="19">
+        <v>634</v>
+      </c>
+      <c r="AM19" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
       <c r="AN19" s="13"/>
       <c r="AO19" s="13"/>
       <c r="AP19"/>
-      <c r="AQ19" s="19"/>
-      <c r="AR19" s="19"/>
-      <c r="AS19" s="14"/>
-      <c r="AT19" s="13"/>
-      <c r="AU19" s="13"/>
-      <c r="AV19" s="14"/>
-      <c r="AW19" s="13"/>
+      <c r="AQ19" s="19">
+        <v>10</v>
+      </c>
+      <c r="AR19" s="19">
+        <v>1</v>
+      </c>
+      <c r="AS19" s="14" t="inlineStr">
+        <is>
+          <t>eusmarthousehold</t>
+        </is>
+      </c>
+      <c r="AT19" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AU19" s="13" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="AV19" s="14" t="inlineStr">
+        <is>
+          <t>Dongguan Guangdong 523710 CN</t>
+        </is>
+      </c>
+      <c r="AW19" s="13" t="inlineStr">
+        <is>
+          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A144XIL10CDODF</t>
+        </is>
+      </c>
       <c r="AX19" s="13"/>
       <c r="AY19" s="13"/>
       <c r="AZ19" s="13"/>
       <c r="BA19" s="13"/>
       <c r="BB19" s="13"/>
-      <c r="BC19" s="13"/>
-      <c r="BD19" s="13"/>
+      <c r="BC19" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="BD19" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BE19" s="13"/>
       <c r="BF19" s="13"/>
       <c r="BG19" s="13"/>
       <c r="BH19" s="14"/>
       <c r="BI19" s="23"/>
-      <c r="BJ19" s="23"/>
-      <c r="BK19" s="23"/>
-      <c r="BL19" s="23"/>
-      <c r="BM19" s="23"/>
-      <c r="BN19" s="23"/>
-      <c r="BO19" s="23"/>
-      <c r="BP19" s="23"/>
-      <c r="BQ19" s="23"/>
-      <c r="BR19" s="13"/>
+      <c r="BJ19" s="23" t="inlineStr">
+        <is>
+          <t>1.23 kg</t>
+        </is>
+      </c>
+      <c r="BK19" s="23" t="inlineStr">
+        <is>
+          <t>1.23 kg</t>
+        </is>
+      </c>
+      <c r="BL19" s="23" t="inlineStr">
+        <is>
+          <t>23.1 x 22.4 x 13 cm</t>
+        </is>
+      </c>
+      <c r="BM19" s="23" t="inlineStr">
+        <is>
+          <t>23.10 x 22.40 x 13.00 cm</t>
+        </is>
+      </c>
+      <c r="BN19" s="23" t="inlineStr">
+        <is>
+          <t>1.28 kg</t>
+        </is>
+      </c>
+      <c r="BO19" s="23" t="inlineStr">
+        <is>
+          <t>1.28 kg</t>
+        </is>
+      </c>
+      <c r="BP19" s="23" t="inlineStr">
+        <is>
+          <t>27.1 x 26.1 x 16.3 cm</t>
+        </is>
+      </c>
+      <c r="BQ19" s="23" t="inlineStr">
+        <is>
+          <t>27.10 x 26.10 x 16.30 cm</t>
+        </is>
+      </c>
+      <c r="BR19" s="13" t="inlineStr">
+        <is>
+          <t>标准包裹</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="13">
@@ -10126,40 +10004,40 @@
       <c r="B20" s="13"/>
       <c r="C20" s="14" t="inlineStr">
         <is>
-          <t>B0DLWJD9MV</t>
+          <t>B0DNYVJ4PL</t>
         </is>
       </c>
       <c r="D20" s="14"/>
       <c r="E20" s="14"/>
       <c r="F20" s="14" t="inlineStr">
         <is>
-          <t>SIKITUT</t>
+          <t>FEPPO</t>
         </is>
       </c>
       <c r="G20" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=SIKITUT</t>
+          <t>https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=FEPPO</t>
         </is>
       </c>
       <c r="H20" s="14" t="inlineStr">
         <is>
-          <t>SIKITUT Battimaterasso, Aspirapolvere per Materassi, Aspira Materasso Antiacaro, Luce UV-C, Rimuove il 99,9% di Batteri e All</t>
+          <t>FEPPO Aspiratore acaro per materassi, 16 Kpa con luce UVC da 253,7 nm, calore 140°F, filtro HEPA e ultrasuoni, aspirapolvere</t>
         </is>
       </c>
       <c r="I20" s="14"/>
       <c r="J20" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0DLWJD9MV?psc=1</t>
+          <t>https://www.amazon.it/dp/B0DNYVJ4PL?psc=1</t>
         </is>
       </c>
       <c r="K20" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71tdIOZsxcL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71X5KPbPpoL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L20" s="14" t="inlineStr">
         <is>
-          <t>B0DLWJD9MV</t>
+          <t>B0DNYVJ4PL</t>
         </is>
       </c>
       <c r="M20" s="14" t="inlineStr">
@@ -10173,7 +10051,7 @@
         </is>
       </c>
       <c r="O20" s="15">
-        <v>292642</v>
+        <v>1380180</v>
       </c>
       <c r="P20" s="15"/>
       <c r="Q20" s="16">
@@ -10186,13 +10064,11 @@
       </c>
       <c r="S20" s="18" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>31</t>
         </is>
       </c>
       <c r="T20" s="15"/>
-      <c r="U20" s="16">
-        <v>-1</v>
-      </c>
+      <c r="U20" s="16"/>
       <c r="V20" s="15"/>
       <c r="W20" s="15"/>
       <c r="X20" s="15"/>
@@ -10200,37 +10076,37 @@
         <v>1</v>
       </c>
       <c r="Z20" s="20">
-        <v>42.98</v>
+        <v>124.76</v>
       </c>
       <c r="AA20"/>
       <c r="AB20"/>
       <c r="AC20" s="2"/>
       <c r="AD20" s="19">
-        <v>108</v>
+        <v>63</v>
       </c>
       <c r="AE20" s="15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF20" s="21">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="AG20" s="22">
         <v>0</v>
       </c>
       <c r="AH20" s="20">
-        <v>5.48</v>
+        <v>5.21</v>
       </c>
       <c r="AI20" s="16">
-        <v>0.72</v>
+        <v>0.81</v>
       </c>
       <c r="AJ20"/>
       <c r="AK20" s="13" t="inlineStr">
         <is>
-          <t>2025-01-11</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AL20" s="19">
-        <v>634</v>
+        <v>557</v>
       </c>
       <c r="AM20" s="13" t="inlineStr">
         <is>
@@ -10248,7 +10124,7 @@
       </c>
       <c r="AS20" s="14" t="inlineStr">
         <is>
-          <t>eusmarthousehold</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="AT20" s="13" t="inlineStr">
@@ -10256,21 +10132,9 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="AU20" s="13" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="AV20" s="14" t="inlineStr">
-        <is>
-          <t>Dongguan Guangdong 523710 CN</t>
-        </is>
-      </c>
-      <c r="AW20" s="13" t="inlineStr">
-        <is>
-          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A144XIL10CDODF</t>
-        </is>
-      </c>
+      <c r="AU20" s="13"/>
+      <c r="AV20" s="14"/>
+      <c r="AW20" s="13"/>
       <c r="AX20" s="13"/>
       <c r="AY20" s="13"/>
       <c r="AZ20" s="13"/>
@@ -10281,11 +10145,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="BD20" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BD20" s="13"/>
       <c r="BE20" s="13"/>
       <c r="BF20" s="13"/>
       <c r="BG20" s="13"/>
@@ -10293,42 +10153,38 @@
       <c r="BI20" s="23"/>
       <c r="BJ20" s="23" t="inlineStr">
         <is>
-          <t>1.23 kg</t>
+          <t>2.22 kg</t>
         </is>
       </c>
       <c r="BK20" s="23" t="inlineStr">
         <is>
-          <t>1.23 kg</t>
+          <t>2.22 kg</t>
         </is>
       </c>
       <c r="BL20" s="23" t="inlineStr">
         <is>
-          <t>23.1 x 22.4 x 13 cm</t>
-        </is>
-      </c>
-      <c r="BM20" s="23" t="inlineStr">
-        <is>
-          <t>23.10 x 22.40 x 13.00 cm</t>
-        </is>
-      </c>
+          <t>30,2L x 25l x 19,5H cm</t>
+        </is>
+      </c>
+      <c r="BM20" s="23"/>
       <c r="BN20" s="23" t="inlineStr">
         <is>
-          <t>1.28 kg</t>
+          <t>2.22 kg</t>
         </is>
       </c>
       <c r="BO20" s="23" t="inlineStr">
         <is>
-          <t>1.28 kg</t>
+          <t>2.22 kg</t>
         </is>
       </c>
       <c r="BP20" s="23" t="inlineStr">
         <is>
-          <t>27.1 x 26.1 x 16.3 cm</t>
+          <t>36.9 x 29.8 x 19.8 cm</t>
         </is>
       </c>
       <c r="BQ20" s="23" t="inlineStr">
         <is>
-          <t>27.10 x 26.10 x 16.30 cm</t>
+          <t>36.90 x 29.80 x 19.80 cm</t>
         </is>
       </c>
       <c r="BR20" s="13" t="inlineStr">
@@ -10344,40 +10200,40 @@
       <c r="B21" s="13"/>
       <c r="C21" s="14" t="inlineStr">
         <is>
-          <t>B0DNYVJ4PL</t>
+          <t>B0DNZ5LDQX</t>
         </is>
       </c>
       <c r="D21" s="14"/>
       <c r="E21" s="14"/>
       <c r="F21" s="14" t="inlineStr">
         <is>
-          <t>FEPPO</t>
+          <t>Liwankaqi</t>
         </is>
       </c>
       <c r="G21" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=FEPPO</t>
+          <t>https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Liwankaqi</t>
         </is>
       </c>
       <c r="H21" s="14" t="inlineStr">
         <is>
-          <t>FEPPO Aspiratore acaro per materassi, 16 Kpa con luce UVC da 253,7 nm, calore 140°F, filtro HEPA e ultrasuoni, aspirapolvere</t>
+          <t>Liwankaqi Aspiratore per acari 14 kPa, velocità di sterilizzazione con lampade UV LED, aspirapolvere per materassi con deterg</t>
         </is>
       </c>
       <c r="I21" s="14"/>
       <c r="J21" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0DNYVJ4PL?psc=1</t>
+          <t>https://www.amazon.it/dp/B0DNZ5LDQX?psc=1</t>
         </is>
       </c>
       <c r="K21" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71X5KPbPpoL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/61YjHSHoT6L._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L21" s="14" t="inlineStr">
         <is>
-          <t>B0DNYVJ4PL</t>
+          <t>B0DNZ5LDQX</t>
         </is>
       </c>
       <c r="M21" s="14" t="inlineStr">
@@ -10391,7 +10247,7 @@
         </is>
       </c>
       <c r="O21" s="15">
-        <v>1380180</v>
+        <v>710896</v>
       </c>
       <c r="P21" s="15"/>
       <c r="Q21" s="16">
@@ -10404,7 +10260,7 @@
       </c>
       <c r="S21" s="18" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>23</t>
         </is>
       </c>
       <c r="T21" s="15"/>
@@ -10416,37 +10272,37 @@
         <v>1</v>
       </c>
       <c r="Z21" s="20">
-        <v>124.76</v>
+        <v>45.99</v>
       </c>
       <c r="AA21"/>
       <c r="AB21"/>
       <c r="AC21" s="2"/>
       <c r="AD21" s="19">
-        <v>63</v>
+        <v>7</v>
       </c>
       <c r="AE21" s="15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF21" s="21">
-        <v>4.6</v>
+        <v>3.4</v>
       </c>
       <c r="AG21" s="22">
         <v>0</v>
       </c>
       <c r="AH21" s="20">
-        <v>5.21</v>
+        <v>5.48</v>
       </c>
       <c r="AI21" s="16">
-        <v>0.81</v>
+        <v>0.73</v>
       </c>
       <c r="AJ21"/>
       <c r="AK21" s="13" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2024-11-27</t>
         </is>
       </c>
       <c r="AL21" s="19">
-        <v>557</v>
+        <v>679</v>
       </c>
       <c r="AM21" s="13" t="inlineStr">
         <is>
@@ -10457,14 +10313,14 @@
       <c r="AO21" s="13"/>
       <c r="AP21"/>
       <c r="AQ21" s="19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AR21" s="19">
         <v>1</v>
       </c>
       <c r="AS21" s="14" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>liwantech</t>
         </is>
       </c>
       <c r="AT21" s="13" t="inlineStr">
@@ -10472,9 +10328,21 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="AU21" s="13"/>
-      <c r="AV21" s="14"/>
-      <c r="AW21" s="13"/>
+      <c r="AU21" s="13" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="AV21" s="14" t="inlineStr">
+        <is>
+          <t>深圳市 南山区 广东 518000 CN</t>
+        </is>
+      </c>
+      <c r="AW21" s="13" t="inlineStr">
+        <is>
+          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1CO438NU9H9Y</t>
+        </is>
+      </c>
       <c r="AX21" s="13"/>
       <c r="AY21" s="13"/>
       <c r="AZ21" s="13"/>
@@ -10485,7 +10353,11 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="BD21" s="13"/>
+      <c r="BD21" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BE21" s="13"/>
       <c r="BF21" s="13"/>
       <c r="BG21" s="13"/>
@@ -10493,38 +10365,42 @@
       <c r="BI21" s="23"/>
       <c r="BJ21" s="23" t="inlineStr">
         <is>
-          <t>2.22 kg</t>
+          <t>955 g</t>
         </is>
       </c>
       <c r="BK21" s="23" t="inlineStr">
         <is>
-          <t>2.22 kg</t>
+          <t>955.00 g</t>
         </is>
       </c>
       <c r="BL21" s="23" t="inlineStr">
         <is>
-          <t>30,2L x 25l x 19,5H cm</t>
-        </is>
-      </c>
-      <c r="BM21" s="23"/>
+          <t>26 x 25 x 20 cm</t>
+        </is>
+      </c>
+      <c r="BM21" s="23" t="inlineStr">
+        <is>
+          <t>26.00 x 25.00 x 20.00 cm</t>
+        </is>
+      </c>
       <c r="BN21" s="23" t="inlineStr">
         <is>
-          <t>2.22 kg</t>
+          <t>955 g</t>
         </is>
       </c>
       <c r="BO21" s="23" t="inlineStr">
         <is>
-          <t>2.22 kg</t>
+          <t>955.00 g</t>
         </is>
       </c>
       <c r="BP21" s="23" t="inlineStr">
         <is>
-          <t>36.9 x 29.8 x 19.8 cm</t>
+          <t>26 x 25 x 20 cm</t>
         </is>
       </c>
       <c r="BQ21" s="23" t="inlineStr">
         <is>
-          <t>36.90 x 29.80 x 19.80 cm</t>
+          <t>26.00 x 25.00 x 20.00 cm</t>
         </is>
       </c>
       <c r="BR21" s="13" t="inlineStr">
@@ -10540,214 +10416,104 @@
       <c r="B22" s="13"/>
       <c r="C22" s="14" t="inlineStr">
         <is>
-          <t>B0DNZ5LDQX</t>
+          <t>B0F2MQCLRJ</t>
         </is>
       </c>
       <c r="D22" s="14"/>
       <c r="E22" s="14"/>
-      <c r="F22" s="14" t="inlineStr">
-        <is>
-          <t>Liwankaqi</t>
-        </is>
-      </c>
+      <c r="F22" s="14"/>
       <c r="G22" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Liwankaqi</t>
+          <t>https://www.amazon.itundefined</t>
         </is>
       </c>
       <c r="H22" s="14" t="inlineStr">
         <is>
-          <t>Liwankaqi Aspiratore per acari 14 kPa, velocità di sterilizzazione con lampade UV LED, aspirapolvere per materassi con deterg</t>
+          <t>CREATULIZE Aspirapolvere antiacaro per materassi, con 1 dispositivo Slap e 3 filtri, filtro portatile per aspirapolvere domes</t>
         </is>
       </c>
       <c r="I22" s="14"/>
       <c r="J22" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0DNZ5LDQX?psc=1</t>
+          <t>https://www.amazon.it/dp/B0F2MQCLRJ?psc=1</t>
         </is>
       </c>
       <c r="K22" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/61YjHSHoT6L._AC_US600_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/51INLecMxKL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L22" s="14" t="inlineStr">
         <is>
-          <t>B0DNZ5LDQX</t>
-        </is>
-      </c>
-      <c r="M22" s="14" t="inlineStr">
-        <is>
-          <t>Casa e cucina:Aspirapolvere e pulizia di pavimenti e finestre:Aspirapolvere:Aspirapolvere per futon</t>
-        </is>
-      </c>
-      <c r="N22" s="14" t="inlineStr">
-        <is>
-          <t>Visualizza i Top 100 nella categoria Casa e c</t>
-        </is>
-      </c>
-      <c r="O22" s="15">
-        <v>710896</v>
-      </c>
+          <t>B0F2MQCLRJ</t>
+        </is>
+      </c>
+      <c r="M22" s="14"/>
+      <c r="N22" s="14"/>
+      <c r="O22" s="15"/>
       <c r="P22" s="15"/>
-      <c r="Q22" s="16">
-        <v>0</v>
-      </c>
-      <c r="R22" s="17" t="inlineStr">
-        <is>
-          <t>Aspirapolvere per futon</t>
-        </is>
-      </c>
-      <c r="S22" s="18" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
+      <c r="Q22" s="16"/>
+      <c r="R22" s="17"/>
+      <c r="S22" s="18"/>
       <c r="T22" s="15"/>
       <c r="U22" s="16"/>
       <c r="V22" s="15"/>
       <c r="W22" s="15"/>
       <c r="X22" s="15"/>
-      <c r="Y22" s="19">
-        <v>1</v>
-      </c>
-      <c r="Z22" s="20">
-        <v>45.99</v>
-      </c>
+      <c r="Y22" s="19"/>
+      <c r="Z22" s="20"/>
       <c r="AA22"/>
       <c r="AB22"/>
       <c r="AC22" s="2"/>
       <c r="AD22" s="19">
-        <v>7</v>
-      </c>
-      <c r="AE22" s="15">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AE22" s="15"/>
       <c r="AF22" s="21">
-        <v>3.4</v>
+        <v>5</v>
       </c>
       <c r="AG22" s="22">
         <v>0</v>
       </c>
-      <c r="AH22" s="20">
-        <v>5.48</v>
-      </c>
+      <c r="AH22" s="20"/>
       <c r="AI22" s="16">
-        <v>0.73</v>
+        <v>0</v>
       </c>
       <c r="AJ22"/>
-      <c r="AK22" s="13" t="inlineStr">
-        <is>
-          <t>2024-11-27</t>
-        </is>
-      </c>
-      <c r="AL22" s="19">
-        <v>679</v>
-      </c>
-      <c r="AM22" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
+      <c r="AK22" s="13"/>
+      <c r="AL22" s="19"/>
+      <c r="AM22" s="13"/>
       <c r="AN22" s="13"/>
       <c r="AO22" s="13"/>
       <c r="AP22"/>
-      <c r="AQ22" s="19">
-        <v>9</v>
-      </c>
-      <c r="AR22" s="19">
-        <v>1</v>
-      </c>
-      <c r="AS22" s="14" t="inlineStr">
-        <is>
-          <t>liwantech</t>
-        </is>
-      </c>
-      <c r="AT22" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AU22" s="13" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="AV22" s="14" t="inlineStr">
-        <is>
-          <t>深圳市 南山区 广东 518000 CN</t>
-        </is>
-      </c>
-      <c r="AW22" s="13" t="inlineStr">
-        <is>
-          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1CO438NU9H9Y</t>
-        </is>
-      </c>
+      <c r="AQ22" s="19"/>
+      <c r="AR22" s="19"/>
+      <c r="AS22" s="14"/>
+      <c r="AT22" s="13"/>
+      <c r="AU22" s="13"/>
+      <c r="AV22" s="14"/>
+      <c r="AW22" s="13"/>
       <c r="AX22" s="13"/>
       <c r="AY22" s="13"/>
       <c r="AZ22" s="13"/>
       <c r="BA22" s="13"/>
       <c r="BB22" s="13"/>
-      <c r="BC22" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BD22" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BC22" s="13"/>
+      <c r="BD22" s="13"/>
       <c r="BE22" s="13"/>
       <c r="BF22" s="13"/>
       <c r="BG22" s="13"/>
       <c r="BH22" s="14"/>
       <c r="BI22" s="23"/>
-      <c r="BJ22" s="23" t="inlineStr">
-        <is>
-          <t>955 g</t>
-        </is>
-      </c>
-      <c r="BK22" s="23" t="inlineStr">
-        <is>
-          <t>955.00 g</t>
-        </is>
-      </c>
-      <c r="BL22" s="23" t="inlineStr">
-        <is>
-          <t>26 x 25 x 20 cm</t>
-        </is>
-      </c>
-      <c r="BM22" s="23" t="inlineStr">
-        <is>
-          <t>26.00 x 25.00 x 20.00 cm</t>
-        </is>
-      </c>
-      <c r="BN22" s="23" t="inlineStr">
-        <is>
-          <t>955 g</t>
-        </is>
-      </c>
-      <c r="BO22" s="23" t="inlineStr">
-        <is>
-          <t>955.00 g</t>
-        </is>
-      </c>
-      <c r="BP22" s="23" t="inlineStr">
-        <is>
-          <t>26 x 25 x 20 cm</t>
-        </is>
-      </c>
-      <c r="BQ22" s="23" t="inlineStr">
-        <is>
-          <t>26.00 x 25.00 x 20.00 cm</t>
-        </is>
-      </c>
-      <c r="BR22" s="13" t="inlineStr">
-        <is>
-          <t>标准包裹</t>
-        </is>
-      </c>
+      <c r="BJ22" s="23"/>
+      <c r="BK22" s="23"/>
+      <c r="BL22" s="23"/>
+      <c r="BM22" s="23"/>
+      <c r="BN22" s="23"/>
+      <c r="BO22" s="23"/>
+      <c r="BP22" s="23"/>
+      <c r="BQ22" s="23"/>
+      <c r="BR22" s="13"/>
     </row>
     <row r="23" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="13">
@@ -10756,83 +10522,149 @@
       <c r="B23" s="13"/>
       <c r="C23" s="14" t="inlineStr">
         <is>
-          <t>B0F2MQCLRJ</t>
+          <t>B0F37ZFRR3</t>
         </is>
       </c>
       <c r="D23" s="14"/>
       <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
+      <c r="F23" s="14" t="inlineStr">
+        <is>
+          <t>Lambluefly</t>
+        </is>
+      </c>
       <c r="G23" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.itundefined</t>
+          <t>https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Lambluefly</t>
         </is>
       </c>
       <c r="H23" s="14" t="inlineStr">
         <is>
-          <t>CREATULIZE Aspirapolvere antiacaro per materassi, con 1 dispositivo Slap e 3 filtri, filtro portatile per aspirapolvere domes</t>
+          <t>Lambluefly Aspirapolvere per Materassi 15KPa, 700W Battimaterasso Antiacaro con Luce-UV 65°C e Ultrasuoni, Doppia Tazza Antip</t>
         </is>
       </c>
       <c r="I23" s="14"/>
       <c r="J23" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0F2MQCLRJ?psc=1</t>
+          <t>https://www.amazon.it/dp/B0F37ZFRR3?psc=1</t>
         </is>
       </c>
       <c r="K23" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/51INLecMxKL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71c5xOT1pjL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L23" s="14" t="inlineStr">
         <is>
-          <t>B0F2MQCLRJ</t>
-        </is>
-      </c>
-      <c r="M23" s="14"/>
-      <c r="N23" s="14"/>
-      <c r="O23" s="15"/>
+          <t>B0F37ZFRR3</t>
+        </is>
+      </c>
+      <c r="M23" s="14" t="inlineStr">
+        <is>
+          <t>Casa e cucina:Aspirapolvere e pulizia di pavimenti e finestre:Aspirapolvere:Aspirapolvere per futon</t>
+        </is>
+      </c>
+      <c r="N23" s="14" t="inlineStr">
+        <is>
+          <t>Visualizza i Top 100 nella categoria Casa e c</t>
+        </is>
+      </c>
+      <c r="O23" s="15">
+        <v>677712</v>
+      </c>
       <c r="P23" s="15"/>
-      <c r="Q23" s="16"/>
-      <c r="R23" s="17"/>
-      <c r="S23" s="18"/>
+      <c r="Q23" s="16">
+        <v>0</v>
+      </c>
+      <c r="R23" s="17" t="inlineStr">
+        <is>
+          <t>Aspirapolvere per futon</t>
+        </is>
+      </c>
+      <c r="S23" s="18" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
       <c r="T23" s="15"/>
       <c r="U23" s="16"/>
       <c r="V23" s="15"/>
       <c r="W23" s="15"/>
       <c r="X23" s="15"/>
-      <c r="Y23" s="19"/>
-      <c r="Z23" s="20"/>
+      <c r="Y23" s="19">
+        <v>1</v>
+      </c>
+      <c r="Z23" s="20">
+        <v>59.99</v>
+      </c>
       <c r="AA23"/>
       <c r="AB23"/>
       <c r="AC23" s="2"/>
       <c r="AD23" s="19">
-        <v>1</v>
-      </c>
-      <c r="AE23" s="15"/>
+        <v>11</v>
+      </c>
+      <c r="AE23" s="15">
+        <v>0</v>
+      </c>
       <c r="AF23" s="21">
-        <v>5</v>
+        <v>2.9</v>
       </c>
       <c r="AG23" s="22">
         <v>0</v>
       </c>
-      <c r="AH23" s="20"/>
+      <c r="AH23" s="20">
+        <v>5.48</v>
+      </c>
       <c r="AI23" s="16">
-        <v>0</v>
+        <v>0.76</v>
       </c>
       <c r="AJ23"/>
-      <c r="AK23" s="13"/>
-      <c r="AL23" s="19"/>
-      <c r="AM23" s="13"/>
+      <c r="AK23" s="13" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AL23" s="19">
+        <v>545</v>
+      </c>
+      <c r="AM23" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
       <c r="AN23" s="13"/>
       <c r="AO23" s="13"/>
       <c r="AP23"/>
-      <c r="AQ23" s="19"/>
-      <c r="AR23" s="19"/>
-      <c r="AS23" s="14"/>
-      <c r="AT23" s="13"/>
-      <c r="AU23" s="13"/>
-      <c r="AV23" s="14"/>
-      <c r="AW23" s="13"/>
+      <c r="AQ23" s="19">
+        <v>9</v>
+      </c>
+      <c r="AR23" s="19">
+        <v>1</v>
+      </c>
+      <c r="AS23" s="14" t="inlineStr">
+        <is>
+          <t>Fiercelion</t>
+        </is>
+      </c>
+      <c r="AT23" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AU23" s="13" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="AV23" s="14" t="inlineStr">
+        <is>
+          <t>汕头市 金平区 广东省 515000 CN</t>
+        </is>
+      </c>
+      <c r="AW23" s="13" t="inlineStr">
+        <is>
+          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2ICHMKIWU9TG5</t>
+        </is>
+      </c>
       <c r="AX23" s="13"/>
       <c r="AY23" s="13"/>
       <c r="AZ23" s="13"/>
@@ -10845,15 +10677,51 @@
       <c r="BG23" s="13"/>
       <c r="BH23" s="14"/>
       <c r="BI23" s="23"/>
-      <c r="BJ23" s="23"/>
-      <c r="BK23" s="23"/>
-      <c r="BL23" s="23"/>
-      <c r="BM23" s="23"/>
-      <c r="BN23" s="23"/>
-      <c r="BO23" s="23"/>
-      <c r="BP23" s="23"/>
-      <c r="BQ23" s="23"/>
-      <c r="BR23" s="13"/>
+      <c r="BJ23" s="23" t="inlineStr">
+        <is>
+          <t>1,98 Kilograms</t>
+        </is>
+      </c>
+      <c r="BK23" s="23" t="inlineStr">
+        <is>
+          <t>1.98 kg</t>
+        </is>
+      </c>
+      <c r="BL23" s="23" t="inlineStr">
+        <is>
+          <t>28 x 20 x 14 cm</t>
+        </is>
+      </c>
+      <c r="BM23" s="23" t="inlineStr">
+        <is>
+          <t>28.00 x 20.00 x 14.00 cm</t>
+        </is>
+      </c>
+      <c r="BN23" s="23" t="inlineStr">
+        <is>
+          <t>1.98 kg</t>
+        </is>
+      </c>
+      <c r="BO23" s="23" t="inlineStr">
+        <is>
+          <t>1.98 kg</t>
+        </is>
+      </c>
+      <c r="BP23" s="23" t="inlineStr">
+        <is>
+          <t>33.1 x 23.7 x 16.1 cm</t>
+        </is>
+      </c>
+      <c r="BQ23" s="23" t="inlineStr">
+        <is>
+          <t>33.10 x 23.70 x 16.10 cm</t>
+        </is>
+      </c>
+      <c r="BR23" s="13" t="inlineStr">
+        <is>
+          <t>标准包裹</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="13">
@@ -10862,40 +10730,40 @@
       <c r="B24" s="13"/>
       <c r="C24" s="14" t="inlineStr">
         <is>
-          <t>B0F37ZFRR3</t>
+          <t>B0F6XNKG8M</t>
         </is>
       </c>
       <c r="D24" s="14"/>
       <c r="E24" s="14"/>
       <c r="F24" s="14" t="inlineStr">
         <is>
-          <t>Lambluefly</t>
+          <t>Tiazhan</t>
         </is>
       </c>
       <c r="G24" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Lambluefly</t>
+          <t>https://www.amazon.it/stores/Tiazhan/page/5D8B0E80-8C93-44AB-A84E-49819E75E76B?lp_asin=B0F6XNKG8M&amp;ref_=ast_bln</t>
         </is>
       </c>
       <c r="H24" s="14" t="inlineStr">
         <is>
-          <t>Lambluefly Aspirapolvere per Materassi 15KPa, 700W Battimaterasso Antiacaro con Luce-UV 65°C e Ultrasuoni, Doppia Tazza Antip</t>
+          <t>Tiazhan Battimaterasso, 400W Aspirapolvere per Materassi,con Lampada Germicida Luce UV-C,60 °C Aria Calda, Filtro HEPA,Può Ri</t>
         </is>
       </c>
       <c r="I24" s="14"/>
       <c r="J24" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0F37ZFRR3?psc=1</t>
+          <t>https://www.amazon.it/dp/B0F6XNKG8M?psc=1</t>
         </is>
       </c>
       <c r="K24" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71c5xOT1pjL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71iADJb-ECL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L24" s="14" t="inlineStr">
         <is>
-          <t>B0F37ZFRR3</t>
+          <t>B0F6XNKG8M</t>
         </is>
       </c>
       <c r="M24" s="14" t="inlineStr">
@@ -10909,7 +10777,7 @@
         </is>
       </c>
       <c r="O24" s="15">
-        <v>677712</v>
+        <v>631174</v>
       </c>
       <c r="P24" s="15"/>
       <c r="Q24" s="16">
@@ -10922,7 +10790,7 @@
       </c>
       <c r="S24" s="18" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="T24" s="15"/>
@@ -10934,37 +10802,37 @@
         <v>1</v>
       </c>
       <c r="Z24" s="20">
-        <v>59.99</v>
+        <v>51.33</v>
       </c>
       <c r="AA24"/>
       <c r="AB24"/>
       <c r="AC24" s="2"/>
       <c r="AD24" s="19">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AE24" s="15">
         <v>0</v>
       </c>
       <c r="AF24" s="21">
-        <v>2.9</v>
+        <v>3.8</v>
       </c>
       <c r="AG24" s="22">
         <v>0</v>
       </c>
       <c r="AH24" s="20">
-        <v>5.48</v>
+        <v>5.46</v>
       </c>
       <c r="AI24" s="16">
-        <v>0.76</v>
+        <v>0.74</v>
       </c>
       <c r="AJ24"/>
       <c r="AK24" s="13" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="AL24" s="19">
-        <v>545</v>
+        <v>352</v>
       </c>
       <c r="AM24" s="13" t="inlineStr">
         <is>
@@ -10982,7 +10850,7 @@
       </c>
       <c r="AS24" s="14" t="inlineStr">
         <is>
-          <t>Fiercelion</t>
+          <t>NOEL AND RUTH JOHNSTON LTD</t>
         </is>
       </c>
       <c r="AT24" s="13" t="inlineStr">
@@ -10992,17 +10860,17 @@
       </c>
       <c r="AU24" s="13" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="AV24" s="14" t="inlineStr">
         <is>
-          <t>汕头市 金平区 广东省 515000 CN</t>
+          <t>NORTHERN IRELAND BT2 7FD GB</t>
         </is>
       </c>
       <c r="AW24" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2ICHMKIWU9TG5</t>
+          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1P6U062ILG5ZO</t>
         </is>
       </c>
       <c r="AX24" s="13"/>
@@ -11010,7 +10878,11 @@
       <c r="AZ24" s="13"/>
       <c r="BA24" s="13"/>
       <c r="BB24" s="13"/>
-      <c r="BC24" s="13"/>
+      <c r="BC24" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BD24" s="13"/>
       <c r="BE24" s="13"/>
       <c r="BF24" s="13"/>
@@ -11019,42 +10891,38 @@
       <c r="BI24" s="23"/>
       <c r="BJ24" s="23" t="inlineStr">
         <is>
-          <t>1,98 Kilograms</t>
+          <t>2,06 Kilograms</t>
         </is>
       </c>
       <c r="BK24" s="23" t="inlineStr">
         <is>
-          <t>1.98 kg</t>
+          <t>2.06 kg</t>
         </is>
       </c>
       <c r="BL24" s="23" t="inlineStr">
         <is>
-          <t>28 x 20 x 14 cm</t>
-        </is>
-      </c>
-      <c r="BM24" s="23" t="inlineStr">
-        <is>
-          <t>28.00 x 20.00 x 14.00 cm</t>
-        </is>
-      </c>
+          <t>28L x 15l x 68H cm</t>
+        </is>
+      </c>
+      <c r="BM24" s="23"/>
       <c r="BN24" s="23" t="inlineStr">
         <is>
-          <t>1.98 kg</t>
+          <t>2.06 kg</t>
         </is>
       </c>
       <c r="BO24" s="23" t="inlineStr">
         <is>
-          <t>1.98 kg</t>
+          <t>2.06 kg</t>
         </is>
       </c>
       <c r="BP24" s="23" t="inlineStr">
         <is>
-          <t>33.1 x 23.7 x 16.1 cm</t>
+          <t>34.4 x 28.5 x 22.2 cm</t>
         </is>
       </c>
       <c r="BQ24" s="23" t="inlineStr">
         <is>
-          <t>33.10 x 23.70 x 16.10 cm</t>
+          <t>34.40 x 28.50 x 22.20 cm</t>
         </is>
       </c>
       <c r="BR24" s="13" t="inlineStr">
@@ -11070,40 +10938,40 @@
       <c r="B25" s="13"/>
       <c r="C25" s="14" t="inlineStr">
         <is>
-          <t>B0F6XNKG8M</t>
+          <t>B0F8HD3649</t>
         </is>
       </c>
       <c r="D25" s="14"/>
       <c r="E25" s="14"/>
       <c r="F25" s="14" t="inlineStr">
         <is>
-          <t>Tiazhan</t>
+          <t>Mayking</t>
         </is>
       </c>
       <c r="G25" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/stores/Tiazhan/page/5D8B0E80-8C93-44AB-A84E-49819E75E76B?lp_asin=B0F6XNKG8M&amp;ref_=ast_bln</t>
+          <t>https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Mayking</t>
         </is>
       </c>
       <c r="H25" s="14" t="inlineStr">
         <is>
-          <t>Tiazhan Battimaterasso, 400W Aspirapolvere per Materassi,con Lampada Germicida Luce UV-C,60 °C Aria Calda, Filtro HEPA,Può Ri</t>
+          <t>Mayking Antiacaro Aspirapolvere Con Luce Uv, 16 KpasRiscaldamento A 65 °C, Filtro Hepa, Ultrasuoni, Aromaterapia, Doppio Fi</t>
         </is>
       </c>
       <c r="I25" s="14"/>
       <c r="J25" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0F6XNKG8M?psc=1</t>
+          <t>https://www.amazon.it/dp/B0F8HD3649?psc=1</t>
         </is>
       </c>
       <c r="K25" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71iADJb-ECL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71CtAiuTm1L._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L25" s="14" t="inlineStr">
         <is>
-          <t>B0F6XNKG8M</t>
+          <t>B0F8HD3649</t>
         </is>
       </c>
       <c r="M25" s="14" t="inlineStr">
@@ -11117,11 +10985,13 @@
         </is>
       </c>
       <c r="O25" s="15">
-        <v>631174</v>
-      </c>
-      <c r="P25" s="15"/>
+        <v>1039449</v>
+      </c>
+      <c r="P25" s="15">
+        <v>-7413</v>
+      </c>
       <c r="Q25" s="16">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="R25" s="17" t="inlineStr">
         <is>
@@ -11130,7 +11000,7 @@
       </c>
       <c r="S25" s="18" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>28</t>
         </is>
       </c>
       <c r="T25" s="15"/>
@@ -11142,37 +11012,37 @@
         <v>1</v>
       </c>
       <c r="Z25" s="20">
-        <v>51.33</v>
+        <v>106.99</v>
       </c>
       <c r="AA25"/>
       <c r="AB25"/>
       <c r="AC25" s="2"/>
       <c r="AD25" s="19">
-        <v>10</v>
+        <v>94</v>
       </c>
       <c r="AE25" s="15">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AF25" s="21">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="AG25" s="22">
         <v>0</v>
       </c>
       <c r="AH25" s="20">
-        <v>5.46</v>
+        <v>8.68</v>
       </c>
       <c r="AI25" s="16">
-        <v>0.74</v>
+        <v>0.77</v>
       </c>
       <c r="AJ25"/>
       <c r="AK25" s="13" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="AL25" s="19">
-        <v>352</v>
+        <v>393</v>
       </c>
       <c r="AM25" s="13" t="inlineStr">
         <is>
@@ -11183,14 +11053,14 @@
       <c r="AO25" s="13"/>
       <c r="AP25"/>
       <c r="AQ25" s="19">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AR25" s="19">
         <v>1</v>
       </c>
       <c r="AS25" s="14" t="inlineStr">
         <is>
-          <t>NOEL AND RUTH JOHNSTON LTD</t>
+          <t>Teant</t>
         </is>
       </c>
       <c r="AT25" s="13" t="inlineStr">
@@ -11200,17 +11070,17 @@
       </c>
       <c r="AU25" s="13" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="AV25" s="14" t="inlineStr">
         <is>
-          <t>NORTHERN IRELAND BT2 7FD GB</t>
+          <t>郑州市 河南 450000 CN</t>
         </is>
       </c>
       <c r="AW25" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1P6U062ILG5ZO</t>
+          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3EVTWEH1TBVG5</t>
         </is>
       </c>
       <c r="AX25" s="13"/>
@@ -11231,43 +11101,47 @@
       <c r="BI25" s="23"/>
       <c r="BJ25" s="23" t="inlineStr">
         <is>
-          <t>2,06 Kilograms</t>
+          <t>1.9 kg</t>
         </is>
       </c>
       <c r="BK25" s="23" t="inlineStr">
         <is>
-          <t>2.06 kg</t>
+          <t>1.90 kg</t>
         </is>
       </c>
       <c r="BL25" s="23" t="inlineStr">
         <is>
-          <t>28L x 15l x 68H cm</t>
-        </is>
-      </c>
-      <c r="BM25" s="23"/>
+          <t>38 x 35 x 25 cm</t>
+        </is>
+      </c>
+      <c r="BM25" s="23" t="inlineStr">
+        <is>
+          <t>38.00 x 35.00 x 25.00 cm</t>
+        </is>
+      </c>
       <c r="BN25" s="23" t="inlineStr">
         <is>
-          <t>2.06 kg</t>
+          <t>2.49 kg</t>
         </is>
       </c>
       <c r="BO25" s="23" t="inlineStr">
         <is>
-          <t>2.06 kg</t>
+          <t>2.49 kg</t>
         </is>
       </c>
       <c r="BP25" s="23" t="inlineStr">
         <is>
-          <t>34.4 x 28.5 x 22.2 cm</t>
+          <t>33.5 x 28 x 27 cm</t>
         </is>
       </c>
       <c r="BQ25" s="23" t="inlineStr">
         <is>
-          <t>34.40 x 28.50 x 22.20 cm</t>
+          <t>33.50 x 28.00 x 27.00 cm</t>
         </is>
       </c>
       <c r="BR25" s="13" t="inlineStr">
         <is>
-          <t>标准包裹</t>
+          <t>轻型标准大件</t>
         </is>
       </c>
     </row>
@@ -11278,40 +11152,40 @@
       <c r="B26" s="13"/>
       <c r="C26" s="14" t="inlineStr">
         <is>
-          <t>B0F8HD3649</t>
+          <t>B0F9NJM4V9</t>
         </is>
       </c>
       <c r="D26" s="14"/>
       <c r="E26" s="14"/>
       <c r="F26" s="14" t="inlineStr">
         <is>
-          <t>Mayking</t>
+          <t>Liwankaqi</t>
         </is>
       </c>
       <c r="G26" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Mayking</t>
+          <t>https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Liwankaqi</t>
         </is>
       </c>
       <c r="H26" s="14" t="inlineStr">
         <is>
-          <t>Mayking Antiacaro Aspirapolvere Con Luce Uv, 16 KpasRiscaldamento A 65 °C, Filtro Hepa, Ultrasuoni, Aromaterapia, Doppio Fi</t>
+          <t>Liwankaqi Aspiratore acaro per materassi, aspirapolvere acari con UVC e ultrasuoni, aspirazione 8KPa senza fili, anti-allerge</t>
         </is>
       </c>
       <c r="I26" s="14"/>
       <c r="J26" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0F8HD3649?psc=1</t>
+          <t>https://www.amazon.it/dp/B0F9NJM4V9?psc=1</t>
         </is>
       </c>
       <c r="K26" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71CtAiuTm1L._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/61GdOBS8v+L._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L26" s="14" t="inlineStr">
         <is>
-          <t>B0F8HD3649</t>
+          <t>B0F9NJM4V9</t>
         </is>
       </c>
       <c r="M26" s="14" t="inlineStr">
@@ -11325,13 +11199,11 @@
         </is>
       </c>
       <c r="O26" s="15">
-        <v>1039449</v>
-      </c>
-      <c r="P26" s="15">
-        <v>-7413</v>
-      </c>
+        <v>1070154</v>
+      </c>
+      <c r="P26" s="15"/>
       <c r="Q26" s="16">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="R26" s="17" t="inlineStr">
         <is>
@@ -11340,7 +11212,7 @@
       </c>
       <c r="S26" s="18" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
       <c r="T26" s="15"/>
@@ -11352,37 +11224,37 @@
         <v>1</v>
       </c>
       <c r="Z26" s="20">
-        <v>106.99</v>
+        <v>49.99</v>
       </c>
       <c r="AA26"/>
       <c r="AB26"/>
       <c r="AC26" s="2"/>
       <c r="AD26" s="19">
-        <v>94</v>
+        <v>2</v>
       </c>
       <c r="AE26" s="15">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AF26" s="21">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="AG26" s="22">
         <v>0</v>
       </c>
       <c r="AH26" s="20">
-        <v>8.68</v>
+        <v>5.56</v>
       </c>
       <c r="AI26" s="16">
-        <v>0.77</v>
+        <v>0.74</v>
       </c>
       <c r="AJ26"/>
       <c r="AK26" s="13" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AL26" s="19">
-        <v>393</v>
+        <v>406</v>
       </c>
       <c r="AM26" s="13" t="inlineStr">
         <is>
@@ -11393,14 +11265,14 @@
       <c r="AO26" s="13"/>
       <c r="AP26"/>
       <c r="AQ26" s="19">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AR26" s="19">
         <v>1</v>
       </c>
       <c r="AS26" s="14" t="inlineStr">
         <is>
-          <t>Teant</t>
+          <t>liwantech</t>
         </is>
       </c>
       <c r="AT26" s="13" t="inlineStr">
@@ -11415,12 +11287,12 @@
       </c>
       <c r="AV26" s="14" t="inlineStr">
         <is>
-          <t>郑州市 河南 450000 CN</t>
+          <t>深圳市 南山区 广东 518000 CN</t>
         </is>
       </c>
       <c r="AW26" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3EVTWEH1TBVG5</t>
+          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1CO438NU9H9Y</t>
         </is>
       </c>
       <c r="AX26" s="13"/>
@@ -11433,7 +11305,11 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="BD26" s="13"/>
+      <c r="BD26" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BE26" s="13"/>
       <c r="BF26" s="13"/>
       <c r="BG26" s="13"/>
@@ -11441,47 +11317,47 @@
       <c r="BI26" s="23"/>
       <c r="BJ26" s="23" t="inlineStr">
         <is>
-          <t>1.9 kg</t>
+          <t>2.24 kg</t>
         </is>
       </c>
       <c r="BK26" s="23" t="inlineStr">
         <is>
-          <t>1.90 kg</t>
+          <t>2.24 kg</t>
         </is>
       </c>
       <c r="BL26" s="23" t="inlineStr">
         <is>
-          <t>38 x 35 x 25 cm</t>
+          <t>29.4 x 2.7 x 18.5 cm</t>
         </is>
       </c>
       <c r="BM26" s="23" t="inlineStr">
         <is>
-          <t>38.00 x 35.00 x 25.00 cm</t>
+          <t>29.40 x 2.70 x 18.50 cm</t>
         </is>
       </c>
       <c r="BN26" s="23" t="inlineStr">
         <is>
-          <t>2.49 kg</t>
+          <t>2.24 kg</t>
         </is>
       </c>
       <c r="BO26" s="23" t="inlineStr">
         <is>
-          <t>2.49 kg</t>
+          <t>2.24 kg</t>
         </is>
       </c>
       <c r="BP26" s="23" t="inlineStr">
         <is>
-          <t>33.5 x 28 x 27 cm</t>
+          <t>34 x 31 x 23 cm</t>
         </is>
       </c>
       <c r="BQ26" s="23" t="inlineStr">
         <is>
-          <t>33.50 x 28.00 x 27.00 cm</t>
+          <t>34.00 x 31.00 x 23.00 cm</t>
         </is>
       </c>
       <c r="BR26" s="13" t="inlineStr">
         <is>
-          <t>轻型标准大件</t>
+          <t>标准包裹</t>
         </is>
       </c>
     </row>
@@ -11492,40 +11368,40 @@
       <c r="B27" s="13"/>
       <c r="C27" s="14" t="inlineStr">
         <is>
-          <t>B0F8W81X7Y</t>
+          <t>B0FKRC3KQY</t>
         </is>
       </c>
       <c r="D27" s="14"/>
       <c r="E27" s="14"/>
       <c r="F27" s="14" t="inlineStr">
         <is>
-          <t>ERINGOGO</t>
+          <t>Yaasier</t>
         </is>
       </c>
       <c r="G27" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=ERINGOGO</t>
+          <t>https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Yaasier</t>
         </is>
       </c>
       <c r="H27" s="14" t="inlineStr">
         <is>
-          <t>ERINGOGO Galleggiante per Lavasciuga Pavimenti Filtro per Serbatoio di Scarico Acciaio Inossidabile Parte Accessori Facile In</t>
+          <t>Yaasier Aspirapolvere per acari con luce UV, mini aspirapolvere con filtro HEPA, Aspirapolvere portatile senza fili con conte</t>
         </is>
       </c>
       <c r="I27" s="14"/>
       <c r="J27" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0F8W81X7Y?psc=1</t>
+          <t>https://www.amazon.it/dp/B0FKRC3KQY?psc=1</t>
         </is>
       </c>
       <c r="K27" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/7132zWnxJ5L._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/511XZVAimmL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L27" s="14" t="inlineStr">
         <is>
-          <t>B0F8W81X7Y</t>
+          <t>B0FKRC3KQY</t>
         </is>
       </c>
       <c r="M27" s="14" t="inlineStr">
@@ -11539,7 +11415,7 @@
         </is>
       </c>
       <c r="O27" s="15">
-        <v>1871734</v>
+        <v>773814</v>
       </c>
       <c r="P27" s="15"/>
       <c r="Q27" s="16">
@@ -11552,7 +11428,7 @@
       </c>
       <c r="S27" s="18" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>25</t>
         </is>
       </c>
       <c r="T27" s="15"/>
@@ -11564,52 +11440,60 @@
         <v>1</v>
       </c>
       <c r="Z27" s="20">
-        <v>19.99</v>
+        <v>22.12</v>
       </c>
       <c r="AA27"/>
       <c r="AB27"/>
       <c r="AC27" s="2"/>
-      <c r="AD27" s="19"/>
-      <c r="AE27" s="15"/>
-      <c r="AF27" s="21"/>
+      <c r="AD27" s="19">
+        <v>15</v>
+      </c>
+      <c r="AE27" s="15">
+        <v>0</v>
+      </c>
+      <c r="AF27" s="21">
+        <v>3.1</v>
+      </c>
       <c r="AG27" s="22">
         <v>0</v>
       </c>
       <c r="AH27" s="20">
-        <v>4.61</v>
+        <v>5.12</v>
       </c>
       <c r="AI27" s="16">
-        <v>0.63</v>
+        <v>0.62</v>
       </c>
       <c r="AJ27"/>
       <c r="AK27" s="13" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-08-31</t>
         </is>
       </c>
       <c r="AL27" s="19">
-        <v>296</v>
+        <v>403</v>
       </c>
       <c r="AM27" s="13" t="inlineStr">
         <is>
-          <t>FBM</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AN27" s="13"/>
       <c r="AO27" s="13"/>
       <c r="AP27"/>
-      <c r="AQ27" s="19"/>
+      <c r="AQ27" s="19">
+        <v>10</v>
+      </c>
       <c r="AR27" s="19">
         <v>1</v>
       </c>
       <c r="AS27" s="14" t="inlineStr">
         <is>
-          <t>idbvd</t>
+          <t>Renyu</t>
         </is>
       </c>
       <c r="AT27" s="13" t="inlineStr">
         <is>
-          <t>FBM</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AU27" s="13" t="inlineStr">
@@ -11619,12 +11503,12 @@
       </c>
       <c r="AV27" s="14" t="inlineStr">
         <is>
-          <t>深圳市 龙岗区 广东 518000 CN</t>
+          <t>dong hu xin ji shu hubei 430223 CN</t>
         </is>
       </c>
       <c r="AW27" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2YR5O9XGNUDX4</t>
+          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=ATK258MBI08TX</t>
         </is>
       </c>
       <c r="AX27" s="13"/>
@@ -11632,7 +11516,11 @@
       <c r="AZ27" s="13"/>
       <c r="BA27" s="13"/>
       <c r="BB27" s="13"/>
-      <c r="BC27" s="13"/>
+      <c r="BC27" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BD27" s="13"/>
       <c r="BE27" s="13"/>
       <c r="BF27" s="13"/>
@@ -11641,42 +11529,42 @@
       <c r="BI27" s="23"/>
       <c r="BJ27" s="23" t="inlineStr">
         <is>
-          <t>100 g</t>
+          <t>400 g</t>
         </is>
       </c>
       <c r="BK27" s="23" t="inlineStr">
         <is>
-          <t>100.00 g</t>
+          <t>400.00 g</t>
         </is>
       </c>
       <c r="BL27" s="23" t="inlineStr">
         <is>
-          <t>13,5 x 6,7 x 6,7 cm</t>
+          <t>4 x 4 x 8 cm</t>
         </is>
       </c>
       <c r="BM27" s="23" t="inlineStr">
         <is>
-          <t>13.50 x 6.70 x 6.70 cm</t>
+          <t>4.00 x 4.00 x 8.00 cm</t>
         </is>
       </c>
       <c r="BN27" s="23" t="inlineStr">
         <is>
-          <t>116 g</t>
+          <t>400 g</t>
         </is>
       </c>
       <c r="BO27" s="23" t="inlineStr">
         <is>
-          <t>116.00 g</t>
+          <t>400.00 g</t>
         </is>
       </c>
       <c r="BP27" s="23" t="inlineStr">
         <is>
-          <t>15 x 9 x 9 cm</t>
+          <t>23.2 x 11.7 x 10.2 cm</t>
         </is>
       </c>
       <c r="BQ27" s="23" t="inlineStr">
         <is>
-          <t>15.00 x 9.00 x 9.00 cm</t>
+          <t>23.20 x 11.70 x 10.20 cm</t>
         </is>
       </c>
       <c r="BR27" s="13" t="inlineStr">
@@ -11692,214 +11580,104 @@
       <c r="B28" s="13"/>
       <c r="C28" s="14" t="inlineStr">
         <is>
-          <t>B0F9NJM4V9</t>
+          <t>B0FMRNV3RZ</t>
         </is>
       </c>
       <c r="D28" s="14"/>
       <c r="E28" s="14"/>
-      <c r="F28" s="14" t="inlineStr">
-        <is>
-          <t>Liwankaqi</t>
-        </is>
-      </c>
+      <c r="F28" s="14"/>
       <c r="G28" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Liwankaqi</t>
+          <t>https://www.amazon.itundefined</t>
         </is>
       </c>
       <c r="H28" s="14" t="inlineStr">
         <is>
-          <t>Liwankaqi Aspiratore acaro per materassi, aspirapolvere acari con UVC e ultrasuoni, aspirazione 8KPa senza fili, anti-allerge</t>
+          <t>Yaasier Aspirapolvere antiacaro per acari, Battimaterasso antiacaro con luce UV e contenitore per polvere permanente HEPA, As</t>
         </is>
       </c>
       <c r="I28" s="14"/>
       <c r="J28" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0F9NJM4V9?psc=1</t>
+          <t>https://www.amazon.it/dp/B0FMRNV3RZ?psc=1</t>
         </is>
       </c>
       <c r="K28" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/61GdOBS8v+L._AC_US600_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/511XZVAimmL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L28" s="14" t="inlineStr">
         <is>
-          <t>B0F9NJM4V9</t>
-        </is>
-      </c>
-      <c r="M28" s="14" t="inlineStr">
-        <is>
-          <t>Casa e cucina:Aspirapolvere e pulizia di pavimenti e finestre:Aspirapolvere:Aspirapolvere per futon</t>
-        </is>
-      </c>
-      <c r="N28" s="14" t="inlineStr">
-        <is>
-          <t>Visualizza i Top 100 nella categoria Casa e c</t>
-        </is>
-      </c>
-      <c r="O28" s="15">
-        <v>1070154</v>
-      </c>
+          <t>B0FMRNV3RZ</t>
+        </is>
+      </c>
+      <c r="M28" s="14"/>
+      <c r="N28" s="14"/>
+      <c r="O28" s="15"/>
       <c r="P28" s="15"/>
-      <c r="Q28" s="16">
-        <v>0</v>
-      </c>
-      <c r="R28" s="17" t="inlineStr">
-        <is>
-          <t>Aspirapolvere per futon</t>
-        </is>
-      </c>
-      <c r="S28" s="18" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
+      <c r="Q28" s="16"/>
+      <c r="R28" s="17"/>
+      <c r="S28" s="18"/>
       <c r="T28" s="15"/>
       <c r="U28" s="16"/>
       <c r="V28" s="15"/>
       <c r="W28" s="15"/>
       <c r="X28" s="15"/>
-      <c r="Y28" s="19">
-        <v>1</v>
-      </c>
-      <c r="Z28" s="20">
-        <v>49.99</v>
-      </c>
+      <c r="Y28" s="19"/>
+      <c r="Z28" s="20"/>
       <c r="AA28"/>
       <c r="AB28"/>
       <c r="AC28" s="2"/>
       <c r="AD28" s="19">
-        <v>2</v>
-      </c>
-      <c r="AE28" s="15">
-        <v>0</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="AE28" s="15"/>
       <c r="AF28" s="21">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="AG28" s="22">
         <v>0</v>
       </c>
-      <c r="AH28" s="20">
-        <v>5.56</v>
-      </c>
+      <c r="AH28" s="20"/>
       <c r="AI28" s="16">
-        <v>0.74</v>
+        <v>0</v>
       </c>
       <c r="AJ28"/>
-      <c r="AK28" s="13" t="inlineStr">
-        <is>
-          <t>2025-08-27</t>
-        </is>
-      </c>
-      <c r="AL28" s="19">
-        <v>406</v>
-      </c>
-      <c r="AM28" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
+      <c r="AK28" s="13"/>
+      <c r="AL28" s="19"/>
+      <c r="AM28" s="13"/>
       <c r="AN28" s="13"/>
       <c r="AO28" s="13"/>
       <c r="AP28"/>
-      <c r="AQ28" s="19">
-        <v>8</v>
-      </c>
-      <c r="AR28" s="19">
-        <v>1</v>
-      </c>
-      <c r="AS28" s="14" t="inlineStr">
-        <is>
-          <t>liwantech</t>
-        </is>
-      </c>
-      <c r="AT28" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AU28" s="13" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="AV28" s="14" t="inlineStr">
-        <is>
-          <t>深圳市 南山区 广东 518000 CN</t>
-        </is>
-      </c>
-      <c r="AW28" s="13" t="inlineStr">
-        <is>
-          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1CO438NU9H9Y</t>
-        </is>
-      </c>
+      <c r="AQ28" s="19"/>
+      <c r="AR28" s="19"/>
+      <c r="AS28" s="14"/>
+      <c r="AT28" s="13"/>
+      <c r="AU28" s="13"/>
+      <c r="AV28" s="14"/>
+      <c r="AW28" s="13"/>
       <c r="AX28" s="13"/>
       <c r="AY28" s="13"/>
       <c r="AZ28" s="13"/>
       <c r="BA28" s="13"/>
       <c r="BB28" s="13"/>
-      <c r="BC28" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BD28" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BC28" s="13"/>
+      <c r="BD28" s="13"/>
       <c r="BE28" s="13"/>
       <c r="BF28" s="13"/>
       <c r="BG28" s="13"/>
       <c r="BH28" s="14"/>
       <c r="BI28" s="23"/>
-      <c r="BJ28" s="23" t="inlineStr">
-        <is>
-          <t>2.24 kg</t>
-        </is>
-      </c>
-      <c r="BK28" s="23" t="inlineStr">
-        <is>
-          <t>2.24 kg</t>
-        </is>
-      </c>
-      <c r="BL28" s="23" t="inlineStr">
-        <is>
-          <t>29.4 x 2.7 x 18.5 cm</t>
-        </is>
-      </c>
-      <c r="BM28" s="23" t="inlineStr">
-        <is>
-          <t>29.40 x 2.70 x 18.50 cm</t>
-        </is>
-      </c>
-      <c r="BN28" s="23" t="inlineStr">
-        <is>
-          <t>2.24 kg</t>
-        </is>
-      </c>
-      <c r="BO28" s="23" t="inlineStr">
-        <is>
-          <t>2.24 kg</t>
-        </is>
-      </c>
-      <c r="BP28" s="23" t="inlineStr">
-        <is>
-          <t>34 x 31 x 23 cm</t>
-        </is>
-      </c>
-      <c r="BQ28" s="23" t="inlineStr">
-        <is>
-          <t>34.00 x 31.00 x 23.00 cm</t>
-        </is>
-      </c>
-      <c r="BR28" s="13" t="inlineStr">
-        <is>
-          <t>标准包裹</t>
-        </is>
-      </c>
+      <c r="BJ28" s="23"/>
+      <c r="BK28" s="23"/>
+      <c r="BL28" s="23"/>
+      <c r="BM28" s="23"/>
+      <c r="BN28" s="23"/>
+      <c r="BO28" s="23"/>
+      <c r="BP28" s="23"/>
+      <c r="BQ28" s="23"/>
+      <c r="BR28" s="13"/>
     </row>
     <row r="29" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="13">
@@ -11908,40 +11686,40 @@
       <c r="B29" s="13"/>
       <c r="C29" s="14" t="inlineStr">
         <is>
-          <t>B0FKRC3KQY</t>
+          <t>B0FN3GPQZM</t>
         </is>
       </c>
       <c r="D29" s="14"/>
       <c r="E29" s="14"/>
       <c r="F29" s="14" t="inlineStr">
         <is>
-          <t>Yaasier</t>
+          <t>Teant</t>
         </is>
       </c>
       <c r="G29" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Yaasier</t>
+          <t>https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Teant</t>
         </is>
       </c>
       <c r="H29" s="14" t="inlineStr">
         <is>
-          <t>Yaasier Aspirapolvere per acari con luce UV, mini aspirapolvere con filtro HEPA, Aspirapolvere portatile senza fili con conte</t>
+          <t>Teant Aspirapolvere per Materassi, 2 Velocità (14 kPa/18 kPa) – con Rilevamento Polvere a Luce Verde, Luce UV-C 253.7 nm, Dis</t>
         </is>
       </c>
       <c r="I29" s="14"/>
       <c r="J29" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0FKRC3KQY?psc=1</t>
+          <t>https://www.amazon.it/dp/B0FN3GPQZM?psc=1</t>
         </is>
       </c>
       <c r="K29" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/511XZVAimmL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71gt+j80L3L._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L29" s="14" t="inlineStr">
         <is>
-          <t>B0FKRC3KQY</t>
+          <t>B0FN3GPQZM</t>
         </is>
       </c>
       <c r="M29" s="14" t="inlineStr">
@@ -11955,11 +11733,13 @@
         </is>
       </c>
       <c r="O29" s="15">
-        <v>773814</v>
-      </c>
-      <c r="P29" s="15"/>
+        <v>962620</v>
+      </c>
+      <c r="P29" s="15">
+        <v>-10023</v>
+      </c>
       <c r="Q29" s="16">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="R29" s="17" t="inlineStr">
         <is>
@@ -11968,7 +11748,7 @@
       </c>
       <c r="S29" s="18" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>27</t>
         </is>
       </c>
       <c r="T29" s="15"/>
@@ -11980,37 +11760,37 @@
         <v>1</v>
       </c>
       <c r="Z29" s="20">
-        <v>22.12</v>
+        <v>131.98</v>
       </c>
       <c r="AA29"/>
       <c r="AB29"/>
       <c r="AC29" s="2"/>
       <c r="AD29" s="19">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="AE29" s="15">
         <v>0</v>
       </c>
       <c r="AF29" s="21">
-        <v>3.1</v>
+        <v>4.6</v>
       </c>
       <c r="AG29" s="22">
         <v>0</v>
       </c>
       <c r="AH29" s="20">
-        <v>5.12</v>
+        <v>8.68</v>
       </c>
       <c r="AI29" s="16">
-        <v>0.62</v>
+        <v>0.78</v>
       </c>
       <c r="AJ29"/>
       <c r="AK29" s="13" t="inlineStr">
         <is>
-          <t>2025-08-31</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="AL29" s="19">
-        <v>403</v>
+        <v>309</v>
       </c>
       <c r="AM29" s="13" t="inlineStr">
         <is>
@@ -12028,7 +11808,7 @@
       </c>
       <c r="AS29" s="14" t="inlineStr">
         <is>
-          <t>Renyu</t>
+          <t>Teant</t>
         </is>
       </c>
       <c r="AT29" s="13" t="inlineStr">
@@ -12043,12 +11823,12 @@
       </c>
       <c r="AV29" s="14" t="inlineStr">
         <is>
-          <t>dong hu xin ji shu hubei 430223 CN</t>
+          <t>郑州市 河南 450000 CN</t>
         </is>
       </c>
       <c r="AW29" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=ATK258MBI08TX</t>
+          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3EVTWEH1TBVG5</t>
         </is>
       </c>
       <c r="AX29" s="13"/>
@@ -12069,47 +11849,47 @@
       <c r="BI29" s="23"/>
       <c r="BJ29" s="23" t="inlineStr">
         <is>
-          <t>400 g</t>
+          <t>1.9 kg</t>
         </is>
       </c>
       <c r="BK29" s="23" t="inlineStr">
         <is>
-          <t>400.00 g</t>
+          <t>1.90 kg</t>
         </is>
       </c>
       <c r="BL29" s="23" t="inlineStr">
         <is>
-          <t>4 x 4 x 8 cm</t>
+          <t>36 x 29 x 25 cm</t>
         </is>
       </c>
       <c r="BM29" s="23" t="inlineStr">
         <is>
-          <t>4.00 x 4.00 x 8.00 cm</t>
+          <t>36.00 x 29.00 x 25.00 cm</t>
         </is>
       </c>
       <c r="BN29" s="23" t="inlineStr">
         <is>
-          <t>400 g</t>
+          <t>2.58 kg</t>
         </is>
       </c>
       <c r="BO29" s="23" t="inlineStr">
         <is>
-          <t>400.00 g</t>
+          <t>2.58 kg</t>
         </is>
       </c>
       <c r="BP29" s="23" t="inlineStr">
         <is>
-          <t>23.2 x 11.7 x 10.2 cm</t>
+          <t>33.1 x 30.9 x 27.4 cm</t>
         </is>
       </c>
       <c r="BQ29" s="23" t="inlineStr">
         <is>
-          <t>23.20 x 11.70 x 10.20 cm</t>
+          <t>33.10 x 30.90 x 27.40 cm</t>
         </is>
       </c>
       <c r="BR29" s="13" t="inlineStr">
         <is>
-          <t>小包裹</t>
+          <t>轻型标准大件</t>
         </is>
       </c>
     </row>
@@ -12120,83 +11900,145 @@
       <c r="B30" s="13"/>
       <c r="C30" s="14" t="inlineStr">
         <is>
-          <t>B0FMRNV3RZ</t>
+          <t>B0FP52HNHM</t>
         </is>
       </c>
       <c r="D30" s="14"/>
       <c r="E30" s="14"/>
-      <c r="F30" s="14"/>
+      <c r="F30" s="14" t="inlineStr">
+        <is>
+          <t>PattenlLevi</t>
+        </is>
+      </c>
       <c r="G30" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.itundefined</t>
+          <t>https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=PattenlLevi</t>
         </is>
       </c>
       <c r="H30" s="14" t="inlineStr">
         <is>
-          <t>Yaasier Aspirapolvere antiacaro per acari, Battimaterasso antiacaro con luce UV e contenitore per polvere permanente HEPA, As</t>
+          <t>PattenlLevi Aspiratore per materassi da 3 a 3,5 W, 3 modalità di pulizia Robot sterilizzazione automatico con luce UV per let</t>
         </is>
       </c>
       <c r="I30" s="14"/>
       <c r="J30" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0FMRNV3RZ?psc=1</t>
+          <t>https://www.amazon.it/dp/B0FP52HNHM?psc=1</t>
         </is>
       </c>
       <c r="K30" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/511XZVAimmL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/41qFOExg5PL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L30" s="14" t="inlineStr">
         <is>
-          <t>B0FMRNV3RZ</t>
-        </is>
-      </c>
-      <c r="M30" s="14"/>
-      <c r="N30" s="14"/>
-      <c r="O30" s="15"/>
+          <t>B0FP52HNHM</t>
+        </is>
+      </c>
+      <c r="M30" s="14" t="inlineStr">
+        <is>
+          <t>Casa e cucina:Aspirapolvere e pulizia di pavimenti e finestre:Aspirapolvere:Aspirapolvere per futon</t>
+        </is>
+      </c>
+      <c r="N30" s="14" t="inlineStr">
+        <is>
+          <t>Visualizza i Top 100 nella categoria Casa e c</t>
+        </is>
+      </c>
+      <c r="O30" s="15">
+        <v>1708056</v>
+      </c>
       <c r="P30" s="15"/>
-      <c r="Q30" s="16"/>
-      <c r="R30" s="17"/>
-      <c r="S30" s="18"/>
+      <c r="Q30" s="16">
+        <v>0</v>
+      </c>
+      <c r="R30" s="17" t="inlineStr">
+        <is>
+          <t>Aspirapolvere per futon</t>
+        </is>
+      </c>
+      <c r="S30" s="18" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
       <c r="T30" s="15"/>
       <c r="U30" s="16"/>
       <c r="V30" s="15"/>
       <c r="W30" s="15"/>
       <c r="X30" s="15"/>
-      <c r="Y30" s="19"/>
-      <c r="Z30" s="20"/>
+      <c r="Y30" s="19">
+        <v>1</v>
+      </c>
+      <c r="Z30" s="20">
+        <v>83</v>
+      </c>
       <c r="AA30"/>
       <c r="AB30"/>
       <c r="AC30" s="2"/>
       <c r="AD30" s="19">
-        <v>13</v>
-      </c>
-      <c r="AE30" s="15"/>
+        <v>1</v>
+      </c>
+      <c r="AE30" s="15">
+        <v>0</v>
+      </c>
       <c r="AF30" s="21">
-        <v>3.1</v>
+        <v>5</v>
       </c>
       <c r="AG30" s="22">
         <v>0</v>
       </c>
       <c r="AH30" s="20"/>
       <c r="AI30" s="16">
-        <v>0</v>
+        <v>0.85</v>
       </c>
       <c r="AJ30"/>
-      <c r="AK30" s="13"/>
-      <c r="AL30" s="19"/>
-      <c r="AM30" s="13"/>
+      <c r="AK30" s="13" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AL30" s="19">
+        <v>382</v>
+      </c>
+      <c r="AM30" s="13" t="inlineStr">
+        <is>
+          <t>FBM</t>
+        </is>
+      </c>
       <c r="AN30" s="13"/>
       <c r="AO30" s="13"/>
       <c r="AP30"/>
       <c r="AQ30" s="19"/>
-      <c r="AR30" s="19"/>
-      <c r="AS30" s="14"/>
-      <c r="AT30" s="13"/>
-      <c r="AU30" s="13"/>
-      <c r="AV30" s="14"/>
-      <c r="AW30" s="13"/>
+      <c r="AR30" s="19">
+        <v>1</v>
+      </c>
+      <c r="AS30" s="14" t="inlineStr">
+        <is>
+          <t>lnBtkuuco</t>
+        </is>
+      </c>
+      <c r="AT30" s="13" t="inlineStr">
+        <is>
+          <t>FBM</t>
+        </is>
+      </c>
+      <c r="AU30" s="13" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="AV30" s="14" t="inlineStr">
+        <is>
+          <t>昆明市 云南省 650000 CN</t>
+        </is>
+      </c>
+      <c r="AW30" s="13" t="inlineStr">
+        <is>
+          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A28PZKXD42YVSB</t>
+        </is>
+      </c>
       <c r="AX30" s="13"/>
       <c r="AY30" s="13"/>
       <c r="AZ30" s="13"/>
@@ -12211,7 +12053,11 @@
       <c r="BI30" s="23"/>
       <c r="BJ30" s="23"/>
       <c r="BK30" s="23"/>
-      <c r="BL30" s="23"/>
+      <c r="BL30" s="23" t="inlineStr">
+        <is>
+          <t>16L x 16l x 5H cm</t>
+        </is>
+      </c>
       <c r="BM30" s="23"/>
       <c r="BN30" s="23"/>
       <c r="BO30" s="23"/>
@@ -12226,40 +12072,40 @@
       <c r="B31" s="13"/>
       <c r="C31" s="14" t="inlineStr">
         <is>
-          <t>B0FN3GPQZM</t>
+          <t>B0FP9CGZYN</t>
         </is>
       </c>
       <c r="D31" s="14"/>
       <c r="E31" s="14"/>
       <c r="F31" s="14" t="inlineStr">
         <is>
-          <t>Teant</t>
+          <t>Yaasier</t>
         </is>
       </c>
       <c r="G31" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Teant</t>
+          <t>https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Yaasier</t>
         </is>
       </c>
       <c r="H31" s="14" t="inlineStr">
         <is>
-          <t>Teant Aspirapolvere per Materassi, 2 Velocità (14 kPa/18 kPa) – con Rilevamento Polvere a Luce Verde, Luce UV-C 253.7 nm, Dis</t>
+          <t>Yaasier Aspirapolvere per materassi,16kpa Battimaterasso Antiacaro con luce UV-C a 253,7nm, Rimuove il 99,9%, Riscaldamento R</t>
         </is>
       </c>
       <c r="I31" s="14"/>
       <c r="J31" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0FN3GPQZM?psc=1</t>
+          <t>https://www.amazon.it/dp/B0FP9CGZYN?psc=1</t>
         </is>
       </c>
       <c r="K31" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71gt+j80L3L._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/61mGX4QmLkL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L31" s="14" t="inlineStr">
         <is>
-          <t>B0FN3GPQZM</t>
+          <t>B0FP9CGZYN</t>
         </is>
       </c>
       <c r="M31" s="14" t="inlineStr">
@@ -12273,13 +12119,13 @@
         </is>
       </c>
       <c r="O31" s="15">
-        <v>962620</v>
+        <v>751540</v>
       </c>
       <c r="P31" s="15">
-        <v>-10023</v>
+        <v>-16970</v>
       </c>
       <c r="Q31" s="16">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="R31" s="17" t="inlineStr">
         <is>
@@ -12288,7 +12134,7 @@
       </c>
       <c r="S31" s="18" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>24</t>
         </is>
       </c>
       <c r="T31" s="15"/>
@@ -12300,25 +12146,25 @@
         <v>1</v>
       </c>
       <c r="Z31" s="20">
-        <v>131.98</v>
+        <v>78.99</v>
       </c>
       <c r="AA31"/>
       <c r="AB31"/>
       <c r="AC31" s="2"/>
       <c r="AD31" s="19">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="AE31" s="15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF31" s="21">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="AG31" s="22">
         <v>0</v>
       </c>
       <c r="AH31" s="20">
-        <v>8.68</v>
+        <v>5.56</v>
       </c>
       <c r="AI31" s="16">
         <v>0.78</v>
@@ -12326,11 +12172,11 @@
       <c r="AJ31"/>
       <c r="AK31" s="13" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-10-12</t>
         </is>
       </c>
       <c r="AL31" s="19">
-        <v>309</v>
+        <v>360</v>
       </c>
       <c r="AM31" s="13" t="inlineStr">
         <is>
@@ -12341,14 +12187,14 @@
       <c r="AO31" s="13"/>
       <c r="AP31"/>
       <c r="AQ31" s="19">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AR31" s="19">
         <v>1</v>
       </c>
       <c r="AS31" s="14" t="inlineStr">
         <is>
-          <t>Teant</t>
+          <t>Renyu</t>
         </is>
       </c>
       <c r="AT31" s="13" t="inlineStr">
@@ -12363,12 +12209,12 @@
       </c>
       <c r="AV31" s="14" t="inlineStr">
         <is>
-          <t>郑州市 河南 450000 CN</t>
+          <t>dong hu xin ji shu hubei 430223 CN</t>
         </is>
       </c>
       <c r="AW31" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3EVTWEH1TBVG5</t>
+          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=ATK258MBI08TX</t>
         </is>
       </c>
       <c r="AX31" s="13"/>
@@ -12381,7 +12227,11 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="BD31" s="13"/>
+      <c r="BD31" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BE31" s="13"/>
       <c r="BF31" s="13"/>
       <c r="BG31" s="13"/>
@@ -12389,47 +12239,47 @@
       <c r="BI31" s="23"/>
       <c r="BJ31" s="23" t="inlineStr">
         <is>
-          <t>1.9 kg</t>
+          <t>250 g</t>
         </is>
       </c>
       <c r="BK31" s="23" t="inlineStr">
         <is>
-          <t>1.90 kg</t>
+          <t>250.00 g</t>
         </is>
       </c>
       <c r="BL31" s="23" t="inlineStr">
         <is>
-          <t>36 x 29 x 25 cm</t>
+          <t>4 x 4 x 8 cm</t>
         </is>
       </c>
       <c r="BM31" s="23" t="inlineStr">
         <is>
-          <t>36.00 x 29.00 x 25.00 cm</t>
+          <t>4.00 x 4.00 x 8.00 cm</t>
         </is>
       </c>
       <c r="BN31" s="23" t="inlineStr">
         <is>
-          <t>2.58 kg</t>
+          <t>2 kg</t>
         </is>
       </c>
       <c r="BO31" s="23" t="inlineStr">
         <is>
-          <t>2.58 kg</t>
+          <t>2.00 kg</t>
         </is>
       </c>
       <c r="BP31" s="23" t="inlineStr">
         <is>
-          <t>33.1 x 30.9 x 27.4 cm</t>
+          <t>32.1 x 30 x 22 cm</t>
         </is>
       </c>
       <c r="BQ31" s="23" t="inlineStr">
         <is>
-          <t>33.10 x 30.90 x 27.40 cm</t>
+          <t>32.10 x 30.00 x 22.00 cm</t>
         </is>
       </c>
       <c r="BR31" s="13" t="inlineStr">
         <is>
-          <t>轻型标准大件</t>
+          <t>标准包裹</t>
         </is>
       </c>
     </row>
@@ -12440,40 +12290,40 @@
       <c r="B32" s="13"/>
       <c r="C32" s="14" t="inlineStr">
         <is>
-          <t>B0FP52HNHM</t>
+          <t>B0FRBB876G</t>
         </is>
       </c>
       <c r="D32" s="14"/>
       <c r="E32" s="14"/>
       <c r="F32" s="14" t="inlineStr">
         <is>
-          <t>PattenlLevi</t>
+          <t>MITE GUARD</t>
         </is>
       </c>
       <c r="G32" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=PattenlLevi</t>
+          <t>https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=MITE+GUARD</t>
         </is>
       </c>
       <c r="H32" s="14" t="inlineStr">
         <is>
-          <t>PattenlLevi Aspiratore per materassi da 3 a 3,5 W, 3 modalità di pulizia Robot sterilizzazione automatico con luce UV per let</t>
+          <t>Miteguard Aspiratore per materassi e imbottiture con 2 spazzole speciali – Luce UV, dispositivo ad ultrasuoni &amp; aria calda a</t>
         </is>
       </c>
       <c r="I32" s="14"/>
       <c r="J32" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0FP52HNHM?psc=1</t>
+          <t>https://www.amazon.it/dp/B0FRBB876G?psc=1</t>
         </is>
       </c>
       <c r="K32" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/41qFOExg5PL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71yKveOz1uL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L32" s="14" t="inlineStr">
         <is>
-          <t>B0FP52HNHM</t>
+          <t>B0FRBB876G</t>
         </is>
       </c>
       <c r="M32" s="14" t="inlineStr">
@@ -12487,11 +12337,13 @@
         </is>
       </c>
       <c r="O32" s="15">
-        <v>1708056</v>
-      </c>
-      <c r="P32" s="15"/>
+        <v>1628350</v>
+      </c>
+      <c r="P32" s="15">
+        <v>-381195</v>
+      </c>
       <c r="Q32" s="16">
-        <v>0</v>
+        <v>-0.31</v>
       </c>
       <c r="R32" s="17" t="inlineStr">
         <is>
@@ -12500,7 +12352,7 @@
       </c>
       <c r="S32" s="18" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>33</t>
         </is>
       </c>
       <c r="T32" s="15"/>
@@ -12512,73 +12364,65 @@
         <v>1</v>
       </c>
       <c r="Z32" s="20">
-        <v>83</v>
+        <v>172.51</v>
       </c>
       <c r="AA32"/>
       <c r="AB32"/>
       <c r="AC32" s="2"/>
       <c r="AD32" s="19">
-        <v>1</v>
+        <v>79</v>
       </c>
       <c r="AE32" s="15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF32" s="21">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="AG32" s="22">
         <v>0</v>
       </c>
-      <c r="AH32" s="20"/>
+      <c r="AH32" s="20">
+        <v>5.21</v>
+      </c>
       <c r="AI32" s="16">
-        <v>0.85</v>
+        <v>0.82</v>
       </c>
       <c r="AJ32"/>
       <c r="AK32" s="13" t="inlineStr">
         <is>
-          <t>2025-09-20</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AL32" s="19">
-        <v>382</v>
+        <v>286</v>
       </c>
       <c r="AM32" s="13" t="inlineStr">
         <is>
-          <t>FBM</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AN32" s="13"/>
       <c r="AO32" s="13"/>
       <c r="AP32"/>
-      <c r="AQ32" s="19"/>
+      <c r="AQ32" s="19">
+        <v>9</v>
+      </c>
       <c r="AR32" s="19">
         <v>1</v>
       </c>
       <c r="AS32" s="14" t="inlineStr">
         <is>
-          <t>lnBtkuuco</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="AT32" s="13" t="inlineStr">
         <is>
-          <t>FBM</t>
-        </is>
-      </c>
-      <c r="AU32" s="13" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="AV32" s="14" t="inlineStr">
-        <is>
-          <t>昆明市 云南省 650000 CN</t>
-        </is>
-      </c>
-      <c r="AW32" s="13" t="inlineStr">
-        <is>
-          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A28PZKXD42YVSB</t>
-        </is>
-      </c>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AU32" s="13"/>
+      <c r="AV32" s="14"/>
+      <c r="AW32" s="13"/>
       <c r="AX32" s="13"/>
       <c r="AY32" s="13"/>
       <c r="AZ32" s="13"/>
@@ -12591,19 +12435,47 @@
       <c r="BG32" s="13"/>
       <c r="BH32" s="14"/>
       <c r="BI32" s="23"/>
-      <c r="BJ32" s="23"/>
-      <c r="BK32" s="23"/>
+      <c r="BJ32" s="23" t="inlineStr">
+        <is>
+          <t>2.2 kg</t>
+        </is>
+      </c>
+      <c r="BK32" s="23" t="inlineStr">
+        <is>
+          <t>2.20 kg</t>
+        </is>
+      </c>
       <c r="BL32" s="23" t="inlineStr">
         <is>
-          <t>16L x 16l x 5H cm</t>
+          <t>28L x 22l x 25H cm</t>
         </is>
       </c>
       <c r="BM32" s="23"/>
-      <c r="BN32" s="23"/>
-      <c r="BO32" s="23"/>
-      <c r="BP32" s="23"/>
-      <c r="BQ32" s="23"/>
-      <c r="BR32" s="13"/>
+      <c r="BN32" s="23" t="inlineStr">
+        <is>
+          <t>3.11 kg</t>
+        </is>
+      </c>
+      <c r="BO32" s="23" t="inlineStr">
+        <is>
+          <t>3.11 kg</t>
+        </is>
+      </c>
+      <c r="BP32" s="23" t="inlineStr">
+        <is>
+          <t>33.2 x 30.3 x 25.4 cm</t>
+        </is>
+      </c>
+      <c r="BQ32" s="23" t="inlineStr">
+        <is>
+          <t>33.20 x 30.30 x 25.40 cm</t>
+        </is>
+      </c>
+      <c r="BR32" s="13" t="inlineStr">
+        <is>
+          <t>标准包裹</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="13">
@@ -12612,40 +12484,40 @@
       <c r="B33" s="13"/>
       <c r="C33" s="14" t="inlineStr">
         <is>
-          <t>B0FP9CGZYN</t>
+          <t>B0FW3MWVJR</t>
         </is>
       </c>
       <c r="D33" s="14"/>
       <c r="E33" s="14"/>
       <c r="F33" s="14" t="inlineStr">
         <is>
-          <t>Yaasier</t>
+          <t>JIGOO</t>
         </is>
       </c>
       <c r="G33" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Yaasier</t>
+          <t>https://www.amazon.it/stores/JIGOO-IT/page/7F1C5254-18CC-4331-A449-F5F68B2E288D?lp_asin=B0FW3MWVJR&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H33" s="14" t="inlineStr">
         <is>
-          <t>Yaasier Aspirapolvere per materassi,16kpa Battimaterasso Antiacaro con luce UV-C a 253,7nm, Rimuove il 99,9%, Riscaldamento R</t>
+          <t>JIGOO Battimaterasso, Aspiratore per acari Soluzione economica, completamente funzionale, con tutti gli accessori. Soddisfa o</t>
         </is>
       </c>
       <c r="I33" s="14"/>
       <c r="J33" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0FP9CGZYN?psc=1</t>
+          <t>https://www.amazon.it/dp/B0FW3MWVJR?psc=1</t>
         </is>
       </c>
       <c r="K33" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/61mGX4QmLkL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/61R1ViIQaTL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L33" s="14" t="inlineStr">
         <is>
-          <t>B0FP9CGZYN</t>
+          <t>B0FW3MWVJR</t>
         </is>
       </c>
       <c r="M33" s="14" t="inlineStr">
@@ -12659,13 +12531,11 @@
         </is>
       </c>
       <c r="O33" s="15">
-        <v>751540</v>
-      </c>
-      <c r="P33" s="15">
-        <v>-16970</v>
-      </c>
+        <v>571192</v>
+      </c>
+      <c r="P33" s="15"/>
       <c r="Q33" s="16">
-        <v>-0.02</v>
+        <v>0</v>
       </c>
       <c r="R33" s="17" t="inlineStr">
         <is>
@@ -12674,7 +12544,7 @@
       </c>
       <c r="S33" s="18" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>19</t>
         </is>
       </c>
       <c r="T33" s="15"/>
@@ -12686,37 +12556,37 @@
         <v>1</v>
       </c>
       <c r="Z33" s="20">
-        <v>78.99</v>
+        <v>65.99</v>
       </c>
       <c r="AA33"/>
       <c r="AB33"/>
       <c r="AC33" s="2"/>
       <c r="AD33" s="19">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="AE33" s="15">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF33" s="21">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG33" s="22">
         <v>0</v>
       </c>
       <c r="AH33" s="20">
-        <v>5.56</v>
+        <v>5.3</v>
       </c>
       <c r="AI33" s="16">
-        <v>0.78</v>
+        <v>0.77</v>
       </c>
       <c r="AJ33"/>
       <c r="AK33" s="13" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="AL33" s="19">
-        <v>360</v>
+        <v>327</v>
       </c>
       <c r="AM33" s="13" t="inlineStr">
         <is>
@@ -12734,7 +12604,7 @@
       </c>
       <c r="AS33" s="14" t="inlineStr">
         <is>
-          <t>Renyu</t>
+          <t>ANISE EDALS52</t>
         </is>
       </c>
       <c r="AT33" s="13" t="inlineStr">
@@ -12744,17 +12614,17 @@
       </c>
       <c r="AU33" s="13" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="AV33" s="14" t="inlineStr">
         <is>
-          <t>dong hu xin ji shu hubei 430223 CN</t>
+          <t>LONDONDERRY NORTHERN IRELAND BT48 7DE GB</t>
         </is>
       </c>
       <c r="AW33" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=ATK258MBI08TX</t>
+          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A99P1VJD8HKQ6</t>
         </is>
       </c>
       <c r="AX33" s="13"/>
@@ -12762,16 +12632,8 @@
       <c r="AZ33" s="13"/>
       <c r="BA33" s="13"/>
       <c r="BB33" s="13"/>
-      <c r="BC33" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BD33" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BC33" s="13"/>
+      <c r="BD33" s="13"/>
       <c r="BE33" s="13"/>
       <c r="BF33" s="13"/>
       <c r="BG33" s="13"/>
@@ -12779,49 +12641,25 @@
       <c r="BI33" s="23"/>
       <c r="BJ33" s="23" t="inlineStr">
         <is>
-          <t>250 g</t>
+          <t>2,72 kg</t>
         </is>
       </c>
       <c r="BK33" s="23" t="inlineStr">
         <is>
-          <t>250.00 g</t>
+          <t>2.72 kg</t>
         </is>
       </c>
       <c r="BL33" s="23" t="inlineStr">
         <is>
-          <t>4 x 4 x 8 cm</t>
-        </is>
-      </c>
-      <c r="BM33" s="23" t="inlineStr">
-        <is>
-          <t>4.00 x 4.00 x 8.00 cm</t>
-        </is>
-      </c>
-      <c r="BN33" s="23" t="inlineStr">
-        <is>
-          <t>2 kg</t>
-        </is>
-      </c>
-      <c r="BO33" s="23" t="inlineStr">
-        <is>
-          <t>2.00 kg</t>
-        </is>
-      </c>
-      <c r="BP33" s="23" t="inlineStr">
-        <is>
-          <t>32.1 x 30 x 22 cm</t>
-        </is>
-      </c>
-      <c r="BQ33" s="23" t="inlineStr">
-        <is>
-          <t>32.10 x 30.00 x 22.00 cm</t>
-        </is>
-      </c>
-      <c r="BR33" s="13" t="inlineStr">
-        <is>
-          <t>标准包裹</t>
-        </is>
-      </c>
+          <t>27,2L x 18,8l x 32,9H cm</t>
+        </is>
+      </c>
+      <c r="BM33" s="23"/>
+      <c r="BN33" s="23"/>
+      <c r="BO33" s="23"/>
+      <c r="BP33" s="23"/>
+      <c r="BQ33" s="23"/>
+      <c r="BR33" s="13"/>
     </row>
     <row r="34" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="13">
@@ -12830,40 +12668,40 @@
       <c r="B34" s="13"/>
       <c r="C34" s="14" t="inlineStr">
         <is>
-          <t>B0FRBB876G</t>
+          <t>B0FYM1D13D</t>
         </is>
       </c>
       <c r="D34" s="14"/>
       <c r="E34" s="14"/>
       <c r="F34" s="14" t="inlineStr">
         <is>
-          <t>MITE GUARD</t>
+          <t>Yaasier</t>
         </is>
       </c>
       <c r="G34" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=MITE+GUARD</t>
+          <t>https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Yaasier</t>
         </is>
       </c>
       <c r="H34" s="14" t="inlineStr">
         <is>
-          <t>Miteguard Aspiratore per materassi e imbottiture con 2 spazzole speciali – Luce UV, dispositivo ad ultrasuoni &amp; aria calda a</t>
+          <t>Aspirapolvere antiacaro per acari, Battimaterasso antiacaro con luce UV e contenitore per polvere permanente HEPA, Aspiratore</t>
         </is>
       </c>
       <c r="I34" s="14"/>
       <c r="J34" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0FRBB876G?psc=1</t>
+          <t>https://www.amazon.it/dp/B0FYM1D13D?psc=1</t>
         </is>
       </c>
       <c r="K34" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71yKveOz1uL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/51dJLeDXofL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L34" s="14" t="inlineStr">
         <is>
-          <t>B0FRBB876G</t>
+          <t>B0FYM1D13D</t>
         </is>
       </c>
       <c r="M34" s="14" t="inlineStr">
@@ -12877,13 +12715,11 @@
         </is>
       </c>
       <c r="O34" s="15">
-        <v>1628350</v>
-      </c>
-      <c r="P34" s="15">
-        <v>-381195</v>
-      </c>
+        <v>1226735</v>
+      </c>
+      <c r="P34" s="15"/>
       <c r="Q34" s="16">
-        <v>-0.31</v>
+        <v>0</v>
       </c>
       <c r="R34" s="17" t="inlineStr">
         <is>
@@ -12892,7 +12728,7 @@
       </c>
       <c r="S34" s="18" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>30</t>
         </is>
       </c>
       <c r="T34" s="15"/>
@@ -12904,37 +12740,37 @@
         <v>1</v>
       </c>
       <c r="Z34" s="20">
-        <v>172.51</v>
+        <v>27.99</v>
       </c>
       <c r="AA34"/>
       <c r="AB34"/>
       <c r="AC34" s="2"/>
       <c r="AD34" s="19">
-        <v>79</v>
+        <v>4</v>
       </c>
       <c r="AE34" s="15">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF34" s="21">
-        <v>4.6</v>
+        <v>3</v>
       </c>
       <c r="AG34" s="22">
         <v>0</v>
       </c>
       <c r="AH34" s="20">
-        <v>5.21</v>
+        <v>5.12</v>
       </c>
       <c r="AI34" s="16">
-        <v>0.82</v>
+        <v>0.67</v>
       </c>
       <c r="AJ34"/>
       <c r="AK34" s="13" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="AL34" s="19">
-        <v>286</v>
+        <v>317</v>
       </c>
       <c r="AM34" s="13" t="inlineStr">
         <is>
@@ -12952,7 +12788,7 @@
       </c>
       <c r="AS34" s="14" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Renyu</t>
         </is>
       </c>
       <c r="AT34" s="13" t="inlineStr">
@@ -12960,16 +12796,36 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="AU34" s="13"/>
-      <c r="AV34" s="14"/>
-      <c r="AW34" s="13"/>
+      <c r="AU34" s="13" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="AV34" s="14" t="inlineStr">
+        <is>
+          <t>dong hu xin ji shu hubei 430223 CN</t>
+        </is>
+      </c>
+      <c r="AW34" s="13" t="inlineStr">
+        <is>
+          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=ATK258MBI08TX</t>
+        </is>
+      </c>
       <c r="AX34" s="13"/>
       <c r="AY34" s="13"/>
       <c r="AZ34" s="13"/>
       <c r="BA34" s="13"/>
       <c r="BB34" s="13"/>
-      <c r="BC34" s="13"/>
-      <c r="BD34" s="13"/>
+      <c r="BC34" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="BD34" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BE34" s="13"/>
       <c r="BF34" s="13"/>
       <c r="BG34" s="13"/>
@@ -12977,43 +12833,43 @@
       <c r="BI34" s="23"/>
       <c r="BJ34" s="23" t="inlineStr">
         <is>
-          <t>2.2 kg</t>
+          <t>400 g</t>
         </is>
       </c>
       <c r="BK34" s="23" t="inlineStr">
         <is>
-          <t>2.20 kg</t>
+          <t>400.00 g</t>
         </is>
       </c>
       <c r="BL34" s="23" t="inlineStr">
         <is>
-          <t>28L x 22l x 25H cm</t>
+          <t>6L x 4l x 8H cm</t>
         </is>
       </c>
       <c r="BM34" s="23"/>
       <c r="BN34" s="23" t="inlineStr">
         <is>
-          <t>3.11 kg</t>
+          <t>400 g</t>
         </is>
       </c>
       <c r="BO34" s="23" t="inlineStr">
         <is>
-          <t>3.11 kg</t>
+          <t>400.00 g</t>
         </is>
       </c>
       <c r="BP34" s="23" t="inlineStr">
         <is>
-          <t>33.2 x 30.3 x 25.4 cm</t>
+          <t>23.8 x 11.7 x 10.2 cm</t>
         </is>
       </c>
       <c r="BQ34" s="23" t="inlineStr">
         <is>
-          <t>33.20 x 30.30 x 25.40 cm</t>
+          <t>23.80 x 11.70 x 10.20 cm</t>
         </is>
       </c>
       <c r="BR34" s="13" t="inlineStr">
         <is>
-          <t>标准包裹</t>
+          <t>小包裹</t>
         </is>
       </c>
     </row>
@@ -13024,40 +12880,40 @@
       <c r="B35" s="13"/>
       <c r="C35" s="14" t="inlineStr">
         <is>
-          <t>B0FW3MWVJR</t>
+          <t>B0GJS592V3</t>
         </is>
       </c>
       <c r="D35" s="14"/>
       <c r="E35" s="14"/>
       <c r="F35" s="14" t="inlineStr">
         <is>
-          <t>JIGOO</t>
+          <t>Yaasier</t>
         </is>
       </c>
       <c r="G35" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/stores/JIGOO-IT/page/7F1C5254-18CC-4331-A449-F5F68B2E288D?lp_asin=B0FW3MWVJR&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Yaasier</t>
         </is>
       </c>
       <c r="H35" s="14" t="inlineStr">
         <is>
-          <t>JIGOO Battimaterasso, Aspiratore per acari Soluzione economica, completamente funzionale, con tutti gli accessori. Soddisfa o</t>
+          <t>Yaasier Aspirapolvere antiacaro per acari, Battimaterasso antiacaro con luce UV e contenitore per polvere permanente HEPA, As</t>
         </is>
       </c>
       <c r="I35" s="14"/>
       <c r="J35" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0FW3MWVJR?psc=1</t>
+          <t>https://www.amazon.it/dp/B0GJS592V3?psc=1</t>
         </is>
       </c>
       <c r="K35" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/61R1ViIQaTL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/51lAD9Ta2TL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L35" s="14" t="inlineStr">
         <is>
-          <t>B0FW3MWVJR</t>
+          <t>B0GJS592V3</t>
         </is>
       </c>
       <c r="M35" s="14" t="inlineStr">
@@ -13071,7 +12927,7 @@
         </is>
       </c>
       <c r="O35" s="15">
-        <v>571192</v>
+        <v>532092</v>
       </c>
       <c r="P35" s="15"/>
       <c r="Q35" s="16">
@@ -13084,7 +12940,7 @@
       </c>
       <c r="S35" s="18" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>35</t>
         </is>
       </c>
       <c r="T35" s="15"/>
@@ -13096,37 +12952,37 @@
         <v>1</v>
       </c>
       <c r="Z35" s="20">
-        <v>65.99</v>
+        <v>39.99</v>
       </c>
       <c r="AA35"/>
       <c r="AB35"/>
       <c r="AC35" s="2"/>
       <c r="AD35" s="19">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="AE35" s="15">
         <v>0</v>
       </c>
       <c r="AF35" s="21">
-        <v>5</v>
+        <v>3.6</v>
       </c>
       <c r="AG35" s="22">
         <v>0</v>
       </c>
       <c r="AH35" s="20">
-        <v>5.3</v>
+        <v>5.12</v>
       </c>
       <c r="AI35" s="16">
-        <v>0.77</v>
+        <v>0.72</v>
       </c>
       <c r="AJ35"/>
       <c r="AK35" s="13" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="AL35" s="19">
-        <v>327</v>
+        <v>247</v>
       </c>
       <c r="AM35" s="13" t="inlineStr">
         <is>
@@ -13144,7 +13000,7 @@
       </c>
       <c r="AS35" s="14" t="inlineStr">
         <is>
-          <t>ANISE EDALS52</t>
+          <t>Renyu</t>
         </is>
       </c>
       <c r="AT35" s="13" t="inlineStr">
@@ -13154,17 +13010,17 @@
       </c>
       <c r="AU35" s="13" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="AV35" s="14" t="inlineStr">
         <is>
-          <t>LONDONDERRY NORTHERN IRELAND BT48 7DE GB</t>
+          <t>dong hu xin ji shu hubei 430223 CN</t>
         </is>
       </c>
       <c r="AW35" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A99P1VJD8HKQ6</t>
+          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=ATK258MBI08TX</t>
         </is>
       </c>
       <c r="AX35" s="13"/>
@@ -13172,7 +13028,11 @@
       <c r="AZ35" s="13"/>
       <c r="BA35" s="13"/>
       <c r="BB35" s="13"/>
-      <c r="BC35" s="13"/>
+      <c r="BC35" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BD35" s="13"/>
       <c r="BE35" s="13"/>
       <c r="BF35" s="13"/>
@@ -13181,25 +13041,49 @@
       <c r="BI35" s="23"/>
       <c r="BJ35" s="23" t="inlineStr">
         <is>
-          <t>2,72 kg</t>
+          <t>250 g</t>
         </is>
       </c>
       <c r="BK35" s="23" t="inlineStr">
         <is>
-          <t>2.72 kg</t>
+          <t>250.00 g</t>
         </is>
       </c>
       <c r="BL35" s="23" t="inlineStr">
         <is>
-          <t>27,2L x 18,8l x 32,9H cm</t>
-        </is>
-      </c>
-      <c r="BM35" s="23"/>
-      <c r="BN35" s="23"/>
-      <c r="BO35" s="23"/>
-      <c r="BP35" s="23"/>
-      <c r="BQ35" s="23"/>
-      <c r="BR35" s="13"/>
+          <t>6 x 4 x 8 cm</t>
+        </is>
+      </c>
+      <c r="BM35" s="23" t="inlineStr">
+        <is>
+          <t>6.00 x 4.00 x 8.00 cm</t>
+        </is>
+      </c>
+      <c r="BN35" s="23" t="inlineStr">
+        <is>
+          <t>400 g</t>
+        </is>
+      </c>
+      <c r="BO35" s="23" t="inlineStr">
+        <is>
+          <t>400.00 g</t>
+        </is>
+      </c>
+      <c r="BP35" s="23" t="inlineStr">
+        <is>
+          <t>23.3 x 11.8 x 10.3 cm</t>
+        </is>
+      </c>
+      <c r="BQ35" s="23" t="inlineStr">
+        <is>
+          <t>23.30 x 11.80 x 10.30 cm</t>
+        </is>
+      </c>
+      <c r="BR35" s="13" t="inlineStr">
+        <is>
+          <t>小包裹</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="13">
@@ -13208,40 +13092,40 @@
       <c r="B36" s="13"/>
       <c r="C36" s="14" t="inlineStr">
         <is>
-          <t>B0FYM1D13D</t>
+          <t>B0GTYZLWW3</t>
         </is>
       </c>
       <c r="D36" s="14"/>
       <c r="E36" s="14"/>
       <c r="F36" s="14" t="inlineStr">
         <is>
-          <t>Yaasier</t>
+          <t>Vehiwell</t>
         </is>
       </c>
       <c r="G36" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Yaasier</t>
+          <t>https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Vehiwell</t>
         </is>
       </c>
       <c r="H36" s="14" t="inlineStr">
         <is>
-          <t>Aspirapolvere antiacaro per acari, Battimaterasso antiacaro con luce UV e contenitore per polvere permanente HEPA, Aspiratore</t>
+          <t>Vehiwell Aspirapolvere per acari, 15 kPa, detergente per materassi con luce UV-C</t>
         </is>
       </c>
       <c r="I36" s="14"/>
       <c r="J36" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0FYM1D13D?psc=1</t>
+          <t>https://www.amazon.it/dp/B0GTYZLWW3?psc=1</t>
         </is>
       </c>
       <c r="K36" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/51dJLeDXofL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71RQJ5XzBgL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L36" s="14" t="inlineStr">
         <is>
-          <t>B0FYM1D13D</t>
+          <t>B0GTYZLWW3</t>
         </is>
       </c>
       <c r="M36" s="14" t="inlineStr">
@@ -13255,11 +13139,13 @@
         </is>
       </c>
       <c r="O36" s="15">
-        <v>1226735</v>
-      </c>
-      <c r="P36" s="15"/>
+        <v>1451348</v>
+      </c>
+      <c r="P36" s="15">
+        <v>-113306</v>
+      </c>
       <c r="Q36" s="16">
-        <v>0</v>
+        <v>-0.08</v>
       </c>
       <c r="R36" s="17" t="inlineStr">
         <is>
@@ -13268,7 +13154,7 @@
       </c>
       <c r="S36" s="18" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>32</t>
         </is>
       </c>
       <c r="T36" s="15"/>
@@ -13280,60 +13166,54 @@
         <v>1</v>
       </c>
       <c r="Z36" s="20">
-        <v>27.99</v>
+        <v>89.99</v>
       </c>
       <c r="AA36"/>
       <c r="AB36"/>
       <c r="AC36" s="2"/>
-      <c r="AD36" s="19">
-        <v>4</v>
-      </c>
-      <c r="AE36" s="15">
-        <v>0</v>
-      </c>
-      <c r="AF36" s="21">
-        <v>3</v>
-      </c>
+      <c r="AD36" s="19"/>
+      <c r="AE36" s="15"/>
+      <c r="AF36" s="21"/>
       <c r="AG36" s="22">
         <v>0</v>
       </c>
       <c r="AH36" s="20">
-        <v>5.12</v>
+        <v>5.21</v>
       </c>
       <c r="AI36" s="16">
-        <v>0.67</v>
+        <v>0.79</v>
       </c>
       <c r="AJ36"/>
       <c r="AK36" s="13" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="AL36" s="19">
-        <v>317</v>
+        <v>122</v>
       </c>
       <c r="AM36" s="13" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>FBA</t>
         </is>
       </c>
       <c r="AN36" s="13"/>
       <c r="AO36" s="13"/>
       <c r="AP36"/>
       <c r="AQ36" s="19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AR36" s="19">
         <v>1</v>
       </c>
       <c r="AS36" s="14" t="inlineStr">
         <is>
-          <t>Renyu</t>
+          <t>DLLest</t>
         </is>
       </c>
       <c r="AT36" s="13" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>FBA</t>
         </is>
       </c>
       <c r="AU36" s="13" t="inlineStr">
@@ -13343,12 +13223,12 @@
       </c>
       <c r="AV36" s="14" t="inlineStr">
         <is>
-          <t>dong hu xin ji shu hubei 430223 CN</t>
+          <t>荆州市 湖北省 434021 CN</t>
         </is>
       </c>
       <c r="AW36" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=ATK258MBI08TX</t>
+          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1F2NCGM6KYOZU</t>
         </is>
       </c>
       <c r="AX36" s="13"/>
@@ -13361,11 +13241,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="BD36" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BD36" s="13"/>
       <c r="BE36" s="13"/>
       <c r="BF36" s="13"/>
       <c r="BG36" s="13"/>
@@ -13373,43 +13249,47 @@
       <c r="BI36" s="23"/>
       <c r="BJ36" s="23" t="inlineStr">
         <is>
-          <t>400 g</t>
+          <t>2 Kilograms</t>
         </is>
       </c>
       <c r="BK36" s="23" t="inlineStr">
         <is>
-          <t>400.00 g</t>
+          <t>2.00 kg</t>
         </is>
       </c>
       <c r="BL36" s="23" t="inlineStr">
         <is>
-          <t>6L x 4l x 8H cm</t>
-        </is>
-      </c>
-      <c r="BM36" s="23"/>
+          <t>34 x 28 x 22 cm</t>
+        </is>
+      </c>
+      <c r="BM36" s="23" t="inlineStr">
+        <is>
+          <t>34.00 x 28.00 x 22.00 cm</t>
+        </is>
+      </c>
       <c r="BN36" s="23" t="inlineStr">
         <is>
-          <t>400 g</t>
+          <t>2 kg</t>
         </is>
       </c>
       <c r="BO36" s="23" t="inlineStr">
         <is>
-          <t>400.00 g</t>
+          <t>2.00 kg</t>
         </is>
       </c>
       <c r="BP36" s="23" t="inlineStr">
         <is>
-          <t>23.8 x 11.7 x 10.2 cm</t>
+          <t>34 x 28 x 22 cm</t>
         </is>
       </c>
       <c r="BQ36" s="23" t="inlineStr">
         <is>
-          <t>23.80 x 11.70 x 10.20 cm</t>
+          <t>34.00 x 28.00 x 22.00 cm</t>
         </is>
       </c>
       <c r="BR36" s="13" t="inlineStr">
         <is>
-          <t>小包裹</t>
+          <t>标准包裹</t>
         </is>
       </c>
     </row>
@@ -13420,40 +13300,40 @@
       <c r="B37" s="13"/>
       <c r="C37" s="14" t="inlineStr">
         <is>
-          <t>B0GJS592V3</t>
+          <t>B0H418FY5Y</t>
         </is>
       </c>
       <c r="D37" s="14"/>
       <c r="E37" s="14"/>
       <c r="F37" s="14" t="inlineStr">
         <is>
-          <t>Yaasier</t>
+          <t>Lubluelu</t>
         </is>
       </c>
       <c r="G37" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Yaasier</t>
+          <t>https://www.amazon.it/stores/Lubluelu/page/14418463-A3CB-412E-B0D5-36E2BEE36429?lp_asin=B0H418FY5Y&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
         </is>
       </c>
       <c r="H37" s="14" t="inlineStr">
         <is>
-          <t>Yaasier Aspirapolvere antiacaro per acari, Battimaterasso antiacaro con luce UV e contenitore per polvere permanente HEPA, As</t>
+          <t>Lubluelu Aspirapolvere acari 20 kPa, 600 W, 65.000 colpi/min, luce UV-CsAspirapolvere per materassi con pulizia profonda, 6</t>
         </is>
       </c>
       <c r="I37" s="14"/>
       <c r="J37" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0GJS592V3?psc=1</t>
+          <t>https://www.amazon.it/dp/B0H418FY5Y?psc=1</t>
         </is>
       </c>
       <c r="K37" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/51lAD9Ta2TL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/61InrYvl2-L._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L37" s="14" t="inlineStr">
         <is>
-          <t>B0GJS592V3</t>
+          <t>B0H418FY5Y</t>
         </is>
       </c>
       <c r="M37" s="14" t="inlineStr">
@@ -13467,7 +13347,7 @@
         </is>
       </c>
       <c r="O37" s="15">
-        <v>532092</v>
+        <v>252469</v>
       </c>
       <c r="P37" s="15"/>
       <c r="Q37" s="16">
@@ -13480,7 +13360,7 @@
       </c>
       <c r="S37" s="18" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>15</t>
         </is>
       </c>
       <c r="T37" s="15"/>
@@ -13492,60 +13372,60 @@
         <v>1</v>
       </c>
       <c r="Z37" s="20">
-        <v>39.99</v>
+        <v>99.99</v>
       </c>
       <c r="AA37"/>
       <c r="AB37"/>
       <c r="AC37" s="2"/>
       <c r="AD37" s="19">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AE37" s="15">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AF37" s="21">
-        <v>3.6</v>
+        <v>4.4</v>
       </c>
       <c r="AG37" s="22">
         <v>0</v>
       </c>
       <c r="AH37" s="20">
-        <v>5.12</v>
+        <v>5.46</v>
       </c>
       <c r="AI37" s="16">
-        <v>0.72</v>
+        <v>0.8</v>
       </c>
       <c r="AJ37"/>
       <c r="AK37" s="13" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="AL37" s="19">
-        <v>247</v>
+        <v>59</v>
       </c>
       <c r="AM37" s="13" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>FBA</t>
         </is>
       </c>
       <c r="AN37" s="13"/>
       <c r="AO37" s="13"/>
       <c r="AP37"/>
       <c r="AQ37" s="19">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AR37" s="19">
         <v>1</v>
       </c>
       <c r="AS37" s="14" t="inlineStr">
         <is>
-          <t>Renyu</t>
+          <t>Lubluelu Official</t>
         </is>
       </c>
       <c r="AT37" s="13" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>FBA</t>
         </is>
       </c>
       <c r="AU37" s="13" t="inlineStr">
@@ -13555,12 +13435,12 @@
       </c>
       <c r="AV37" s="14" t="inlineStr">
         <is>
-          <t>dong hu xin ji shu hubei 430223 CN</t>
+          <t>HuMenZhen GuangDong 523000 CN</t>
         </is>
       </c>
       <c r="AW37" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=ATK258MBI08TX</t>
+          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A23BRZJD26C30N</t>
         </is>
       </c>
       <c r="AX37" s="13"/>
@@ -13568,11 +13448,7 @@
       <c r="AZ37" s="13"/>
       <c r="BA37" s="13"/>
       <c r="BB37" s="13"/>
-      <c r="BC37" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BC37" s="13"/>
       <c r="BD37" s="13"/>
       <c r="BE37" s="13"/>
       <c r="BF37" s="13"/>
@@ -13581,571 +13457,49 @@
       <c r="BI37" s="23"/>
       <c r="BJ37" s="23" t="inlineStr">
         <is>
-          <t>250 g</t>
+          <t>2,34 Kilograms</t>
         </is>
       </c>
       <c r="BK37" s="23" t="inlineStr">
         <is>
-          <t>250.00 g</t>
+          <t>2.34 kg</t>
         </is>
       </c>
       <c r="BL37" s="23" t="inlineStr">
         <is>
-          <t>6 x 4 x 8 cm</t>
+          <t>42 x 31 x 18 cm</t>
         </is>
       </c>
       <c r="BM37" s="23" t="inlineStr">
         <is>
-          <t>6.00 x 4.00 x 8.00 cm</t>
+          <t>42.00 x 31.00 x 18.00 cm</t>
         </is>
       </c>
       <c r="BN37" s="23" t="inlineStr">
         <is>
-          <t>400 g</t>
+          <t>2.34 kg</t>
         </is>
       </c>
       <c r="BO37" s="23" t="inlineStr">
         <is>
-          <t>400.00 g</t>
+          <t>2.34 kg</t>
         </is>
       </c>
       <c r="BP37" s="23" t="inlineStr">
         <is>
-          <t>23.3 x 11.8 x 10.3 cm</t>
+          <t>35 x 33.5 x 25.4 cm</t>
         </is>
       </c>
       <c r="BQ37" s="23" t="inlineStr">
         <is>
-          <t>23.30 x 11.80 x 10.30 cm</t>
+          <t>35.00 x 33.50 x 25.40 cm</t>
         </is>
       </c>
       <c r="BR37" s="13" t="inlineStr">
         <is>
-          <t>小包裹</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="13">
-        <v>37</v>
-      </c>
-      <c r="B38" s="13"/>
-      <c r="C38" s="14" t="inlineStr">
-        <is>
-          <t>B0GTYZLWW3</t>
-        </is>
-      </c>
-      <c r="D38" s="14"/>
-      <c r="E38" s="14"/>
-      <c r="F38" s="14" t="inlineStr">
-        <is>
-          <t>Vehiwell</t>
-        </is>
-      </c>
-      <c r="G38" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Vehiwell</t>
-        </is>
-      </c>
-      <c r="H38" s="14" t="inlineStr">
-        <is>
-          <t>Vehiwell Aspirapolvere per acari, 15 kPa, detergente per materassi con luce UV-C</t>
-        </is>
-      </c>
-      <c r="I38" s="14"/>
-      <c r="J38" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.it/dp/B0GTYZLWW3?psc=1</t>
-        </is>
-      </c>
-      <c r="K38" s="14" t="inlineStr">
-        <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71RQJ5XzBgL._AC_US600_.jpg</t>
-        </is>
-      </c>
-      <c r="L38" s="14" t="inlineStr">
-        <is>
-          <t>B0GTYZLWW3</t>
-        </is>
-      </c>
-      <c r="M38" s="14" t="inlineStr">
-        <is>
-          <t>Casa e cucina:Aspirapolvere e pulizia di pavimenti e finestre:Aspirapolvere:Aspirapolvere per futon</t>
-        </is>
-      </c>
-      <c r="N38" s="14" t="inlineStr">
-        <is>
-          <t>Visualizza i Top 100 nella categoria Casa e c</t>
-        </is>
-      </c>
-      <c r="O38" s="15">
-        <v>1451348</v>
-      </c>
-      <c r="P38" s="15">
-        <v>-113306</v>
-      </c>
-      <c r="Q38" s="16">
-        <v>-0.08</v>
-      </c>
-      <c r="R38" s="17" t="inlineStr">
-        <is>
-          <t>Aspirapolvere per futon</t>
-        </is>
-      </c>
-      <c r="S38" s="18" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="T38" s="15"/>
-      <c r="U38" s="16"/>
-      <c r="V38" s="15"/>
-      <c r="W38" s="15"/>
-      <c r="X38" s="15"/>
-      <c r="Y38" s="19">
-        <v>1</v>
-      </c>
-      <c r="Z38" s="20">
-        <v>89.99</v>
-      </c>
-      <c r="AA38"/>
-      <c r="AB38"/>
-      <c r="AC38" s="2"/>
-      <c r="AD38" s="19"/>
-      <c r="AE38" s="15"/>
-      <c r="AF38" s="21"/>
-      <c r="AG38" s="22">
-        <v>0</v>
-      </c>
-      <c r="AH38" s="20">
-        <v>5.21</v>
-      </c>
-      <c r="AI38" s="16">
-        <v>0.79</v>
-      </c>
-      <c r="AJ38"/>
-      <c r="AK38" s="13" t="inlineStr">
-        <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-      <c r="AL38" s="19">
-        <v>122</v>
-      </c>
-      <c r="AM38" s="13" t="inlineStr">
-        <is>
-          <t>FBA</t>
-        </is>
-      </c>
-      <c r="AN38" s="13"/>
-      <c r="AO38" s="13"/>
-      <c r="AP38"/>
-      <c r="AQ38" s="19">
-        <v>8</v>
-      </c>
-      <c r="AR38" s="19">
-        <v>1</v>
-      </c>
-      <c r="AS38" s="14" t="inlineStr">
-        <is>
-          <t>DLLest</t>
-        </is>
-      </c>
-      <c r="AT38" s="13" t="inlineStr">
-        <is>
-          <t>FBA</t>
-        </is>
-      </c>
-      <c r="AU38" s="13" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="AV38" s="14" t="inlineStr">
-        <is>
-          <t>荆州市 湖北省 434021 CN</t>
-        </is>
-      </c>
-      <c r="AW38" s="13" t="inlineStr">
-        <is>
-          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1F2NCGM6KYOZU</t>
-        </is>
-      </c>
-      <c r="AX38" s="13"/>
-      <c r="AY38" s="13"/>
-      <c r="AZ38" s="13"/>
-      <c r="BA38" s="13"/>
-      <c r="BB38" s="13"/>
-      <c r="BC38" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BD38" s="13"/>
-      <c r="BE38" s="13"/>
-      <c r="BF38" s="13"/>
-      <c r="BG38" s="13"/>
-      <c r="BH38" s="14"/>
-      <c r="BI38" s="23"/>
-      <c r="BJ38" s="23" t="inlineStr">
-        <is>
-          <t>2 Kilograms</t>
-        </is>
-      </c>
-      <c r="BK38" s="23" t="inlineStr">
-        <is>
-          <t>2.00 kg</t>
-        </is>
-      </c>
-      <c r="BL38" s="23" t="inlineStr">
-        <is>
-          <t>34 x 28 x 22 cm</t>
-        </is>
-      </c>
-      <c r="BM38" s="23" t="inlineStr">
-        <is>
-          <t>34.00 x 28.00 x 22.00 cm</t>
-        </is>
-      </c>
-      <c r="BN38" s="23" t="inlineStr">
-        <is>
-          <t>2 kg</t>
-        </is>
-      </c>
-      <c r="BO38" s="23" t="inlineStr">
-        <is>
-          <t>2.00 kg</t>
-        </is>
-      </c>
-      <c r="BP38" s="23" t="inlineStr">
-        <is>
-          <t>34 x 28 x 22 cm</t>
-        </is>
-      </c>
-      <c r="BQ38" s="23" t="inlineStr">
-        <is>
-          <t>34.00 x 28.00 x 22.00 cm</t>
-        </is>
-      </c>
-      <c r="BR38" s="13" t="inlineStr">
-        <is>
           <t>标准包裹</t>
         </is>
       </c>
-    </row>
-    <row r="39" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="13">
-        <v>38</v>
-      </c>
-      <c r="B39" s="13"/>
-      <c r="C39" s="14" t="inlineStr">
-        <is>
-          <t>B0H418FY5Y</t>
-        </is>
-      </c>
-      <c r="D39" s="14"/>
-      <c r="E39" s="14"/>
-      <c r="F39" s="14" t="inlineStr">
-        <is>
-          <t>Lubluelu</t>
-        </is>
-      </c>
-      <c r="G39" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.it/stores/Lubluelu/page/14418463-A3CB-412E-B0D5-36E2BEE36429?lp_asin=B0H418FY5Y&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
-        </is>
-      </c>
-      <c r="H39" s="14" t="inlineStr">
-        <is>
-          <t>Lubluelu Aspirapolvere acari 20 kPa, 600 W, 65.000 colpi/min, luce UV-CsAspirapolvere per materassi con pulizia profonda, 6</t>
-        </is>
-      </c>
-      <c r="I39" s="14"/>
-      <c r="J39" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.it/dp/B0H418FY5Y?psc=1</t>
-        </is>
-      </c>
-      <c r="K39" s="14" t="inlineStr">
-        <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/61InrYvl2-L._AC_US600_.jpg</t>
-        </is>
-      </c>
-      <c r="L39" s="14" t="inlineStr">
-        <is>
-          <t>B0H418FY5Y</t>
-        </is>
-      </c>
-      <c r="M39" s="14" t="inlineStr">
-        <is>
-          <t>Casa e cucina:Aspirapolvere e pulizia di pavimenti e finestre:Aspirapolvere:Aspirapolvere per futon</t>
-        </is>
-      </c>
-      <c r="N39" s="14" t="inlineStr">
-        <is>
-          <t>Visualizza i Top 100 nella categoria Casa e c</t>
-        </is>
-      </c>
-      <c r="O39" s="15">
-        <v>252469</v>
-      </c>
-      <c r="P39" s="15"/>
-      <c r="Q39" s="16">
-        <v>0</v>
-      </c>
-      <c r="R39" s="17" t="inlineStr">
-        <is>
-          <t>Aspirapolvere per futon</t>
-        </is>
-      </c>
-      <c r="S39" s="18" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="T39" s="15"/>
-      <c r="U39" s="16"/>
-      <c r="V39" s="15"/>
-      <c r="W39" s="15"/>
-      <c r="X39" s="15"/>
-      <c r="Y39" s="19">
-        <v>1</v>
-      </c>
-      <c r="Z39" s="20">
-        <v>99.99</v>
-      </c>
-      <c r="AA39"/>
-      <c r="AB39"/>
-      <c r="AC39" s="2"/>
-      <c r="AD39" s="19">
-        <v>25</v>
-      </c>
-      <c r="AE39" s="15">
-        <v>15</v>
-      </c>
-      <c r="AF39" s="21">
-        <v>4.4</v>
-      </c>
-      <c r="AG39" s="22">
-        <v>0</v>
-      </c>
-      <c r="AH39" s="20">
-        <v>5.46</v>
-      </c>
-      <c r="AI39" s="16">
-        <v>0.8</v>
-      </c>
-      <c r="AJ39"/>
-      <c r="AK39" s="13" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="AL39" s="19">
-        <v>59</v>
-      </c>
-      <c r="AM39" s="13" t="inlineStr">
-        <is>
-          <t>FBA</t>
-        </is>
-      </c>
-      <c r="AN39" s="13"/>
-      <c r="AO39" s="13"/>
-      <c r="AP39"/>
-      <c r="AQ39" s="19">
-        <v>7</v>
-      </c>
-      <c r="AR39" s="19">
-        <v>1</v>
-      </c>
-      <c r="AS39" s="14" t="inlineStr">
-        <is>
-          <t>Lubluelu Official</t>
-        </is>
-      </c>
-      <c r="AT39" s="13" t="inlineStr">
-        <is>
-          <t>FBA</t>
-        </is>
-      </c>
-      <c r="AU39" s="13" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="AV39" s="14" t="inlineStr">
-        <is>
-          <t>HuMenZhen GuangDong 523000 CN</t>
-        </is>
-      </c>
-      <c r="AW39" s="13" t="inlineStr">
-        <is>
-          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A23BRZJD26C30N</t>
-        </is>
-      </c>
-      <c r="AX39" s="13"/>
-      <c r="AY39" s="13"/>
-      <c r="AZ39" s="13"/>
-      <c r="BA39" s="13"/>
-      <c r="BB39" s="13"/>
-      <c r="BC39" s="13"/>
-      <c r="BD39" s="13"/>
-      <c r="BE39" s="13"/>
-      <c r="BF39" s="13"/>
-      <c r="BG39" s="13"/>
-      <c r="BH39" s="14"/>
-      <c r="BI39" s="23"/>
-      <c r="BJ39" s="23" t="inlineStr">
-        <is>
-          <t>2,34 Kilograms</t>
-        </is>
-      </c>
-      <c r="BK39" s="23" t="inlineStr">
-        <is>
-          <t>2.34 kg</t>
-        </is>
-      </c>
-      <c r="BL39" s="23" t="inlineStr">
-        <is>
-          <t>42 x 31 x 18 cm</t>
-        </is>
-      </c>
-      <c r="BM39" s="23" t="inlineStr">
-        <is>
-          <t>42.00 x 31.00 x 18.00 cm</t>
-        </is>
-      </c>
-      <c r="BN39" s="23" t="inlineStr">
-        <is>
-          <t>2.34 kg</t>
-        </is>
-      </c>
-      <c r="BO39" s="23" t="inlineStr">
-        <is>
-          <t>2.34 kg</t>
-        </is>
-      </c>
-      <c r="BP39" s="23" t="inlineStr">
-        <is>
-          <t>35 x 33.5 x 25.4 cm</t>
-        </is>
-      </c>
-      <c r="BQ39" s="23" t="inlineStr">
-        <is>
-          <t>35.00 x 33.50 x 25.40 cm</t>
-        </is>
-      </c>
-      <c r="BR39" s="13" t="inlineStr">
-        <is>
-          <t>标准包裹</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="13">
-        <v>39</v>
-      </c>
-      <c r="B40" s="13"/>
-      <c r="C40" s="14" t="inlineStr">
-        <is>
-          <t>B0H6Q8KWCD</t>
-        </is>
-      </c>
-      <c r="D40" s="14"/>
-      <c r="E40" s="14"/>
-      <c r="F40" s="14"/>
-      <c r="G40" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.itundefined</t>
-        </is>
-      </c>
-      <c r="H40" s="14" t="inlineStr">
-        <is>
-          <t>Taurus - Pulitore Aspiratore ad Acqua per Tappezzerie e Tappeti, Liquidi e Solidi, Serbatoi per Acqua Pulita e Acqua Sporca</t>
-        </is>
-      </c>
-      <c r="I40" s="14"/>
-      <c r="J40" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.it/dp/B0H6Q8KWCD?psc=1</t>
-        </is>
-      </c>
-      <c r="K40" s="14" t="inlineStr">
-        <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/61nyUqj7HSL._AC_UL300_SR300,200_.jpg</t>
-        </is>
-      </c>
-      <c r="L40" s="14" t="inlineStr">
-        <is>
-          <t>B0H6Q8KWCD</t>
-        </is>
-      </c>
-      <c r="M40" s="14"/>
-      <c r="N40" s="14"/>
-      <c r="O40" s="15"/>
-      <c r="P40" s="15"/>
-      <c r="Q40" s="16"/>
-      <c r="R40" s="17"/>
-      <c r="S40" s="18"/>
-      <c r="T40" s="15"/>
-      <c r="U40" s="16"/>
-      <c r="V40" s="15"/>
-      <c r="W40" s="15"/>
-      <c r="X40" s="15"/>
-      <c r="Y40" s="19"/>
-      <c r="Z40" s="20"/>
-      <c r="AA40"/>
-      <c r="AB40"/>
-      <c r="AC40" s="2"/>
-      <c r="AD40" s="19">
-        <v>10</v>
-      </c>
-      <c r="AE40" s="15"/>
-      <c r="AF40" s="21">
-        <v>3.6</v>
-      </c>
-      <c r="AG40" s="22">
-        <v>0</v>
-      </c>
-      <c r="AH40" s="20"/>
-      <c r="AI40" s="16">
-        <v>0</v>
-      </c>
-      <c r="AJ40"/>
-      <c r="AK40" s="13"/>
-      <c r="AL40" s="19"/>
-      <c r="AM40" s="13"/>
-      <c r="AN40" s="13"/>
-      <c r="AO40" s="13"/>
-      <c r="AP40"/>
-      <c r="AQ40" s="19"/>
-      <c r="AR40" s="19"/>
-      <c r="AS40" s="14"/>
-      <c r="AT40" s="13"/>
-      <c r="AU40" s="13"/>
-      <c r="AV40" s="14"/>
-      <c r="AW40" s="13"/>
-      <c r="AX40" s="13"/>
-      <c r="AY40" s="13"/>
-      <c r="AZ40" s="13"/>
-      <c r="BA40" s="13"/>
-      <c r="BB40" s="13"/>
-      <c r="BC40" s="13"/>
-      <c r="BD40" s="13"/>
-      <c r="BE40" s="13"/>
-      <c r="BF40" s="13"/>
-      <c r="BG40" s="13"/>
-      <c r="BH40" s="14"/>
-      <c r="BI40" s="23"/>
-      <c r="BJ40" s="23"/>
-      <c r="BK40" s="23"/>
-      <c r="BL40" s="23"/>
-      <c r="BM40" s="23"/>
-      <c r="BN40" s="23"/>
-      <c r="BO40" s="23"/>
-      <c r="BP40" s="23"/>
-      <c r="BQ40" s="23"/>
-      <c r="BR40" s="13"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -14259,768 +13613,177 @@
     <hyperlink ref="M15" r:id="rId106" tooltip="https://www.amazon.it/b?node=13713022031"/>
     <hyperlink ref="N15" r:id="rId107"/>
     <hyperlink ref="AW15" r:id="rId108" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=ASTEKNQOF9QUQ"/>
-    <hyperlink ref="C16" r:id="rId109" tooltip="https://www.amazon.it/dp/B0FDWVV95V"/>
-    <hyperlink ref="G16" r:id="rId110" tooltip="https://www.amazon.it/stores/JIGOO-IT/page/7F1C5254-18CC-4331-A449-F5F68B2E288D?lp_asin=B0FDWVV95V&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J16" r:id="rId111" tooltip="https://www.amazon.it/dp/B0FDWVV95V?psc=1"/>
-    <hyperlink ref="K16" r:id="rId112" tooltip="https://images-na.ssl-images-amazon.com/images/I/61tL+-AcL6L._AC_US600_.jpg"/>
-    <hyperlink ref="L16" r:id="rId113" tooltip="https://www.amazon.it/dp/B0FDWVV95V"/>
+    <hyperlink ref="C16" r:id="rId109" tooltip="https://www.amazon.it/dp/B0BPKND56B"/>
+    <hyperlink ref="G16" r:id="rId110" tooltip="https://www.amazon.it/Vihoom/b/ref=bl_dp_s_web_76112668031?ie=UTF8&amp;node=76112668031&amp;field-lbr_brands_browse-bin=Vihoom"/>
+    <hyperlink ref="J16" r:id="rId111" tooltip="https://www.amazon.it/dp/B0BPKND56B?psc=1"/>
+    <hyperlink ref="K16" r:id="rId112" tooltip="https://images-na.ssl-images-amazon.com/images/I/61soarCZgdL._AC_US600_.jpg"/>
+    <hyperlink ref="L16" r:id="rId113" tooltip="https://www.amazon.it/dp/B0BPKND56B"/>
     <hyperlink ref="M16" r:id="rId114" tooltip="https://www.amazon.it/b?node=13713022031"/>
     <hyperlink ref="N16" r:id="rId115"/>
-    <hyperlink ref="AW16" r:id="rId116" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1OG68CATOOAOD"/>
-    <hyperlink ref="C17" r:id="rId117" tooltip="https://www.amazon.it/dp/B0BPKND56B"/>
-    <hyperlink ref="G17" r:id="rId118" tooltip="https://www.amazon.it/Vihoom/b/ref=bl_dp_s_web_76112668031?ie=UTF8&amp;node=76112668031&amp;field-lbr_brands_browse-bin=Vihoom"/>
-    <hyperlink ref="J17" r:id="rId119" tooltip="https://www.amazon.it/dp/B0BPKND56B?psc=1"/>
-    <hyperlink ref="K17" r:id="rId120" tooltip="https://images-na.ssl-images-amazon.com/images/I/61soarCZgdL._AC_US600_.jpg"/>
-    <hyperlink ref="L17" r:id="rId121" tooltip="https://www.amazon.it/dp/B0BPKND56B"/>
+    <hyperlink ref="AW16" r:id="rId116" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1AHZ7S75PQI7K"/>
+    <hyperlink ref="C17" r:id="rId117" tooltip="https://www.amazon.it/dp/B0CSN4RZV3"/>
+    <hyperlink ref="G17" r:id="rId118" tooltip="https://www.amazon.it/stores/Dibea/page/2F0F673F-94DF-4200-9096-92CD398CE8D0?lp_asin=B0CSN4RZV3&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J17" r:id="rId119" tooltip="https://www.amazon.it/dp/B0CSN4RZV3?psc=1"/>
+    <hyperlink ref="K17" r:id="rId120" tooltip="https://images-na.ssl-images-amazon.com/images/I/61kgLFAeJWL._AC_US600_.jpg"/>
+    <hyperlink ref="L17" r:id="rId121" tooltip="https://www.amazon.it/dp/B0CSN4RZV3"/>
     <hyperlink ref="M17" r:id="rId122" tooltip="https://www.amazon.it/b?node=13713022031"/>
     <hyperlink ref="N17" r:id="rId123"/>
-    <hyperlink ref="AW17" r:id="rId124" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1AHZ7S75PQI7K"/>
-    <hyperlink ref="C18" r:id="rId125" tooltip="https://www.amazon.it/dp/B0CSN4RZV3"/>
-    <hyperlink ref="G18" r:id="rId126" tooltip="https://www.amazon.it/stores/Dibea/page/2F0F673F-94DF-4200-9096-92CD398CE8D0?lp_asin=B0CSN4RZV3&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J18" r:id="rId127" tooltip="https://www.amazon.it/dp/B0CSN4RZV3?psc=1"/>
-    <hyperlink ref="K18" r:id="rId128" tooltip="https://images-na.ssl-images-amazon.com/images/I/61kgLFAeJWL._AC_US600_.jpg"/>
-    <hyperlink ref="L18" r:id="rId129" tooltip="https://www.amazon.it/dp/B0CSN4RZV3"/>
-    <hyperlink ref="M18" r:id="rId130" tooltip="https://www.amazon.it/b?node=13713022031"/>
-    <hyperlink ref="N18" r:id="rId131"/>
-    <hyperlink ref="AW18" r:id="rId132" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3B52P1ZT41O2I"/>
-    <hyperlink ref="C19" r:id="rId133" tooltip="https://www.amazon.it/dp/B0D454221Z"/>
-    <hyperlink ref="G19" r:id="rId134" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J19" r:id="rId135" tooltip="https://www.amazon.it/dp/B0D454221Z?psc=1"/>
-    <hyperlink ref="K19" r:id="rId136" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71MEJ7kD0dL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L19" r:id="rId137" tooltip="https://www.amazon.it/dp/B0D454221Z"/>
-    <hyperlink ref="C20" r:id="rId138" tooltip="https://www.amazon.it/dp/B0DLWJD9MV"/>
-    <hyperlink ref="G20" r:id="rId139" tooltip="https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=SIKITUT"/>
-    <hyperlink ref="J20" r:id="rId140" tooltip="https://www.amazon.it/dp/B0DLWJD9MV?psc=1"/>
-    <hyperlink ref="K20" r:id="rId141" tooltip="https://images-na.ssl-images-amazon.com/images/I/71tdIOZsxcL._AC_US600_.jpg"/>
-    <hyperlink ref="L20" r:id="rId142" tooltip="https://www.amazon.it/dp/B0DLWJD9MV"/>
+    <hyperlink ref="AW17" r:id="rId124" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3B52P1ZT41O2I"/>
+    <hyperlink ref="C18" r:id="rId125" tooltip="https://www.amazon.it/dp/B0D454221Z"/>
+    <hyperlink ref="G18" r:id="rId126" tooltip="https://www.amazon.itundefined"/>
+    <hyperlink ref="J18" r:id="rId127" tooltip="https://www.amazon.it/dp/B0D454221Z?psc=1"/>
+    <hyperlink ref="K18" r:id="rId128" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71MEJ7kD0dL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L18" r:id="rId129" tooltip="https://www.amazon.it/dp/B0D454221Z"/>
+    <hyperlink ref="C19" r:id="rId130" tooltip="https://www.amazon.it/dp/B0DLWJD9MV"/>
+    <hyperlink ref="G19" r:id="rId131" tooltip="https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=SIKITUT"/>
+    <hyperlink ref="J19" r:id="rId132" tooltip="https://www.amazon.it/dp/B0DLWJD9MV?psc=1"/>
+    <hyperlink ref="K19" r:id="rId133" tooltip="https://images-na.ssl-images-amazon.com/images/I/71tdIOZsxcL._AC_US600_.jpg"/>
+    <hyperlink ref="L19" r:id="rId134" tooltip="https://www.amazon.it/dp/B0DLWJD9MV"/>
+    <hyperlink ref="M19" r:id="rId135" tooltip="https://www.amazon.it/b?node=13713022031"/>
+    <hyperlink ref="N19" r:id="rId136"/>
+    <hyperlink ref="AW19" r:id="rId137" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A144XIL10CDODF"/>
+    <hyperlink ref="C20" r:id="rId138" tooltip="https://www.amazon.it/dp/B0DNYVJ4PL"/>
+    <hyperlink ref="G20" r:id="rId139" tooltip="https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=FEPPO"/>
+    <hyperlink ref="J20" r:id="rId140" tooltip="https://www.amazon.it/dp/B0DNYVJ4PL?psc=1"/>
+    <hyperlink ref="K20" r:id="rId141" tooltip="https://images-na.ssl-images-amazon.com/images/I/71X5KPbPpoL._AC_US600_.jpg"/>
+    <hyperlink ref="L20" r:id="rId142" tooltip="https://www.amazon.it/dp/B0DNYVJ4PL"/>
     <hyperlink ref="M20" r:id="rId143" tooltip="https://www.amazon.it/b?node=13713022031"/>
     <hyperlink ref="N20" r:id="rId144"/>
-    <hyperlink ref="AW20" r:id="rId145" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A144XIL10CDODF"/>
-    <hyperlink ref="C21" r:id="rId146" tooltip="https://www.amazon.it/dp/B0DNYVJ4PL"/>
-    <hyperlink ref="G21" r:id="rId147" tooltip="https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=FEPPO"/>
-    <hyperlink ref="J21" r:id="rId148" tooltip="https://www.amazon.it/dp/B0DNYVJ4PL?psc=1"/>
-    <hyperlink ref="K21" r:id="rId149" tooltip="https://images-na.ssl-images-amazon.com/images/I/71X5KPbPpoL._AC_US600_.jpg"/>
-    <hyperlink ref="L21" r:id="rId150" tooltip="https://www.amazon.it/dp/B0DNYVJ4PL"/>
-    <hyperlink ref="M21" r:id="rId151" tooltip="https://www.amazon.it/b?node=13713022031"/>
-    <hyperlink ref="N21" r:id="rId152"/>
-    <hyperlink ref="C22" r:id="rId153" tooltip="https://www.amazon.it/dp/B0DNZ5LDQX"/>
-    <hyperlink ref="G22" r:id="rId154" tooltip="https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Liwankaqi"/>
-    <hyperlink ref="J22" r:id="rId155" tooltip="https://www.amazon.it/dp/B0DNZ5LDQX?psc=1"/>
-    <hyperlink ref="K22" r:id="rId156" tooltip="https://images-na.ssl-images-amazon.com/images/I/61YjHSHoT6L._AC_US600_.jpg"/>
-    <hyperlink ref="L22" r:id="rId157" tooltip="https://www.amazon.it/dp/B0DNZ5LDQX"/>
-    <hyperlink ref="M22" r:id="rId158" tooltip="https://www.amazon.it/b?node=13713022031"/>
-    <hyperlink ref="N22" r:id="rId159"/>
-    <hyperlink ref="AW22" r:id="rId160" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1CO438NU9H9Y"/>
-    <hyperlink ref="C23" r:id="rId161" tooltip="https://www.amazon.it/dp/B0F2MQCLRJ"/>
-    <hyperlink ref="G23" r:id="rId162" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J23" r:id="rId163" tooltip="https://www.amazon.it/dp/B0F2MQCLRJ?psc=1"/>
-    <hyperlink ref="K23" r:id="rId164" tooltip="https://images-eu.ssl-images-amazon.com/images/I/51INLecMxKL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L23" r:id="rId165" tooltip="https://www.amazon.it/dp/B0F2MQCLRJ"/>
-    <hyperlink ref="C24" r:id="rId166" tooltip="https://www.amazon.it/dp/B0F37ZFRR3"/>
-    <hyperlink ref="G24" r:id="rId167" tooltip="https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Lambluefly"/>
-    <hyperlink ref="J24" r:id="rId168" tooltip="https://www.amazon.it/dp/B0F37ZFRR3?psc=1"/>
-    <hyperlink ref="K24" r:id="rId169" tooltip="https://images-na.ssl-images-amazon.com/images/I/71c5xOT1pjL._AC_US600_.jpg"/>
-    <hyperlink ref="L24" r:id="rId170" tooltip="https://www.amazon.it/dp/B0F37ZFRR3"/>
+    <hyperlink ref="C21" r:id="rId145" tooltip="https://www.amazon.it/dp/B0DNZ5LDQX"/>
+    <hyperlink ref="G21" r:id="rId146" tooltip="https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Liwankaqi"/>
+    <hyperlink ref="J21" r:id="rId147" tooltip="https://www.amazon.it/dp/B0DNZ5LDQX?psc=1"/>
+    <hyperlink ref="K21" r:id="rId148" tooltip="https://images-na.ssl-images-amazon.com/images/I/61YjHSHoT6L._AC_US600_.jpg"/>
+    <hyperlink ref="L21" r:id="rId149" tooltip="https://www.amazon.it/dp/B0DNZ5LDQX"/>
+    <hyperlink ref="M21" r:id="rId150" tooltip="https://www.amazon.it/b?node=13713022031"/>
+    <hyperlink ref="N21" r:id="rId151"/>
+    <hyperlink ref="AW21" r:id="rId152" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1CO438NU9H9Y"/>
+    <hyperlink ref="C22" r:id="rId153" tooltip="https://www.amazon.it/dp/B0F2MQCLRJ"/>
+    <hyperlink ref="G22" r:id="rId154" tooltip="https://www.amazon.itundefined"/>
+    <hyperlink ref="J22" r:id="rId155" tooltip="https://www.amazon.it/dp/B0F2MQCLRJ?psc=1"/>
+    <hyperlink ref="K22" r:id="rId156" tooltip="https://images-eu.ssl-images-amazon.com/images/I/51INLecMxKL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L22" r:id="rId157" tooltip="https://www.amazon.it/dp/B0F2MQCLRJ"/>
+    <hyperlink ref="C23" r:id="rId158" tooltip="https://www.amazon.it/dp/B0F37ZFRR3"/>
+    <hyperlink ref="G23" r:id="rId159" tooltip="https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Lambluefly"/>
+    <hyperlink ref="J23" r:id="rId160" tooltip="https://www.amazon.it/dp/B0F37ZFRR3?psc=1"/>
+    <hyperlink ref="K23" r:id="rId161" tooltip="https://images-na.ssl-images-amazon.com/images/I/71c5xOT1pjL._AC_US600_.jpg"/>
+    <hyperlink ref="L23" r:id="rId162" tooltip="https://www.amazon.it/dp/B0F37ZFRR3"/>
+    <hyperlink ref="M23" r:id="rId163" tooltip="https://www.amazon.it/b?node=13713022031"/>
+    <hyperlink ref="N23" r:id="rId164"/>
+    <hyperlink ref="AW23" r:id="rId165" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2ICHMKIWU9TG5"/>
+    <hyperlink ref="C24" r:id="rId166" tooltip="https://www.amazon.it/dp/B0F6XNKG8M"/>
+    <hyperlink ref="G24" r:id="rId167" tooltip="https://www.amazon.it/stores/Tiazhan/page/5D8B0E80-8C93-44AB-A84E-49819E75E76B?lp_asin=B0F6XNKG8M&amp;ref_=ast_bln"/>
+    <hyperlink ref="J24" r:id="rId168" tooltip="https://www.amazon.it/dp/B0F6XNKG8M?psc=1"/>
+    <hyperlink ref="K24" r:id="rId169" tooltip="https://images-na.ssl-images-amazon.com/images/I/71iADJb-ECL._AC_US600_.jpg"/>
+    <hyperlink ref="L24" r:id="rId170" tooltip="https://www.amazon.it/dp/B0F6XNKG8M"/>
     <hyperlink ref="M24" r:id="rId171" tooltip="https://www.amazon.it/b?node=13713022031"/>
     <hyperlink ref="N24" r:id="rId172"/>
-    <hyperlink ref="AW24" r:id="rId173" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2ICHMKIWU9TG5"/>
-    <hyperlink ref="C25" r:id="rId174" tooltip="https://www.amazon.it/dp/B0F6XNKG8M"/>
-    <hyperlink ref="G25" r:id="rId175" tooltip="https://www.amazon.it/stores/Tiazhan/page/5D8B0E80-8C93-44AB-A84E-49819E75E76B?lp_asin=B0F6XNKG8M&amp;ref_=ast_bln"/>
-    <hyperlink ref="J25" r:id="rId176" tooltip="https://www.amazon.it/dp/B0F6XNKG8M?psc=1"/>
-    <hyperlink ref="K25" r:id="rId177" tooltip="https://images-na.ssl-images-amazon.com/images/I/71iADJb-ECL._AC_US600_.jpg"/>
-    <hyperlink ref="L25" r:id="rId178" tooltip="https://www.amazon.it/dp/B0F6XNKG8M"/>
+    <hyperlink ref="AW24" r:id="rId173" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1P6U062ILG5ZO"/>
+    <hyperlink ref="C25" r:id="rId174" tooltip="https://www.amazon.it/dp/B0F8HD3649"/>
+    <hyperlink ref="G25" r:id="rId175" tooltip="https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Mayking"/>
+    <hyperlink ref="J25" r:id="rId176" tooltip="https://www.amazon.it/dp/B0F8HD3649?psc=1"/>
+    <hyperlink ref="K25" r:id="rId177" tooltip="https://images-na.ssl-images-amazon.com/images/I/71CtAiuTm1L._AC_US600_.jpg"/>
+    <hyperlink ref="L25" r:id="rId178" tooltip="https://www.amazon.it/dp/B0F8HD3649"/>
     <hyperlink ref="M25" r:id="rId179" tooltip="https://www.amazon.it/b?node=13713022031"/>
     <hyperlink ref="N25" r:id="rId180"/>
-    <hyperlink ref="AW25" r:id="rId181" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1P6U062ILG5ZO"/>
-    <hyperlink ref="C26" r:id="rId182" tooltip="https://www.amazon.it/dp/B0F8HD3649"/>
-    <hyperlink ref="G26" r:id="rId183" tooltip="https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Mayking"/>
-    <hyperlink ref="J26" r:id="rId184" tooltip="https://www.amazon.it/dp/B0F8HD3649?psc=1"/>
-    <hyperlink ref="K26" r:id="rId185" tooltip="https://images-na.ssl-images-amazon.com/images/I/71CtAiuTm1L._AC_US600_.jpg"/>
-    <hyperlink ref="L26" r:id="rId186" tooltip="https://www.amazon.it/dp/B0F8HD3649"/>
+    <hyperlink ref="AW25" r:id="rId181" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3EVTWEH1TBVG5"/>
+    <hyperlink ref="C26" r:id="rId182" tooltip="https://www.amazon.it/dp/B0F9NJM4V9"/>
+    <hyperlink ref="G26" r:id="rId183" tooltip="https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Liwankaqi"/>
+    <hyperlink ref="J26" r:id="rId184" tooltip="https://www.amazon.it/dp/B0F9NJM4V9?psc=1"/>
+    <hyperlink ref="K26" r:id="rId185" tooltip="https://images-na.ssl-images-amazon.com/images/I/61GdOBS8v+L._AC_US600_.jpg"/>
+    <hyperlink ref="L26" r:id="rId186" tooltip="https://www.amazon.it/dp/B0F9NJM4V9"/>
     <hyperlink ref="M26" r:id="rId187" tooltip="https://www.amazon.it/b?node=13713022031"/>
     <hyperlink ref="N26" r:id="rId188"/>
-    <hyperlink ref="AW26" r:id="rId189" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3EVTWEH1TBVG5"/>
-    <hyperlink ref="C27" r:id="rId190" tooltip="https://www.amazon.it/dp/B0F8W81X7Y"/>
-    <hyperlink ref="G27" r:id="rId191" tooltip="https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=ERINGOGO"/>
-    <hyperlink ref="J27" r:id="rId192" tooltip="https://www.amazon.it/dp/B0F8W81X7Y?psc=1"/>
-    <hyperlink ref="K27" r:id="rId193" tooltip="https://images-na.ssl-images-amazon.com/images/I/7132zWnxJ5L._AC_US600_.jpg"/>
-    <hyperlink ref="L27" r:id="rId194" tooltip="https://www.amazon.it/dp/B0F8W81X7Y"/>
+    <hyperlink ref="AW26" r:id="rId189" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1CO438NU9H9Y"/>
+    <hyperlink ref="C27" r:id="rId190" tooltip="https://www.amazon.it/dp/B0FKRC3KQY"/>
+    <hyperlink ref="G27" r:id="rId191" tooltip="https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Yaasier"/>
+    <hyperlink ref="J27" r:id="rId192" tooltip="https://www.amazon.it/dp/B0FKRC3KQY?psc=1"/>
+    <hyperlink ref="K27" r:id="rId193" tooltip="https://images-na.ssl-images-amazon.com/images/I/511XZVAimmL._AC_US600_.jpg"/>
+    <hyperlink ref="L27" r:id="rId194" tooltip="https://www.amazon.it/dp/B0FKRC3KQY"/>
     <hyperlink ref="M27" r:id="rId195" tooltip="https://www.amazon.it/b?node=13713022031"/>
     <hyperlink ref="N27" r:id="rId196"/>
-    <hyperlink ref="AW27" r:id="rId197" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2YR5O9XGNUDX4"/>
-    <hyperlink ref="C28" r:id="rId198" tooltip="https://www.amazon.it/dp/B0F9NJM4V9"/>
-    <hyperlink ref="G28" r:id="rId199" tooltip="https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Liwankaqi"/>
-    <hyperlink ref="J28" r:id="rId200" tooltip="https://www.amazon.it/dp/B0F9NJM4V9?psc=1"/>
-    <hyperlink ref="K28" r:id="rId201" tooltip="https://images-na.ssl-images-amazon.com/images/I/61GdOBS8v+L._AC_US600_.jpg"/>
-    <hyperlink ref="L28" r:id="rId202" tooltip="https://www.amazon.it/dp/B0F9NJM4V9"/>
-    <hyperlink ref="M28" r:id="rId203" tooltip="https://www.amazon.it/b?node=13713022031"/>
-    <hyperlink ref="N28" r:id="rId204"/>
-    <hyperlink ref="AW28" r:id="rId205" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1CO438NU9H9Y"/>
-    <hyperlink ref="C29" r:id="rId206" tooltip="https://www.amazon.it/dp/B0FKRC3KQY"/>
-    <hyperlink ref="G29" r:id="rId207" tooltip="https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Yaasier"/>
-    <hyperlink ref="J29" r:id="rId208" tooltip="https://www.amazon.it/dp/B0FKRC3KQY?psc=1"/>
-    <hyperlink ref="K29" r:id="rId209" tooltip="https://images-na.ssl-images-amazon.com/images/I/511XZVAimmL._AC_US600_.jpg"/>
-    <hyperlink ref="L29" r:id="rId210" tooltip="https://www.amazon.it/dp/B0FKRC3KQY"/>
-    <hyperlink ref="M29" r:id="rId211" tooltip="https://www.amazon.it/b?node=13713022031"/>
-    <hyperlink ref="N29" r:id="rId212"/>
-    <hyperlink ref="AW29" r:id="rId213" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=ATK258MBI08TX"/>
-    <hyperlink ref="C30" r:id="rId214" tooltip="https://www.amazon.it/dp/B0FMRNV3RZ"/>
-    <hyperlink ref="G30" r:id="rId215" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J30" r:id="rId216" tooltip="https://www.amazon.it/dp/B0FMRNV3RZ?psc=1"/>
-    <hyperlink ref="K30" r:id="rId217" tooltip="https://images-eu.ssl-images-amazon.com/images/I/511XZVAimmL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L30" r:id="rId218" tooltip="https://www.amazon.it/dp/B0FMRNV3RZ"/>
-    <hyperlink ref="C31" r:id="rId219" tooltip="https://www.amazon.it/dp/B0FN3GPQZM"/>
-    <hyperlink ref="G31" r:id="rId220" tooltip="https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Teant"/>
-    <hyperlink ref="J31" r:id="rId221" tooltip="https://www.amazon.it/dp/B0FN3GPQZM?psc=1"/>
-    <hyperlink ref="K31" r:id="rId222" tooltip="https://images-na.ssl-images-amazon.com/images/I/71gt+j80L3L._AC_US600_.jpg"/>
-    <hyperlink ref="L31" r:id="rId223" tooltip="https://www.amazon.it/dp/B0FN3GPQZM"/>
+    <hyperlink ref="AW27" r:id="rId197" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=ATK258MBI08TX"/>
+    <hyperlink ref="C28" r:id="rId198" tooltip="https://www.amazon.it/dp/B0FMRNV3RZ"/>
+    <hyperlink ref="G28" r:id="rId199" tooltip="https://www.amazon.itundefined"/>
+    <hyperlink ref="J28" r:id="rId200" tooltip="https://www.amazon.it/dp/B0FMRNV3RZ?psc=1"/>
+    <hyperlink ref="K28" r:id="rId201" tooltip="https://images-eu.ssl-images-amazon.com/images/I/511XZVAimmL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L28" r:id="rId202" tooltip="https://www.amazon.it/dp/B0FMRNV3RZ"/>
+    <hyperlink ref="C29" r:id="rId203" tooltip="https://www.amazon.it/dp/B0FN3GPQZM"/>
+    <hyperlink ref="G29" r:id="rId204" tooltip="https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Teant"/>
+    <hyperlink ref="J29" r:id="rId205" tooltip="https://www.amazon.it/dp/B0FN3GPQZM?psc=1"/>
+    <hyperlink ref="K29" r:id="rId206" tooltip="https://images-na.ssl-images-amazon.com/images/I/71gt+j80L3L._AC_US600_.jpg"/>
+    <hyperlink ref="L29" r:id="rId207" tooltip="https://www.amazon.it/dp/B0FN3GPQZM"/>
+    <hyperlink ref="M29" r:id="rId208" tooltip="https://www.amazon.it/b?node=13713022031"/>
+    <hyperlink ref="N29" r:id="rId209"/>
+    <hyperlink ref="AW29" r:id="rId210" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3EVTWEH1TBVG5"/>
+    <hyperlink ref="C30" r:id="rId211" tooltip="https://www.amazon.it/dp/B0FP52HNHM"/>
+    <hyperlink ref="G30" r:id="rId212" tooltip="https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=PattenlLevi"/>
+    <hyperlink ref="J30" r:id="rId213" tooltip="https://www.amazon.it/dp/B0FP52HNHM?psc=1"/>
+    <hyperlink ref="K30" r:id="rId214" tooltip="https://images-na.ssl-images-amazon.com/images/I/41qFOExg5PL._AC_US600_.jpg"/>
+    <hyperlink ref="L30" r:id="rId215" tooltip="https://www.amazon.it/dp/B0FP52HNHM"/>
+    <hyperlink ref="M30" r:id="rId216" tooltip="https://www.amazon.it/b?node=13713022031"/>
+    <hyperlink ref="N30" r:id="rId217"/>
+    <hyperlink ref="AW30" r:id="rId218" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A28PZKXD42YVSB"/>
+    <hyperlink ref="C31" r:id="rId219" tooltip="https://www.amazon.it/dp/B0FP9CGZYN"/>
+    <hyperlink ref="G31" r:id="rId220" tooltip="https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Yaasier"/>
+    <hyperlink ref="J31" r:id="rId221" tooltip="https://www.amazon.it/dp/B0FP9CGZYN?psc=1"/>
+    <hyperlink ref="K31" r:id="rId222" tooltip="https://images-na.ssl-images-amazon.com/images/I/61mGX4QmLkL._AC_US600_.jpg"/>
+    <hyperlink ref="L31" r:id="rId223" tooltip="https://www.amazon.it/dp/B0FP9CGZYN"/>
     <hyperlink ref="M31" r:id="rId224" tooltip="https://www.amazon.it/b?node=13713022031"/>
     <hyperlink ref="N31" r:id="rId225"/>
-    <hyperlink ref="AW31" r:id="rId226" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3EVTWEH1TBVG5"/>
-    <hyperlink ref="C32" r:id="rId227" tooltip="https://www.amazon.it/dp/B0FP52HNHM"/>
-    <hyperlink ref="G32" r:id="rId228" tooltip="https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=PattenlLevi"/>
-    <hyperlink ref="J32" r:id="rId229" tooltip="https://www.amazon.it/dp/B0FP52HNHM?psc=1"/>
-    <hyperlink ref="K32" r:id="rId230" tooltip="https://images-na.ssl-images-amazon.com/images/I/41qFOExg5PL._AC_US600_.jpg"/>
-    <hyperlink ref="L32" r:id="rId231" tooltip="https://www.amazon.it/dp/B0FP52HNHM"/>
+    <hyperlink ref="AW31" r:id="rId226" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=ATK258MBI08TX"/>
+    <hyperlink ref="C32" r:id="rId227" tooltip="https://www.amazon.it/dp/B0FRBB876G"/>
+    <hyperlink ref="G32" r:id="rId228" tooltip="https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=MITE+GUARD"/>
+    <hyperlink ref="J32" r:id="rId229" tooltip="https://www.amazon.it/dp/B0FRBB876G?psc=1"/>
+    <hyperlink ref="K32" r:id="rId230" tooltip="https://images-na.ssl-images-amazon.com/images/I/71yKveOz1uL._AC_US600_.jpg"/>
+    <hyperlink ref="L32" r:id="rId231" tooltip="https://www.amazon.it/dp/B0FRBB876G"/>
     <hyperlink ref="M32" r:id="rId232" tooltip="https://www.amazon.it/b?node=13713022031"/>
     <hyperlink ref="N32" r:id="rId233"/>
-    <hyperlink ref="AW32" r:id="rId234" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A28PZKXD42YVSB"/>
-    <hyperlink ref="C33" r:id="rId235" tooltip="https://www.amazon.it/dp/B0FP9CGZYN"/>
-    <hyperlink ref="G33" r:id="rId236" tooltip="https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Yaasier"/>
-    <hyperlink ref="J33" r:id="rId237" tooltip="https://www.amazon.it/dp/B0FP9CGZYN?psc=1"/>
-    <hyperlink ref="K33" r:id="rId238" tooltip="https://images-na.ssl-images-amazon.com/images/I/61mGX4QmLkL._AC_US600_.jpg"/>
-    <hyperlink ref="L33" r:id="rId239" tooltip="https://www.amazon.it/dp/B0FP9CGZYN"/>
-    <hyperlink ref="M33" r:id="rId240" tooltip="https://www.amazon.it/b?node=13713022031"/>
-    <hyperlink ref="N33" r:id="rId241"/>
-    <hyperlink ref="AW33" r:id="rId242" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=ATK258MBI08TX"/>
-    <hyperlink ref="C34" r:id="rId243" tooltip="https://www.amazon.it/dp/B0FRBB876G"/>
-    <hyperlink ref="G34" r:id="rId244" tooltip="https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=MITE+GUARD"/>
-    <hyperlink ref="J34" r:id="rId245" tooltip="https://www.amazon.it/dp/B0FRBB876G?psc=1"/>
-    <hyperlink ref="K34" r:id="rId246" tooltip="https://images-na.ssl-images-amazon.com/images/I/71yKveOz1uL._AC_US600_.jpg"/>
-    <hyperlink ref="L34" r:id="rId247" tooltip="https://www.amazon.it/dp/B0FRBB876G"/>
-    <hyperlink ref="M34" r:id="rId248" tooltip="https://www.amazon.it/b?node=13713022031"/>
-    <hyperlink ref="N34" r:id="rId249"/>
-    <hyperlink ref="C35" r:id="rId250" tooltip="https://www.amazon.it/dp/B0FW3MWVJR"/>
-    <hyperlink ref="G35" r:id="rId251" tooltip="https://www.amazon.it/stores/JIGOO-IT/page/7F1C5254-18CC-4331-A449-F5F68B2E288D?lp_asin=B0FW3MWVJR&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J35" r:id="rId252" tooltip="https://www.amazon.it/dp/B0FW3MWVJR?psc=1"/>
-    <hyperlink ref="K35" r:id="rId253" tooltip="https://images-na.ssl-images-amazon.com/images/I/61R1ViIQaTL._AC_US600_.jpg"/>
-    <hyperlink ref="L35" r:id="rId254" tooltip="https://www.amazon.it/dp/B0FW3MWVJR"/>
+    <hyperlink ref="C33" r:id="rId234" tooltip="https://www.amazon.it/dp/B0FW3MWVJR"/>
+    <hyperlink ref="G33" r:id="rId235" tooltip="https://www.amazon.it/stores/JIGOO-IT/page/7F1C5254-18CC-4331-A449-F5F68B2E288D?lp_asin=B0FW3MWVJR&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J33" r:id="rId236" tooltip="https://www.amazon.it/dp/B0FW3MWVJR?psc=1"/>
+    <hyperlink ref="K33" r:id="rId237" tooltip="https://images-na.ssl-images-amazon.com/images/I/61R1ViIQaTL._AC_US600_.jpg"/>
+    <hyperlink ref="L33" r:id="rId238" tooltip="https://www.amazon.it/dp/B0FW3MWVJR"/>
+    <hyperlink ref="M33" r:id="rId239" tooltip="https://www.amazon.it/b?node=13713022031"/>
+    <hyperlink ref="N33" r:id="rId240"/>
+    <hyperlink ref="AW33" r:id="rId241" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A99P1VJD8HKQ6"/>
+    <hyperlink ref="C34" r:id="rId242" tooltip="https://www.amazon.it/dp/B0FYM1D13D"/>
+    <hyperlink ref="G34" r:id="rId243" tooltip="https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Yaasier"/>
+    <hyperlink ref="J34" r:id="rId244" tooltip="https://www.amazon.it/dp/B0FYM1D13D?psc=1"/>
+    <hyperlink ref="K34" r:id="rId245" tooltip="https://images-na.ssl-images-amazon.com/images/I/51dJLeDXofL._AC_US600_.jpg"/>
+    <hyperlink ref="L34" r:id="rId246" tooltip="https://www.amazon.it/dp/B0FYM1D13D"/>
+    <hyperlink ref="M34" r:id="rId247" tooltip="https://www.amazon.it/b?node=13713022031"/>
+    <hyperlink ref="N34" r:id="rId248"/>
+    <hyperlink ref="AW34" r:id="rId249" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=ATK258MBI08TX"/>
+    <hyperlink ref="C35" r:id="rId250" tooltip="https://www.amazon.it/dp/B0GJS592V3"/>
+    <hyperlink ref="G35" r:id="rId251" tooltip="https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Yaasier"/>
+    <hyperlink ref="J35" r:id="rId252" tooltip="https://www.amazon.it/dp/B0GJS592V3?psc=1"/>
+    <hyperlink ref="K35" r:id="rId253" tooltip="https://images-na.ssl-images-amazon.com/images/I/51lAD9Ta2TL._AC_US600_.jpg"/>
+    <hyperlink ref="L35" r:id="rId254" tooltip="https://www.amazon.it/dp/B0GJS592V3"/>
     <hyperlink ref="M35" r:id="rId255" tooltip="https://www.amazon.it/b?node=13713022031"/>
     <hyperlink ref="N35" r:id="rId256"/>
-    <hyperlink ref="AW35" r:id="rId257" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A99P1VJD8HKQ6"/>
-    <hyperlink ref="C36" r:id="rId258" tooltip="https://www.amazon.it/dp/B0FYM1D13D"/>
-    <hyperlink ref="G36" r:id="rId259" tooltip="https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Yaasier"/>
-    <hyperlink ref="J36" r:id="rId260" tooltip="https://www.amazon.it/dp/B0FYM1D13D?psc=1"/>
-    <hyperlink ref="K36" r:id="rId261" tooltip="https://images-na.ssl-images-amazon.com/images/I/51dJLeDXofL._AC_US600_.jpg"/>
-    <hyperlink ref="L36" r:id="rId262" tooltip="https://www.amazon.it/dp/B0FYM1D13D"/>
+    <hyperlink ref="AW35" r:id="rId257" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=ATK258MBI08TX"/>
+    <hyperlink ref="C36" r:id="rId258" tooltip="https://www.amazon.it/dp/B0GTYZLWW3"/>
+    <hyperlink ref="G36" r:id="rId259" tooltip="https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Vehiwell"/>
+    <hyperlink ref="J36" r:id="rId260" tooltip="https://www.amazon.it/dp/B0GTYZLWW3?psc=1"/>
+    <hyperlink ref="K36" r:id="rId261" tooltip="https://images-na.ssl-images-amazon.com/images/I/71RQJ5XzBgL._AC_US600_.jpg"/>
+    <hyperlink ref="L36" r:id="rId262" tooltip="https://www.amazon.it/dp/B0GTYZLWW3"/>
     <hyperlink ref="M36" r:id="rId263" tooltip="https://www.amazon.it/b?node=13713022031"/>
     <hyperlink ref="N36" r:id="rId264"/>
-    <hyperlink ref="AW36" r:id="rId265" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=ATK258MBI08TX"/>
-    <hyperlink ref="C37" r:id="rId266" tooltip="https://www.amazon.it/dp/B0GJS592V3"/>
-    <hyperlink ref="G37" r:id="rId267" tooltip="https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Yaasier"/>
-    <hyperlink ref="J37" r:id="rId268" tooltip="https://www.amazon.it/dp/B0GJS592V3?psc=1"/>
-    <hyperlink ref="K37" r:id="rId269" tooltip="https://images-na.ssl-images-amazon.com/images/I/51lAD9Ta2TL._AC_US600_.jpg"/>
-    <hyperlink ref="L37" r:id="rId270" tooltip="https://www.amazon.it/dp/B0GJS592V3"/>
+    <hyperlink ref="AW36" r:id="rId265" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1F2NCGM6KYOZU"/>
+    <hyperlink ref="C37" r:id="rId266" tooltip="https://www.amazon.it/dp/B0H418FY5Y"/>
+    <hyperlink ref="G37" r:id="rId267" tooltip="https://www.amazon.it/stores/Lubluelu/page/14418463-A3CB-412E-B0D5-36E2BEE36429?lp_asin=B0H418FY5Y&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J37" r:id="rId268" tooltip="https://www.amazon.it/dp/B0H418FY5Y?psc=1"/>
+    <hyperlink ref="K37" r:id="rId269" tooltip="https://images-na.ssl-images-amazon.com/images/I/61InrYvl2-L._AC_US600_.jpg"/>
+    <hyperlink ref="L37" r:id="rId270" tooltip="https://www.amazon.it/dp/B0H418FY5Y"/>
     <hyperlink ref="M37" r:id="rId271" tooltip="https://www.amazon.it/b?node=13713022031"/>
     <hyperlink ref="N37" r:id="rId272"/>
-    <hyperlink ref="AW37" r:id="rId273" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=ATK258MBI08TX"/>
-    <hyperlink ref="C38" r:id="rId274" tooltip="https://www.amazon.it/dp/B0GTYZLWW3"/>
-    <hyperlink ref="G38" r:id="rId275" tooltip="https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Vehiwell"/>
-    <hyperlink ref="J38" r:id="rId276" tooltip="https://www.amazon.it/dp/B0GTYZLWW3?psc=1"/>
-    <hyperlink ref="K38" r:id="rId277" tooltip="https://images-na.ssl-images-amazon.com/images/I/71RQJ5XzBgL._AC_US600_.jpg"/>
-    <hyperlink ref="L38" r:id="rId278" tooltip="https://www.amazon.it/dp/B0GTYZLWW3"/>
-    <hyperlink ref="M38" r:id="rId279" tooltip="https://www.amazon.it/b?node=13713022031"/>
-    <hyperlink ref="N38" r:id="rId280"/>
-    <hyperlink ref="AW38" r:id="rId281" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1F2NCGM6KYOZU"/>
-    <hyperlink ref="C39" r:id="rId282" tooltip="https://www.amazon.it/dp/B0H418FY5Y"/>
-    <hyperlink ref="G39" r:id="rId283" tooltip="https://www.amazon.it/stores/Lubluelu/page/14418463-A3CB-412E-B0D5-36E2BEE36429?lp_asin=B0H418FY5Y&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J39" r:id="rId284" tooltip="https://www.amazon.it/dp/B0H418FY5Y?psc=1"/>
-    <hyperlink ref="K39" r:id="rId285" tooltip="https://images-na.ssl-images-amazon.com/images/I/61InrYvl2-L._AC_US600_.jpg"/>
-    <hyperlink ref="L39" r:id="rId286" tooltip="https://www.amazon.it/dp/B0H418FY5Y"/>
-    <hyperlink ref="M39" r:id="rId287" tooltip="https://www.amazon.it/b?node=13713022031"/>
-    <hyperlink ref="N39" r:id="rId288"/>
-    <hyperlink ref="AW39" r:id="rId289" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A23BRZJD26C30N"/>
-    <hyperlink ref="C40" r:id="rId290" tooltip="https://www.amazon.it/dp/B0H6Q8KWCD"/>
-    <hyperlink ref="G40" r:id="rId291" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J40" r:id="rId292" tooltip="https://www.amazon.it/dp/B0H6Q8KWCD?psc=1"/>
-    <hyperlink ref="K40" r:id="rId293" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61nyUqj7HSL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L40" r:id="rId294" tooltip="https://www.amazon.it/dp/B0H6Q8KWCD"/>
+    <hyperlink ref="AW37" r:id="rId273" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A23BRZJD26C30N"/>
   </hyperlinks>
-  <drawing r:id="rId295"/>
+  <drawing r:id="rId274"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G27"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
-  <cols>
-    <col min="1" max="1" width="25" style="1" customWidth="1"/>
-    <col min="2" max="5" width="13" style="2" customWidth="1"/>
-    <col min="6" max="6" width="10" style="4" customWidth="1"/>
-    <col min="7" max="7" width="10" style="6" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="inlineStr">
-        <is>
-          <t>品牌</t>
-        </is>
-      </c>
-      <c r="B1" s="8" t="inlineStr">
-        <is>
-          <t>月销量</t>
-        </is>
-      </c>
-      <c r="C1" s="8" t="inlineStr">
-        <is>
-          <t>月销售额(€)</t>
-        </is>
-      </c>
-      <c r="D1" s="8" t="inlineStr">
-        <is>
-          <t>近1年销量</t>
-        </is>
-      </c>
-      <c r="E1" s="8" t="inlineStr">
-        <is>
-          <t>近一年销售额(€)</t>
-        </is>
-      </c>
-      <c r="F1" s="10" t="inlineStr">
-        <is>
-          <t>平均价格(€)</t>
-        </is>
-      </c>
-      <c r="G1" s="12" t="inlineStr">
-        <is>
-          <t>市场份额</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="14" t="inlineStr">
-        <is>
-          <t>JIGOO</t>
-        </is>
-      </c>
-      <c r="B2" s="15">
-        <v>391</v>
-      </c>
-      <c r="C2" s="15">
-        <v>26926</v>
-      </c>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="20">
-        <v>68.86445012787723</v>
-      </c>
-      <c r="G2" s="22">
-        <v>0.28898743532889876</v>
-      </c>
-    </row>
-    <row r="3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="14" t="inlineStr">
-        <is>
-          <t>Hoover</t>
-        </is>
-      </c>
-      <c r="B3" s="15">
-        <v>202</v>
-      </c>
-      <c r="C3" s="15">
-        <v>19392</v>
-      </c>
-      <c r="D3" s="15"/>
-      <c r="E3" s="15"/>
-      <c r="F3" s="20">
-        <v>96.0</v>
-      </c>
-      <c r="G3" s="22">
-        <v>0.14929785661492978</v>
-      </c>
-    </row>
-    <row r="4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="14" t="inlineStr">
-        <is>
-          <t>HYCHIKA BETTER TOOLS FOR BETTER LIFE</t>
-        </is>
-      </c>
-      <c r="B4" s="15">
-        <v>235</v>
-      </c>
-      <c r="C4" s="15">
-        <v>15310</v>
-      </c>
-      <c r="D4" s="15"/>
-      <c r="E4" s="15"/>
-      <c r="F4" s="20">
-        <v>65.14893617021276</v>
-      </c>
-      <c r="G4" s="22">
-        <v>0.1736881005173688</v>
-      </c>
-    </row>
-    <row r="5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="14" t="inlineStr">
-        <is>
-          <t>Cecotec</t>
-        </is>
-      </c>
-      <c r="B5" s="15">
-        <v>284</v>
-      </c>
-      <c r="C5" s="15">
-        <v>10764</v>
-      </c>
-      <c r="D5" s="15"/>
-      <c r="E5" s="15"/>
-      <c r="F5" s="20">
-        <v>37.901408450704224</v>
-      </c>
-      <c r="G5" s="22">
-        <v>0.2099039172209904</v>
-      </c>
-    </row>
-    <row r="6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="14" t="inlineStr">
-        <is>
-          <t>KÄRCHER</t>
-        </is>
-      </c>
-      <c r="B6" s="15">
-        <v>78</v>
-      </c>
-      <c r="C6" s="15">
-        <v>4798</v>
-      </c>
-      <c r="D6" s="15"/>
-      <c r="E6" s="15"/>
-      <c r="F6" s="20">
-        <v>61.51282051282051</v>
-      </c>
-      <c r="G6" s="22">
-        <v>0.057649667405764965</v>
-      </c>
-    </row>
-    <row r="7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="14" t="inlineStr">
-        <is>
-          <t>Circlio</t>
-        </is>
-      </c>
-      <c r="B7" s="15">
-        <v>41</v>
-      </c>
-      <c r="C7" s="15">
-        <v>3505</v>
-      </c>
-      <c r="D7" s="15"/>
-      <c r="E7" s="15"/>
-      <c r="F7" s="20">
-        <v>85.48780487804878</v>
-      </c>
-      <c r="G7" s="22">
-        <v>0.030303030303030304</v>
-      </c>
-    </row>
-    <row r="8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="14" t="inlineStr">
-        <is>
-          <t>XINYUDAILY</t>
-        </is>
-      </c>
-      <c r="B8" s="15">
-        <v>47</v>
-      </c>
-      <c r="C8" s="15">
-        <v>3125</v>
-      </c>
-      <c r="D8" s="15"/>
-      <c r="E8" s="15"/>
-      <c r="F8" s="20">
-        <v>66.48936170212765</v>
-      </c>
-      <c r="G8" s="22">
-        <v>0.03473762010347376</v>
-      </c>
-    </row>
-    <row r="9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="14" t="inlineStr">
-        <is>
-          <t>Lubluelu</t>
-        </is>
-      </c>
-      <c r="B9" s="15">
-        <v>26</v>
-      </c>
-      <c r="C9" s="15">
-        <v>2080</v>
-      </c>
-      <c r="D9" s="15"/>
-      <c r="E9" s="15"/>
-      <c r="F9" s="20">
-        <v>80.0</v>
-      </c>
-      <c r="G9" s="22">
-        <v>0.019216555801921657</v>
-      </c>
-    </row>
-    <row r="10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="14" t="inlineStr">
-        <is>
-          <t>Elecbee</t>
-        </is>
-      </c>
-      <c r="B10" s="15">
-        <v>17</v>
-      </c>
-      <c r="C10" s="15">
-        <v>1122</v>
-      </c>
-      <c r="D10" s="15"/>
-      <c r="E10" s="15"/>
-      <c r="F10" s="20">
-        <v>66.0</v>
-      </c>
-      <c r="G10" s="22">
-        <v>0.012564671101256468</v>
-      </c>
-    </row>
-    <row r="11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="14" t="inlineStr">
-        <is>
-          <t>HAUSHOF</t>
-        </is>
-      </c>
-      <c r="B11" s="15">
-        <v>16</v>
-      </c>
-      <c r="C11" s="15">
-        <v>1120</v>
-      </c>
-      <c r="D11" s="15"/>
-      <c r="E11" s="15"/>
-      <c r="F11" s="20">
-        <v>70.0</v>
-      </c>
-      <c r="G11" s="22">
-        <v>0.011825572801182557</v>
-      </c>
-    </row>
-    <row r="12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="14" t="inlineStr">
-        <is>
-          <t>ALLILUYAA</t>
-        </is>
-      </c>
-      <c r="B12" s="15">
-        <v>16</v>
-      </c>
-      <c r="C12" s="15">
-        <v>464</v>
-      </c>
-      <c r="D12" s="15"/>
-      <c r="E12" s="15"/>
-      <c r="F12" s="20">
-        <v>29.0</v>
-      </c>
-      <c r="G12" s="22">
-        <v>0.011825572801182557</v>
-      </c>
-    </row>
-    <row r="13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="14" t="inlineStr">
-        <is>
-          <t>Dibea</t>
-        </is>
-      </c>
-      <c r="B13" s="15">
-        <v>0</v>
-      </c>
-      <c r="C13" s="15">
-        <v>0</v>
-      </c>
-      <c r="D13" s="15"/>
-      <c r="E13" s="15"/>
-      <c r="F13" s="20"/>
-      <c r="G13" s="22">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="14" t="inlineStr">
-        <is>
-          <t>ERINGOGO</t>
-        </is>
-      </c>
-      <c r="B14" s="15">
-        <v>0</v>
-      </c>
-      <c r="C14" s="15">
-        <v>0</v>
-      </c>
-      <c r="D14" s="15"/>
-      <c r="E14" s="15"/>
-      <c r="F14" s="20"/>
-      <c r="G14" s="22">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="14" t="inlineStr">
-        <is>
-          <t>FEPPO</t>
-        </is>
-      </c>
-      <c r="B15" s="15">
-        <v>0</v>
-      </c>
-      <c r="C15" s="15">
-        <v>0</v>
-      </c>
-      <c r="D15" s="15"/>
-      <c r="E15" s="15"/>
-      <c r="F15" s="20"/>
-      <c r="G15" s="22">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="14" t="inlineStr">
-        <is>
-          <t>Lambluefly</t>
-        </is>
-      </c>
-      <c r="B16" s="15">
-        <v>0</v>
-      </c>
-      <c r="C16" s="15">
-        <v>0</v>
-      </c>
-      <c r="D16" s="15"/>
-      <c r="E16" s="15"/>
-      <c r="F16" s="20"/>
-      <c r="G16" s="22">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="14" t="inlineStr">
-        <is>
-          <t>Liwankaqi</t>
-        </is>
-      </c>
-      <c r="B17" s="15">
-        <v>0</v>
-      </c>
-      <c r="C17" s="15">
-        <v>0</v>
-      </c>
-      <c r="D17" s="15"/>
-      <c r="E17" s="15"/>
-      <c r="F17" s="20"/>
-      <c r="G17" s="22">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="18" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="14" t="inlineStr">
-        <is>
-          <t>MITE GUARD</t>
-        </is>
-      </c>
-      <c r="B18" s="15">
-        <v>0</v>
-      </c>
-      <c r="C18" s="15">
-        <v>0</v>
-      </c>
-      <c r="D18" s="15"/>
-      <c r="E18" s="15"/>
-      <c r="F18" s="20"/>
-      <c r="G18" s="22">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="19" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="14" t="inlineStr">
-        <is>
-          <t>Mayking</t>
-        </is>
-      </c>
-      <c r="B19" s="15">
-        <v>0</v>
-      </c>
-      <c r="C19" s="15">
-        <v>0</v>
-      </c>
-      <c r="D19" s="15"/>
-      <c r="E19" s="15"/>
-      <c r="F19" s="20"/>
-      <c r="G19" s="22">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="14" t="inlineStr">
-        <is>
-          <t>PattenlLevi</t>
-        </is>
-      </c>
-      <c r="B20" s="15">
-        <v>0</v>
-      </c>
-      <c r="C20" s="15">
-        <v>0</v>
-      </c>
-      <c r="D20" s="15"/>
-      <c r="E20" s="15"/>
-      <c r="F20" s="20"/>
-      <c r="G20" s="22">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="21" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="14" t="inlineStr">
-        <is>
-          <t>SIKITUT</t>
-        </is>
-      </c>
-      <c r="B21" s="15">
-        <v>0</v>
-      </c>
-      <c r="C21" s="15">
-        <v>0</v>
-      </c>
-      <c r="D21" s="15"/>
-      <c r="E21" s="15"/>
-      <c r="F21" s="20"/>
-      <c r="G21" s="22">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="14" t="inlineStr">
-        <is>
-          <t>Teant</t>
-        </is>
-      </c>
-      <c r="B22" s="15">
-        <v>0</v>
-      </c>
-      <c r="C22" s="15">
-        <v>0</v>
-      </c>
-      <c r="D22" s="15"/>
-      <c r="E22" s="15"/>
-      <c r="F22" s="20"/>
-      <c r="G22" s="22">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="23" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="14" t="inlineStr">
-        <is>
-          <t>Tiazhan</t>
-        </is>
-      </c>
-      <c r="B23" s="15">
-        <v>0</v>
-      </c>
-      <c r="C23" s="15">
-        <v>0</v>
-      </c>
-      <c r="D23" s="15"/>
-      <c r="E23" s="15"/>
-      <c r="F23" s="20"/>
-      <c r="G23" s="22">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="24" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="14" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="B24" s="15">
-        <v>0</v>
-      </c>
-      <c r="C24" s="15">
-        <v>0</v>
-      </c>
-      <c r="D24" s="15"/>
-      <c r="E24" s="15"/>
-      <c r="F24" s="20"/>
-      <c r="G24" s="22">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="25" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="14" t="inlineStr">
-        <is>
-          <t>Vehiwell</t>
-        </is>
-      </c>
-      <c r="B25" s="15">
-        <v>0</v>
-      </c>
-      <c r="C25" s="15">
-        <v>0</v>
-      </c>
-      <c r="D25" s="15"/>
-      <c r="E25" s="15"/>
-      <c r="F25" s="20"/>
-      <c r="G25" s="22">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="26" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="14" t="inlineStr">
-        <is>
-          <t>Vihoom</t>
-        </is>
-      </c>
-      <c r="B26" s="15">
-        <v>0</v>
-      </c>
-      <c r="C26" s="15">
-        <v>0</v>
-      </c>
-      <c r="D26" s="15"/>
-      <c r="E26" s="15"/>
-      <c r="F26" s="20"/>
-      <c r="G26" s="22">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="27" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="14" t="inlineStr">
-        <is>
-          <t>Yaasier</t>
-        </is>
-      </c>
-      <c r="B27" s="15">
-        <v>0</v>
-      </c>
-      <c r="C27" s="15">
-        <v>0</v>
-      </c>
-      <c r="D27" s="15"/>
-      <c r="E27" s="15"/>
-      <c r="F27" s="20"/>
-      <c r="G27" s="22">
-        <v>0.0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G26"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
@@ -15034,7 +13797,7 @@
     <row r="1" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>卖家</t>
+          <t>品牌</t>
         </is>
       </c>
       <c r="B1" s="8" t="inlineStr">
@@ -15071,28 +13834,28 @@
     <row r="2" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>JIGOO</t>
         </is>
       </c>
       <c r="B2" s="15">
-        <v>646</v>
+        <v>385</v>
       </c>
       <c r="C2" s="15">
-        <v>42461</v>
+        <v>26812</v>
       </c>
       <c r="D2" s="15"/>
       <c r="E2" s="15"/>
       <c r="F2" s="20">
-        <v>65.72910216718266</v>
+        <v>69.64155844155844</v>
       </c>
       <c r="G2" s="22">
-        <v>0.47745750184774577</v>
+        <v>0.2858203414996288</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="inlineStr">
         <is>
-          <t>tekworld</t>
+          <t>Hoover</t>
         </is>
       </c>
       <c r="B3" s="15">
@@ -15107,202 +13870,202 @@
         <v>96.0</v>
       </c>
       <c r="G3" s="22">
-        <v>0.14929785661492978</v>
+        <v>0.14996288047512993</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="inlineStr">
         <is>
-          <t>Cecotec Italy</t>
+          <t>HYCHIKA BETTER TOOLS FOR BETTER LIFE</t>
         </is>
       </c>
       <c r="B4" s="15">
-        <v>284</v>
+        <v>235</v>
       </c>
       <c r="C4" s="15">
-        <v>10764</v>
+        <v>15310</v>
       </c>
       <c r="D4" s="15"/>
       <c r="E4" s="15"/>
       <c r="F4" s="20">
-        <v>37.901408450704224</v>
+        <v>65.14893617021276</v>
       </c>
       <c r="G4" s="22">
-        <v>0.2099039172209904</v>
+        <v>0.1744617668893838</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="inlineStr">
         <is>
-          <t>ZILLOW TECH</t>
+          <t>Cecotec</t>
         </is>
       </c>
       <c r="B5" s="15">
-        <v>60</v>
+        <v>284</v>
       </c>
       <c r="C5" s="15">
-        <v>4199</v>
+        <v>10764</v>
       </c>
       <c r="D5" s="15"/>
       <c r="E5" s="15"/>
       <c r="F5" s="20">
-        <v>69.98333333333333</v>
+        <v>37.901408450704224</v>
       </c>
       <c r="G5" s="22">
-        <v>0.04434589800443459</v>
+        <v>0.21083890126206384</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="inlineStr">
         <is>
-          <t>Zenithor it</t>
+          <t>KÄRCHER</t>
         </is>
       </c>
       <c r="B6" s="15">
-        <v>41</v>
+        <v>78</v>
       </c>
       <c r="C6" s="15">
-        <v>3505</v>
+        <v>4798</v>
       </c>
       <c r="D6" s="15"/>
       <c r="E6" s="15"/>
       <c r="F6" s="20">
-        <v>85.48780487804878</v>
+        <v>61.51282051282051</v>
       </c>
       <c r="G6" s="22">
-        <v>0.030303030303030304</v>
+        <v>0.05790645879732739</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="inlineStr">
         <is>
-          <t>XINYU-EU</t>
+          <t>Circlio</t>
         </is>
       </c>
       <c r="B7" s="15">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C7" s="15">
-        <v>3125</v>
+        <v>3505</v>
       </c>
       <c r="D7" s="15"/>
       <c r="E7" s="15"/>
       <c r="F7" s="20">
-        <v>66.48936170212765</v>
+        <v>85.48780487804878</v>
       </c>
       <c r="G7" s="22">
-        <v>0.03473762010347376</v>
+        <v>0.030438010393466965</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>Quantaforge</t>
+          <t>XINYUDAILY</t>
         </is>
       </c>
       <c r="B8" s="15">
-        <v>18</v>
+        <v>47</v>
       </c>
       <c r="C8" s="15">
-        <v>2340</v>
+        <v>3125</v>
       </c>
       <c r="D8" s="15"/>
       <c r="E8" s="15"/>
       <c r="F8" s="20">
-        <v>130.0</v>
+        <v>66.48936170212765</v>
       </c>
       <c r="G8" s="22">
-        <v>0.013303769401330377</v>
+        <v>0.034892353377876766</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>WUHAN RENHOTEC TECHNOLOGY LTD</t>
+          <t>Lubluelu</t>
         </is>
       </c>
       <c r="B9" s="15">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="C9" s="15">
-        <v>1122</v>
+        <v>2080</v>
       </c>
       <c r="D9" s="15"/>
       <c r="E9" s="15"/>
       <c r="F9" s="20">
-        <v>66.0</v>
+        <v>80.0</v>
       </c>
       <c r="G9" s="22">
-        <v>0.012564671101256468</v>
+        <v>0.019302152932442463</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>TS.Werkzeug</t>
+          <t>Elecbee</t>
         </is>
       </c>
       <c r="B10" s="15">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C10" s="15">
-        <v>1120</v>
+        <v>1122</v>
       </c>
       <c r="D10" s="15"/>
       <c r="E10" s="15"/>
       <c r="F10" s="20">
-        <v>70.0</v>
+        <v>66.0</v>
       </c>
       <c r="G10" s="22">
-        <v>0.011825572801182557</v>
+        <v>0.012620638455827766</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>HONGTELL</t>
+          <t>HAUSHOF</t>
         </is>
       </c>
       <c r="B11" s="15">
         <v>16</v>
       </c>
       <c r="C11" s="15">
-        <v>464</v>
+        <v>1120</v>
       </c>
       <c r="D11" s="15"/>
       <c r="E11" s="15"/>
       <c r="F11" s="20">
-        <v>29.0</v>
+        <v>70.0</v>
       </c>
       <c r="G11" s="22">
-        <v>0.011825572801182557</v>
+        <v>0.011878247958426132</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="14" t="inlineStr">
         <is>
-          <t>yefengdianzi</t>
+          <t>ALLILUYAA</t>
         </is>
       </c>
       <c r="B12" s="15">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C12" s="15">
-        <v>114</v>
+        <v>464</v>
       </c>
       <c r="D12" s="15"/>
       <c r="E12" s="15"/>
       <c r="F12" s="20">
-        <v>19.0</v>
+        <v>29.0</v>
       </c>
       <c r="G12" s="22">
-        <v>0.004434589800443459</v>
+        <v>0.011878247958426132</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="14" t="inlineStr">
         <is>
-          <t>ANISE EDALS52</t>
+          <t>Dibea</t>
         </is>
       </c>
       <c r="B13" s="15">
@@ -15321,7 +14084,7 @@
     <row r="14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="14" t="inlineStr">
         <is>
-          <t>DIBEA HOME</t>
+          <t>FEPPO</t>
         </is>
       </c>
       <c r="B14" s="15">
@@ -15340,7 +14103,7 @@
     <row r="15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="14" t="inlineStr">
         <is>
-          <t>DLLest</t>
+          <t>Lambluefly</t>
         </is>
       </c>
       <c r="B15" s="15">
@@ -15359,7 +14122,7 @@
     <row r="16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="inlineStr">
         <is>
-          <t>Fiercelion</t>
+          <t>Liwankaqi</t>
         </is>
       </c>
       <c r="B16" s="15">
@@ -15378,7 +14141,7 @@
     <row r="17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="inlineStr">
         <is>
-          <t>Lubluelu Official</t>
+          <t>MITE GUARD</t>
         </is>
       </c>
       <c r="B17" s="15">
@@ -15397,7 +14160,7 @@
     <row r="18" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="inlineStr">
         <is>
-          <t>NOEL AND RUTH JOHNSTON LTD</t>
+          <t>Mayking</t>
         </is>
       </c>
       <c r="B18" s="15">
@@ -15416,7 +14179,7 @@
     <row r="19" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="inlineStr">
         <is>
-          <t>PETERTOS Kft.</t>
+          <t>PattenlLevi</t>
         </is>
       </c>
       <c r="B19" s="15">
@@ -15435,7 +14198,7 @@
     <row r="20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="inlineStr">
         <is>
-          <t>Renyu</t>
+          <t>SIKITUT</t>
         </is>
       </c>
       <c r="B20" s="15">
@@ -15473,7 +14236,7 @@
     <row r="22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Tiazhan</t>
         </is>
       </c>
       <c r="B22" s="15">
@@ -15492,7 +14255,7 @@
     <row r="23" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="inlineStr">
         <is>
-          <t>eusmarthousehold</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="B23" s="15">
@@ -15511,7 +14274,7 @@
     <row r="24" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="inlineStr">
         <is>
-          <t>idbvd</t>
+          <t>Vehiwell</t>
         </is>
       </c>
       <c r="B24" s="15">
@@ -15530,7 +14293,7 @@
     <row r="25" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="inlineStr">
         <is>
-          <t>liwantech</t>
+          <t>Vihoom</t>
         </is>
       </c>
       <c r="B25" s="15">
@@ -15549,7 +14312,7 @@
     <row r="26" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="inlineStr">
         <is>
-          <t>lnBtkuuco</t>
+          <t>Yaasier</t>
         </is>
       </c>
       <c r="B26" s="15">
@@ -15562,6 +14325,517 @@
       <c r="E26" s="15"/>
       <c r="F26" s="20"/>
       <c r="G26" s="22">
+        <v>0.0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G24"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="25" style="1" customWidth="1"/>
+    <col min="2" max="5" width="13" style="2" customWidth="1"/>
+    <col min="6" max="6" width="10" style="4" customWidth="1"/>
+    <col min="7" max="7" width="10" style="6" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>卖家</t>
+        </is>
+      </c>
+      <c r="B1" s="8" t="inlineStr">
+        <is>
+          <t>月销量</t>
+        </is>
+      </c>
+      <c r="C1" s="8" t="inlineStr">
+        <is>
+          <t>月销售额(€)</t>
+        </is>
+      </c>
+      <c r="D1" s="8" t="inlineStr">
+        <is>
+          <t>近1年销量</t>
+        </is>
+      </c>
+      <c r="E1" s="8" t="inlineStr">
+        <is>
+          <t>近一年销售额(€)</t>
+        </is>
+      </c>
+      <c r="F1" s="10" t="inlineStr">
+        <is>
+          <t>平均价格(€)</t>
+        </is>
+      </c>
+      <c r="G1" s="12" t="inlineStr">
+        <is>
+          <t>市场份额</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="14" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="B2" s="15">
+        <v>646</v>
+      </c>
+      <c r="C2" s="15">
+        <v>42461</v>
+      </c>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="20">
+        <v>65.72910216718266</v>
+      </c>
+      <c r="G2" s="22">
+        <v>0.4795842613214551</v>
+      </c>
+    </row>
+    <row r="3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="14" t="inlineStr">
+        <is>
+          <t>tekworld</t>
+        </is>
+      </c>
+      <c r="B3" s="15">
+        <v>202</v>
+      </c>
+      <c r="C3" s="15">
+        <v>19392</v>
+      </c>
+      <c r="D3" s="15"/>
+      <c r="E3" s="15"/>
+      <c r="F3" s="20">
+        <v>96.0</v>
+      </c>
+      <c r="G3" s="22">
+        <v>0.14996288047512993</v>
+      </c>
+    </row>
+    <row r="4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="14" t="inlineStr">
+        <is>
+          <t>Cecotec Italy</t>
+        </is>
+      </c>
+      <c r="B4" s="15">
+        <v>284</v>
+      </c>
+      <c r="C4" s="15">
+        <v>10764</v>
+      </c>
+      <c r="D4" s="15"/>
+      <c r="E4" s="15"/>
+      <c r="F4" s="20">
+        <v>37.901408450704224</v>
+      </c>
+      <c r="G4" s="22">
+        <v>0.21083890126206384</v>
+      </c>
+    </row>
+    <row r="5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="14" t="inlineStr">
+        <is>
+          <t>ZILLOW TECH</t>
+        </is>
+      </c>
+      <c r="B5" s="15">
+        <v>60</v>
+      </c>
+      <c r="C5" s="15">
+        <v>4199</v>
+      </c>
+      <c r="D5" s="15"/>
+      <c r="E5" s="15"/>
+      <c r="F5" s="20">
+        <v>69.98333333333333</v>
+      </c>
+      <c r="G5" s="22">
+        <v>0.044543429844097995</v>
+      </c>
+    </row>
+    <row r="6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="14" t="inlineStr">
+        <is>
+          <t>Zenithor it</t>
+        </is>
+      </c>
+      <c r="B6" s="15">
+        <v>41</v>
+      </c>
+      <c r="C6" s="15">
+        <v>3505</v>
+      </c>
+      <c r="D6" s="15"/>
+      <c r="E6" s="15"/>
+      <c r="F6" s="20">
+        <v>85.48780487804878</v>
+      </c>
+      <c r="G6" s="22">
+        <v>0.030438010393466965</v>
+      </c>
+    </row>
+    <row r="7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="14" t="inlineStr">
+        <is>
+          <t>XINYU-EU</t>
+        </is>
+      </c>
+      <c r="B7" s="15">
+        <v>47</v>
+      </c>
+      <c r="C7" s="15">
+        <v>3125</v>
+      </c>
+      <c r="D7" s="15"/>
+      <c r="E7" s="15"/>
+      <c r="F7" s="20">
+        <v>66.48936170212765</v>
+      </c>
+      <c r="G7" s="22">
+        <v>0.034892353377876766</v>
+      </c>
+    </row>
+    <row r="8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="14" t="inlineStr">
+        <is>
+          <t>Quantaforge</t>
+        </is>
+      </c>
+      <c r="B8" s="15">
+        <v>18</v>
+      </c>
+      <c r="C8" s="15">
+        <v>2340</v>
+      </c>
+      <c r="D8" s="15"/>
+      <c r="E8" s="15"/>
+      <c r="F8" s="20">
+        <v>130.0</v>
+      </c>
+      <c r="G8" s="22">
+        <v>0.013363028953229399</v>
+      </c>
+    </row>
+    <row r="9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="14" t="inlineStr">
+        <is>
+          <t>WUHAN RENHOTEC TECHNOLOGY LTD</t>
+        </is>
+      </c>
+      <c r="B9" s="15">
+        <v>17</v>
+      </c>
+      <c r="C9" s="15">
+        <v>1122</v>
+      </c>
+      <c r="D9" s="15"/>
+      <c r="E9" s="15"/>
+      <c r="F9" s="20">
+        <v>66.0</v>
+      </c>
+      <c r="G9" s="22">
+        <v>0.012620638455827766</v>
+      </c>
+    </row>
+    <row r="10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="14" t="inlineStr">
+        <is>
+          <t>TS.Werkzeug</t>
+        </is>
+      </c>
+      <c r="B10" s="15">
+        <v>16</v>
+      </c>
+      <c r="C10" s="15">
+        <v>1120</v>
+      </c>
+      <c r="D10" s="15"/>
+      <c r="E10" s="15"/>
+      <c r="F10" s="20">
+        <v>70.0</v>
+      </c>
+      <c r="G10" s="22">
+        <v>0.011878247958426132</v>
+      </c>
+    </row>
+    <row r="11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="14" t="inlineStr">
+        <is>
+          <t>HONGTELL</t>
+        </is>
+      </c>
+      <c r="B11" s="15">
+        <v>16</v>
+      </c>
+      <c r="C11" s="15">
+        <v>464</v>
+      </c>
+      <c r="D11" s="15"/>
+      <c r="E11" s="15"/>
+      <c r="F11" s="20">
+        <v>29.0</v>
+      </c>
+      <c r="G11" s="22">
+        <v>0.011878247958426132</v>
+      </c>
+    </row>
+    <row r="12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="14" t="inlineStr">
+        <is>
+          <t>ANISE EDALS52</t>
+        </is>
+      </c>
+      <c r="B12" s="15">
+        <v>0</v>
+      </c>
+      <c r="C12" s="15">
+        <v>0</v>
+      </c>
+      <c r="D12" s="15"/>
+      <c r="E12" s="15"/>
+      <c r="F12" s="20"/>
+      <c r="G12" s="22">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="14" t="inlineStr">
+        <is>
+          <t>DIBEA HOME</t>
+        </is>
+      </c>
+      <c r="B13" s="15">
+        <v>0</v>
+      </c>
+      <c r="C13" s="15">
+        <v>0</v>
+      </c>
+      <c r="D13" s="15"/>
+      <c r="E13" s="15"/>
+      <c r="F13" s="20"/>
+      <c r="G13" s="22">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="14" t="inlineStr">
+        <is>
+          <t>DLLest</t>
+        </is>
+      </c>
+      <c r="B14" s="15">
+        <v>0</v>
+      </c>
+      <c r="C14" s="15">
+        <v>0</v>
+      </c>
+      <c r="D14" s="15"/>
+      <c r="E14" s="15"/>
+      <c r="F14" s="20"/>
+      <c r="G14" s="22">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="14" t="inlineStr">
+        <is>
+          <t>Fiercelion</t>
+        </is>
+      </c>
+      <c r="B15" s="15">
+        <v>0</v>
+      </c>
+      <c r="C15" s="15">
+        <v>0</v>
+      </c>
+      <c r="D15" s="15"/>
+      <c r="E15" s="15"/>
+      <c r="F15" s="20"/>
+      <c r="G15" s="22">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="14" t="inlineStr">
+        <is>
+          <t>Lubluelu Official</t>
+        </is>
+      </c>
+      <c r="B16" s="15">
+        <v>0</v>
+      </c>
+      <c r="C16" s="15">
+        <v>0</v>
+      </c>
+      <c r="D16" s="15"/>
+      <c r="E16" s="15"/>
+      <c r="F16" s="20"/>
+      <c r="G16" s="22">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="14" t="inlineStr">
+        <is>
+          <t>NOEL AND RUTH JOHNSTON LTD</t>
+        </is>
+      </c>
+      <c r="B17" s="15">
+        <v>0</v>
+      </c>
+      <c r="C17" s="15">
+        <v>0</v>
+      </c>
+      <c r="D17" s="15"/>
+      <c r="E17" s="15"/>
+      <c r="F17" s="20"/>
+      <c r="G17" s="22">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="18" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="14" t="inlineStr">
+        <is>
+          <t>PETERTOS Kft.</t>
+        </is>
+      </c>
+      <c r="B18" s="15">
+        <v>0</v>
+      </c>
+      <c r="C18" s="15">
+        <v>0</v>
+      </c>
+      <c r="D18" s="15"/>
+      <c r="E18" s="15"/>
+      <c r="F18" s="20"/>
+      <c r="G18" s="22">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="19" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="14" t="inlineStr">
+        <is>
+          <t>Renyu</t>
+        </is>
+      </c>
+      <c r="B19" s="15">
+        <v>0</v>
+      </c>
+      <c r="C19" s="15">
+        <v>0</v>
+      </c>
+      <c r="D19" s="15"/>
+      <c r="E19" s="15"/>
+      <c r="F19" s="20"/>
+      <c r="G19" s="22">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="14" t="inlineStr">
+        <is>
+          <t>Teant</t>
+        </is>
+      </c>
+      <c r="B20" s="15">
+        <v>0</v>
+      </c>
+      <c r="C20" s="15">
+        <v>0</v>
+      </c>
+      <c r="D20" s="15"/>
+      <c r="E20" s="15"/>
+      <c r="F20" s="20"/>
+      <c r="G20" s="22">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="21" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="14" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B21" s="15">
+        <v>0</v>
+      </c>
+      <c r="C21" s="15">
+        <v>0</v>
+      </c>
+      <c r="D21" s="15"/>
+      <c r="E21" s="15"/>
+      <c r="F21" s="20"/>
+      <c r="G21" s="22">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="14" t="inlineStr">
+        <is>
+          <t>eusmarthousehold</t>
+        </is>
+      </c>
+      <c r="B22" s="15">
+        <v>0</v>
+      </c>
+      <c r="C22" s="15">
+        <v>0</v>
+      </c>
+      <c r="D22" s="15"/>
+      <c r="E22" s="15"/>
+      <c r="F22" s="20"/>
+      <c r="G22" s="22">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="23" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="14" t="inlineStr">
+        <is>
+          <t>liwantech</t>
+        </is>
+      </c>
+      <c r="B23" s="15">
+        <v>0</v>
+      </c>
+      <c r="C23" s="15">
+        <v>0</v>
+      </c>
+      <c r="D23" s="15"/>
+      <c r="E23" s="15"/>
+      <c r="F23" s="20"/>
+      <c r="G23" s="22">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="24" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="14" t="inlineStr">
+        <is>
+          <t>lnBtkuuco</t>
+        </is>
+      </c>
+      <c r="B24" s="15">
+        <v>0</v>
+      </c>
+      <c r="C24" s="15">
+        <v>0</v>
+      </c>
+      <c r="D24" s="15"/>
+      <c r="E24" s="15"/>
+      <c r="F24" s="20"/>
+      <c r="G24" s="22">
         <v>0.0</v>
       </c>
     </row>
